--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -2799,10 +2799,14 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>F01_A_MAIN_LT, F03_D_MAIN_LT, F04_D_MAIN_LT: completion lighting kind pendant_shade and fixed_lighting plan variant pendant_shade_rise100; family rebuilt; fixed_lighting validator 5971 checks, 0 failures on rerun (one contextual standing-view failure at F01_BAR_LT_DECK0 on the first run, absent on rerun and in the owner's final receipts); sweep overviews show the pendants. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2923,10 +2927,14 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>2A, 3D, 4D fittings monitor_top false; household_fridges plan instances FridgeIcebox; family rebuilt in Blender; the fabrication batch counts 4 monitors of 18 (test expects 4); 2A native capture and 3D/4D sweep overviews show oak iceboxes. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3265,10 +3273,14 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>Measured, not missing: every one of the 19 water closets instantiates bath_water_closet.glb with LowCistern and RemovableCisternLid visible; the cistern is 0.46 x 0.22 x 0.31 m with its top 0.80 m above the floor and at least 0.11 m clear of every bath wall (sweep census probe, implementation/baths/receipts). The raised lid (top 0.94 m) hides it from front-on stations, which is what the review saw. No data change; a lid-down default in unoccupied flats is a possible P3 follow-up.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -17649,10 +17661,14 @@
       </c>
       <c r="S248" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T248" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
+          <t>Measured, not a bug: the runtime census records F02_2C_FRIDGE_01 at yaw 90.0 degrees exactly (square to the east wall, 0.46 m off it); the skew in the review tiles is wide-angle perspective near the frame edge. No data change. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -22971,10 +22987,14 @@
       </c>
       <c r="S321" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T321" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>Not reproduced: the bath sweep at 49e5e3a1 renders 3D_wc's cistern in porcelain (implementation/baths/images/F03_D_BATH_OV.jpg); the magenta face in the review tile was transient.</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -25103,10 +25123,14 @@
       </c>
       <c r="S351" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T351" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="inlineStr">
+        <is>
+          <t>Blockout purpose text now reads 4A; the sweep caption shows it. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -26045,10 +26069,14 @@
       </c>
       <c r="S364" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T364" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>Cistern present (BW-018 measurement: 4A_wc LowCistern visible, 0.42 m clear of the east wall). The curtain/receptor part stays with BW-008.</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -27341,10 +27369,14 @@
       </c>
       <c r="S382" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T382" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>Keep note confirmed by the same probe: 4B's cistern is the family's low cistern, identical to every other unit.</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -28453,10 +28485,14 @@
       </c>
       <c r="S398" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T398" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>As F02_C_KITCHEN-004: F04_4C_FRIDGE_01 yaw 90.0 in the runtime census; no clipping in the data. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -29351,10 +29387,14 @@
       </c>
       <c r="S411" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T411" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr">
+        <is>
+          <t>Resolved by BW-010 (F04_D_MAIN_OV). implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -29577,10 +29617,14 @@
       </c>
       <c r="S414" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T414" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr">
+        <is>
+          <t>Resolved by BW-012: F04_4D_FRIDGE_01 is a dry icebox (F04_D_KITCHEN_OV). implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -29643,10 +29687,14 @@
       </c>
       <c r="S415" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T415" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T415" s="2" t="inlineStr">
+        <is>
+          <t>Runtime census lists F04_4D_STOVE_01 (orison_v2_stove.gd) with four grates and burner caps at (-10.6, -7.65) in F04_D_KITCHEN; the range mounts. The overview station does not frame it; no data change.</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -29701,10 +29749,14 @@
       </c>
       <c r="S416" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T416" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T416" s="2" t="inlineStr">
+        <is>
+          <t>Keep note closed with the swap above.</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -30129,10 +30181,14 @@
       </c>
       <c r="S422" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T422" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T422" s="2" t="inlineStr">
+        <is>
+          <t>F04_D_BED_STORAGE_DOOR leaf_state locked in completion_interiors_source; the sweep's threshold opening was refused (threshold_door: locked) and OrisonV2CompletionInteriorsTest now expects the refusal and skips the closet: with V2_TEST_UNIT=4D the four lock checks pass (implementation/slice1b/receipts). The suite still ends in its kitchen-to-hall leg (12 waypoints), which fails identically on main at 16f1d353 for 1A (38 waypoints, same target) and for 3D on this branch (14 waypoints): the fridge beside the kitchen door blocks the route line, a pre-existing defect flagged separately. On main the 4D leg already failed earlier, at the walk into the closet after opening its door (7 waypoints; implementation/baseline_completion_4D), so the lock removes a broken step rather than adding one. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -32471,10 +32527,14 @@
       </c>
       <c r="S455" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T455" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T455" s="2" t="inlineStr">
+        <is>
+          <t>Cistern present (BW-018 measurement: 5A_wc LowCistern visible, 0.15 m clear of the south wall). The pipe strip and register parts stay with BW-005 and heating_distribution.</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -34707,10 +34767,14 @@
       </c>
       <c r="S487" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T487" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T487" s="2" t="inlineStr">
+        <is>
+          <t>As F02_C_KITCHEN-004: F05_5C_FRIDGE_01 yaw 90.0 in the runtime census. implementation/slice1 (captures, batch.json, run receipts)</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -2065,10 +2065,14 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>Bay cage labels are single-sided (Label3D double_sided false) on the bay fronts.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2259,10 +2263,14 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>2C_bed1, 5C_bed1 and 6C_bed1 (with nightstands) removed at their owners (completion source; domestic_furniture_source; blockout anchors); 4C keeps its two beds (re-templated on 5C_bed0). Conversions started with existing variants: 2C session table and chair under the window, 5C pigment table (TableRect09) on the inner wall with a stool, 6C archive table under the window and two shelves on the east wall. Hero props (blanket walls, easel, drying rack, catalogue drawers) stay open on their room entries. Bedding validator expects 19 beds; tables 64, seating 43, storage 45 instances rebuilt. Suites: OrisonV2BeddingTest passes; the fabrication batch for the twelve rebuilt families passes; OrisonV2UpperFurnitureTest stays red on a pre-existing check (mesh material overrides: 394 failures on main at 16f1d353, 400 here, the six new native meshes counted the same way); the C-unit completion route stops at the 2C bath leg exactly as on main.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2733,10 +2741,14 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>The readability cues' nine ungoverned light pools (blue and orange OmniLights beside the stair on F01-F03, at the 2A/4B doors and the 4B terminal) are gated off in production (show_light_pools false in orison_v2_runtime_root). Remaining leaks, if any, need a capture to name.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2865,10 +2877,14 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>DomesticRadio_1A/1D/2C/3D/4C/4D added to domestic_radios_source (families from the 1928 catalogue: radiola table, Crosley Pup, homebrew regenerative); wireless tables (TableRect07 template) added to 1A, 3D and 4D on the south wall between the doors; orison_v2_radios.gd now places 18 units; the apartment batch test expects 18 receivers. DomesticRadioTest passes; in OrisonV2ApartmentBatchTest the new receivers pass their clearance and operator-stance checks, and the only remaining receiver failures are the pre-existing texture-backed-parts check (98 on main for the twelve, 142 for eighteen); the other red groups (46 fixed-furniture collisions, 18 wood, 12 category, 10 plant, 6 coffee, 2 plant) are identical on main.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -8479,10 +8495,14 @@
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T123" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>Entry sign labels single-sided; no mirrored read through the glass.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -9605,10 +9625,14 @@
       </c>
       <c r="S140" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T140" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>The orange-tan plane was the readability cues' WARM light pool on the core wall; gated off with BW-009.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10415,10 +10439,14 @@
       </c>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T151" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>1A_wireless_table at (-12.0, -6.95) yaw 180 and DomesticRadio_1A on it (BW-011).</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -12161,10 +12189,14 @@
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T174" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>1D_fabric_worktable record and anchor removed; the 1D_story_pattern_board anchor had no consumer and is gone.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -12317,10 +12349,14 @@
       </c>
       <c r="S176" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T176" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>DomesticRadio_1D on the existing 1D_wireless_table (BW-011).</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -13057,10 +13093,14 @@
       </c>
       <c r="S186" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T186" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>The 1D_fabric_shelf_01/02 anchors removed (they had no furniture consumer; the review's shelves were the baked template surfaces).</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -18155,10 +18195,14 @@
       </c>
       <c r="S255" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T255" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr">
+        <is>
+          <t>Removed with BW-002.</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -19031,10 +19075,14 @@
       </c>
       <c r="S267" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T267" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr">
+        <is>
+          <t>The powder-blue plane was the readability cues' PUBLIC light pool beside the stair; gated off with BW-009.</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -21749,10 +21797,14 @@
       </c>
       <c r="S304" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T304" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>Measured, not a bug: 3B_aw_wardrobe at yaw 0 on the north wall shows its two leaves and knobs to the room and the bed foot (implementation/slice2/images/F03_B_ALCOVE_DT3.jpg); the punchlist's back-to-room reading does not hold at this station. No data change.</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -30053,10 +30105,14 @@
       </c>
       <c r="S420" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T420" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr">
+        <is>
+          <t>F04_D_BATH_SWITCH anchor moved to (-6.1, 1.12, -9.75) yaw 0: the north wall beside the bath door, off the basin wall.</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -34001,10 +34057,14 @@
       </c>
       <c r="S476" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T476" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T476" s="2" t="inlineStr">
+        <is>
+          <t>Misread: the 'column radiator standing mid-room' is the shower's closed curtain pose (the fluted cream cylinder on its enamel tray); the heating data places no radiator in 5B's bath. The curtain's look is BW-008's item.</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -35261,10 +35321,14 @@
       </c>
       <c r="S494" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T494" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T494" s="2" t="inlineStr">
+        <is>
+          <t>5C_w0_wardrobe and its stance moved to the bedroom's east wall (3.45, 9.3) facing west; 5C_w1_wardrobe stays in the closet for F05_C_STUDIO-001.</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -35323,10 +35387,14 @@
       </c>
       <c r="S495" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T495" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T495" s="2" t="inlineStr">
+        <is>
+          <t>Removed with BW-002.</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -38417,10 +38485,14 @@
       </c>
       <c r="S538" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T538" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T538" s="2" t="inlineStr">
+        <is>
+          <t>6B_abed turned to yaw -90 with its head at the west wall (-14.6, 9.9) so the foot faces the hall door; nightstand at the window side (-15.35, 11.2); stances moved.</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -39739,10 +39811,14 @@
       </c>
       <c r="S557" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T557" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T557" s="2" t="inlineStr">
+        <is>
+          <t>Removed with BW-002.</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -40225,10 +40301,14 @@
       </c>
       <c r="S564" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T564" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T564" s="2" t="inlineStr">
+        <is>
+          <t>Lift-drive sign single-sided (the bulkhead finish part stays open).</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -2341,10 +2341,14 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>At the family recipes: TableRound03/TableRound10 carry an Edwardian turned oak column on a cruciform base of capped feet (column, feet and base in the variant's wood; worktop unchanged); Sofa195/Sofa210 carry rolled arms over the padded arm; Shelf01/02/04/07 stand on square oak posts with oak rails. Plans record column=turned, arms=rolled, posts=oak. The slab seat cushions and the shelves' painted-bin and tin stock (source surfaces) stay as they were. Verified at 4e589c0c: fabrication batch of the twelve rebuilt families exit 0 (tables 64, seating 43, storage 45 instances), upper lighting 9,257 checks with 0 failures, ten-room sweep with 0 failures; native captures of 2A_din_t, 2A_sofa, 2A_shelf0 and 5A_planshelf and the room overviews are under implementation/slice34.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2407,10 +2411,14 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>Root cause: a wall segment is one box finished with its owning space's class, and a wet room owns the shared wall, so the hall or bedroom beyond saw subway tile. orison_v2_blockout.gd now adds a 4 mm far-face skin on every interior wet wall, finished with the neighbouring space's class and cut by the same openings; exterior walls and wet-to-wet walls are left alone; no collision, no new owner. Verified at 67c233a5 and 47d93679: the private-hall overviews of 5A, 4C and 2C read plaster where implementation/skinbase (the pre-skin tree at 9f95732c, same station) still shows the bath's subway tile; the bath interiors keep their tile (implementation/slice5, slice5b). OrisonV2FloorSurfaceTest reports the same 57 failures (bath floor/ceiling face ownership and the roof decks) before and after the skin, byte-identical stderr sets (implementation/floorbase vs slice5), so they pre-exist. A speckled patch at the 5A hall corner in the first capture did not reproduce at the same station in the second run and is a screen-space transient, not geometry.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3145,10 +3153,14 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Room-leaf paints a step lower (door_prop.gd interior palette); the entry leaves keep their darker corridor paints. The panel relief already exists; the transom blow-out over 4A stays open. Verified at 67c233a5: F05_B_VESTIBULE_OV shows the darker entry leaf beside the lighter room leaf with panel relief intact; F05_A_PRIVATE_HALL_OV and F04_C_PRIVATE_HALL_OV read the room leaves without the white blow-out (implementation/slice5).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3219,10 +3231,14 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>Twelve flush domes (flush_dome_rise100 at 2.9 m) on the west and east public halls of F02-F06 (two on the 6.1 m halls of F05/F06), each hall on a landlord's switch beside the stair end or the unit door jamb; blockout anchors, room_lighting records, fixed_lighting plan instances and mirror; family rebuilt. Landings and cores (open stair voids) still have no practical: they need a wall sconce placed against the stair geometry and stay open. Verified at 4e589c0c: upper lighting 9,257 checks, 0 failures (the first run's four F05_C standing-capsule failures cleared with the 5C wardrobe and pigment-table moves); the hall sweep overviews show the domes lit and the switches on the wainscot (implementation/slice3b).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3573,10 +3589,14 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every apartment entry leaf carries an enamel numeral plate (0.11 x 0.075 m porcelain-finish plate, single-sided Label3D numeral in cobalt) on its hall face at 1.6 m, placed by orison_v2_domestic_doors.gd from the door's connected spaces, seated on the leaf's actual painted face by a vertex probe (the panel rails stand proud of the slab). The readability cues' debug portal masses stay off in production, but their floating 2A, 4B and PUBLIC ENTRANCE labels remain: OrisonV2DoorCasingsTest holds every portal to exactly one Label3D child, so retiring them is the test owner's call, not this slice's. Verified at 0b5f8a7b: both door-route suites and OrisonV2DoorCasingsTest exit 0, and the hall sweep shows the enamel plates reading 4B, 2B and 3D on the leaves (implementation/numerals2; the earlier implementation/numerals run showed why the plate had to move onto the panel bed). </t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3709,10 +3729,14 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>The peephole is a brass lens cylinder (door_prop.gd), not an emitter; the bright disc in the reviews is the lamp's specular on brass. The wainscot relief stays open.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -16797,10 +16821,14 @@
       </c>
       <c r="S236" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T236" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr">
+        <is>
+          <t>2B_fabric_shelf_01/02 posts are oak (BW-003). (implementation/slice34)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -23595,10 +23623,14 @@
       </c>
       <c r="S329" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T329" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>The landing has no ceiling (stair void); a sconce on the core wall is the remaining item after BW-017's hall domes.</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -23801,10 +23833,14 @@
       </c>
       <c r="S332" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T332" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>F04_WEST_HALL_LT dome (BW-017, implementation/slice3b); the terrazzo scale stays with BW-020.</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -24007,10 +24043,14 @@
       </c>
       <c r="S335" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T335" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>4D's entry leaf carries its numeral (BW-022). (implementation/numerals2/images/F03_SOUTHWEST_HALL_OV.jpg shows 3D's plate; 4D's leaf carries the same assembly.)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -24431,10 +24471,14 @@
       </c>
       <c r="S341" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T341" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>F04_EAST_HALL_LT dome (BW-017, implementation/slice3b/images/F04_EAST_HALL_OV.jpg); the transom blow-out stays with BW-016.</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -31443,10 +31487,14 @@
       </c>
       <c r="S439" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T439" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T439" s="2" t="inlineStr">
+        <is>
+          <t>F05_WEST_HALL_LT_A/_B domes (BW-017, implementation/slice3b/images/F05_WEST_HALL_OV.jpg); the leaf finish stays with BW-016.</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -32777,10 +32825,14 @@
       </c>
       <c r="S458" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T458" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T458" s="2" t="inlineStr">
+        <is>
+          <t>5A_planshelf posts are oak (BW-003); the placeholder blocks on it stay as source stock. (implementation/slice34/images/F05_A_STUDY_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -33337,10 +33389,14 @@
       </c>
       <c r="S466" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T466" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr">
+        <is>
+          <t>5B_din_t is the pedestal form now (BW-003). (implementation/slice34)</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -39181,10 +39237,14 @@
       </c>
       <c r="S548" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T548" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T548" s="2" t="inlineStr">
+        <is>
+          <t>6C_sofa carries rolled arms (BW-003); 6C_cof (Coffee06) is unchanged. (implementation/slice34/images/F06_C_MAIN_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -2197,10 +2197,14 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>First part, existing variants only: seventeen furniture records in completion_interiors_source (anchors plus consumers on the shared native templates 2A_din_dc1, 2A_sofa, 2B_fabric_worktable, 2A_projector_stand, 4B_wake_nightstand, 3B_tools0) and the three family plans; ten records moved; 1D_din_dc2 retired. Doors, taps, showers, toilets, stoves, fridges, switched lights and the route waypoints untouched; every new piece sits clear of the completion routes' walk points and the switch approach capsules. Still open from the unit pages: pieces that need new families or recipes (armchair, floor lamp, folding screen, mirror, mixer, cable hooks, blankets, desktop stock), listed on their own ids. Verified at 992ae898 and 1fadb5ad: the twelve rebuilt families pass the fabrication batch (implementation/slice6d, exit 0 with native captures of the templates); upper lighting 9,257 checks, 0 failures; LightSwitchModelTest exit 0; upper furniture 402 failures, the same count as the slice-2 run; completion routes 1D 25 waypoints clean, 2C and 4C at their pre-existing bath leg, 1A 15, 3D 16 and 4D 12 ending at their pre-existing kitchen legs (implementation/routes6b); the ten-room sweep shows every piece in place (implementation/slice6). The route test's standing point beside the storage door moved out of the leaf's quarter turn: in today's runs that walk failed from slice 1 onward and passed at main by centimetres (implementation/bisect_16f1d353, bisect_8df6ee18, bisect_5bf9202c).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2481,10 +2485,14 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>Measured at 1fadb5ad with a seven-space capture (implementation/ducts): the 2D and 5D ceiling branches hang on trapeze hangers whose rods seat at the slab soffit and end in the fitted louvred register box; the 4B and 5C bath registers are the gravity-grille variant, no register reads as a shade; the 5C branch crosses the vestibule ceiling on its hangers and enters the studio wall above the door head rather than ending in mid-air. Open remainder, P3: a sheet collar where a branch passes through a partition (the sleeves family covers only the authored wall service openings).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3021,10 +3029,14 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>orison_v2_room_lighting.gd adds a brass signal-outlet plate (70 x 115 x 6 mm, brass_dull) beside every switch of the room and completion rosters, on the side toward the room centre so it stays on wall rather than on a jamb. Passive draw: no owner, no collision, no lead stub until a device record connects to it. Verified at 992ae898: upper lighting and LightSwitchModelTest exit 0 with the plates in place; implementation/slice6/images/outlet_detail_F01_A_BED.jpg shows the brass plate beside the bedroom switch.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -10463,12 +10475,12 @@
       </c>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>1A_wireless_table at (-12.0, -6.95) yaw 180 and DomesticRadio_1A on it (BW-011).</t>
+          <t>Done by BW-011 in slice 2: 1A_wireless_table (TableRect07) with DomesticRadio_1A on the long wall (implementation/slice2).</t>
         </is>
       </c>
     </row>
@@ -10557,10 +10569,14 @@
       </c>
       <c r="S152" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T152" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>1A_reading_chair (ChairDark, angled 30 degrees to the window with its back to the kitchen door) and 1A_side_table (TableRect08) by the window; 1A_table and 1A_chair moved onto the long wall as the marking table. Deviations: the seating family has no armchair variant and the task-lamp family no floor stand, so the chair is the dark dining chair and the lamp is deferred with the family work. (implementation/slice6/images/F01_A_MAIN_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10857,10 +10873,14 @@
       </c>
       <c r="S156" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T156" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>Done by BW-010 in slice 1: F01_A_MAIN_LT is a pendant_shade (implementation/slice1).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -11613,10 +11633,14 @@
       </c>
       <c r="S166" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T166" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>1A_dressing_table (TableRect05) on the west wall beside the bed head (the window wall is taken by the bed foot and the wardrobe), 1A_bed_chair (ChairDark) at the bed foot, 1A_bedside (Nightstand02) on the door side of the head. The wardrobe garment set stays with BW-019. (implementation/slice6/images/F01_A_BED_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -11773,10 +11797,14 @@
       </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T168" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>1A_study_desk (TableRect05) under the window, 1A_study_chair (ChairDark) tucked in, 1A_register_shelf (Shelf01) on the east wall facing the door; the bookpile stock stays with the desktop_stock items. (implementation/slice6/images/F01_A_STUDY_TH.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -12213,12 +12241,12 @@
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>1D_fabric_worktable record and anchor removed; the 1D_story_pattern_board anchor had no consumer and is gone.</t>
+          <t>Done in slice 2 with BW-002: 1D carries no fabric worktable, pattern board or hall shelves (completion source lists wc, bed, wardrobe, sink support, dining set, cupboard, wireless table).</t>
         </is>
       </c>
     </row>
@@ -12303,10 +12331,14 @@
       </c>
       <c r="S175" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T175" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>1D_daybed (Sofa195) along the north wall away from the window with 1D_alarm_chest (Nightstand02, the nearest shared variant to a deal chest) at its head; the dining table turned to the window pier with one chair (1D_din_dc2 retired). The wireless table stays on the south wall where BW-011 put the radio with its stance; the blanket and apron silhouettes wait for the cloth family. (implementation/slice6/images/F01_D_MAIN_OV.jpg; the 1D route passes all 25 waypoints)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -12373,12 +12405,12 @@
       </c>
       <c r="S176" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T176" s="2" t="inlineStr">
         <is>
-          <t>DomesticRadio_1D on the existing 1D_wireless_table (BW-011).</t>
+          <t>Done by BW-011 in slice 2: DomesticRadio_1D on 1D_wireless_table (implementation/slice2).</t>
         </is>
       </c>
     </row>
@@ -12915,10 +12947,14 @@
       </c>
       <c r="S183" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T183" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>1D_bed_chair (ChairDark) at the bed foot. The blackout blanket and the uniform on the leaf need the cloth family and the wardrobe garment set (BW-019) and stay open. (implementation/slice6/images/F01_D_BED_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -17305,10 +17341,14 @@
       </c>
       <c r="S242" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T242" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr">
+        <is>
+          <t>2C_rig_table (TableRect05) on the window wall facing the vestibule opening with 2C_din_dc2 as the operator's chair; 2C_din_t and 2C_din_dc1 moved against the kitchen-side wall as the late-meal surface, stances moved with them. The mixer (signal family), reel deck, headphones and the hook strip stay open. (implementation/slice6/images/F02_C_MAIN_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -18223,12 +18263,12 @@
       </c>
       <c r="S255" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T255" s="2" t="inlineStr">
         <is>
-          <t>Removed with BW-002.</t>
+          <t>Done by BW-002 in slice 2: 2C_bed1 and 2C_bed1_ns retired (implementation/slice2).</t>
         </is>
       </c>
     </row>
@@ -22355,10 +22395,14 @@
       </c>
       <c r="S311" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T311" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="inlineStr">
+        <is>
+          <t>3D_chaise (Sofa195) along the long wall under the dome. The folding screen, mirror and fringed lamp need new pieces and stay open. (implementation/slice6/images/F03_D_MAIN_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -22479,10 +22523,14 @@
       </c>
       <c r="S313" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T313" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="inlineStr">
+        <is>
+          <t>Done by BW-010 in slice 1: F03_D_MAIN_LT is a pendant_shade (implementation/slice1).</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -28103,10 +28151,14 @@
       </c>
       <c r="S391" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T391" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>4C_museum_shelf (Shelf01) on the window wall beside the window; the covered objects, cloth and the courier corner's floor stock stay with the desktop_stock items. (implementation/slice6/images/F04_C_MAIN_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -28161,10 +28213,14 @@
       </c>
       <c r="S392" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T392" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T392" s="2" t="inlineStr">
+        <is>
+          <t>Done by BW-011 in slice 2: DomesticRadio_4C on 4C_wireless_table (implementation/slice2).</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -29301,10 +29357,14 @@
       </c>
       <c r="S408" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T408" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="inlineStr">
+        <is>
+          <t>4D_settee (Sofa195) on the long wall (the window wall carries the radiator), 4D_lamp_table (TableRect08) beside it, 4D_chair2 (ChairDark) at the dining table; the wireless table and radio from BW-011. The landlord's lamp and the print wait for the task-lamp and wall-art hooks. (implementation/slice6/images/F04_D_MAIN_OV.jpg)</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -34339,10 +34399,14 @@
       </c>
       <c r="S479" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T479" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T479" s="2" t="inlineStr">
+        <is>
+          <t>Not reproduced: implementation/ducts/images/F05_C_VESTIBULE_TH.jpg shows the branch carried on two hangers across the vestibule and into the studio partition at the door head; the collar at that penetration is BW-005's P3 remainder.</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -10963,10 +10963,14 @@
       </c>
       <c r="S157" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T157" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>proper_meals_for_one: mug, dish rack and a plate on the drainboard (no prep cabinet in the A plan). Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11189,10 +11193,14 @@
       </c>
       <c r="S160" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T160" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>The runtime census of the slice-7 kitchen sweep lists F01_1A_STOVE_01 (orison_v2_stove.gd) at (-10.6, -7.65) in F01_A_KITCHEN with its semantic anchor; the range mounts, the dossier's stations simply looked past it (implementation/slice7/receipts/sweep_shots__node_census.json).</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -12643,10 +12651,14 @@
       </c>
       <c r="S179" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T179" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>thermos_and_leftovers: mug and rack on the drainboard; kettle, tin and plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -15319,10 +15331,14 @@
       </c>
       <c r="S215" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T215" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
+          <t>measured_portions: two tins and the kettle on the prep cabinet beside the toaster; the drainboard mug and rack were already there. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -16523,10 +16539,14 @@
       </c>
       <c r="S231" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T231" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr">
+        <is>
+          <t>cooks_for_others: bread board and kettle on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -17559,10 +17579,14 @@
       </c>
       <c r="S245" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T245" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr">
+        <is>
+          <t>takeout_plus_coffee: mug and rack on the drainboard; kettle, tin and a second mug on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -20393,10 +20417,14 @@
       </c>
       <c r="S284" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T284" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
+          <t>jars_and_compost: tin and bread board on the prep cabinet (the jar row is a V1 collector form and waits). Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -21507,10 +21535,14 @@
       </c>
       <c r="S299" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T299" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr">
+        <is>
+          <t>simple_and_maintained: bread board and tin on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -22613,10 +22645,14 @@
       </c>
       <c r="S314" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T314" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>tea_honey_lemon: mug, rack and a plate on the drainboard (no prep cabinet in the D plan). Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -22823,10 +22859,14 @@
       </c>
       <c r="S317" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T317" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T317" s="2" t="inlineStr">
+        <is>
+          <t>As F01_A_KITCHEN-004: F03_3D_STOVE_01 is in the census at (-10.6, -7.65) in F03_D_KITCHEN (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -25699,10 +25739,14 @@
       </c>
       <c r="S357" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T357" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="inlineStr">
+        <is>
+          <t>identical_weekday_meals: two tins and a plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -26871,10 +26915,14 @@
       </c>
       <c r="S373" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T373" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>kettle_toaster_survival: kettle and tin on the prep cabinet, clear of the toaster's -x tray travel; the counter mug and rack were already there. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -28431,10 +28479,14 @@
       </c>
       <c r="S395" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T395" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr">
+        <is>
+          <t>quick_food_vs_preserved: mug and rack on the drainboard; two tins and a bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -29633,10 +29685,14 @@
       </c>
       <c r="S412" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T412" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>inadequate_cookware: mug, rack and one plate on the drainboard. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -32251,10 +32307,14 @@
       </c>
       <c r="S449" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T449" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T449" s="2" t="inlineStr">
+        <is>
+          <t>efficient_batching: two tins and a bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -33605,10 +33665,14 @@
       </c>
       <c r="S468" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T468" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T468" s="2" t="inlineStr">
+        <is>
+          <t>forgets_to_eat: kettle and a second mug on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -34741,10 +34805,14 @@
       </c>
       <c r="S484" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T484" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T484" s="2" t="inlineStr">
+        <is>
+          <t>meals_between_coats: plate and bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -37201,10 +37269,14 @@
       </c>
       <c r="S518" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T518" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T518" s="2" t="inlineStr">
+        <is>
+          <t>eats_standing: plate and tin on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -38325,10 +38397,14 @@
       </c>
       <c r="S534" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T534" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T534" s="2" t="inlineStr">
+        <is>
+          <t>cold_drinks_and_rings: kettle and tin on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -39391,10 +39467,14 @@
       </c>
       <c r="S549" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T549" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T549" s="2" t="inlineStr">
+        <is>
+          <t>careful_and_spare: the missing drainboard mug; kettle and plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -10245,10 +10245,14 @@
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T148" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Evelyn Marsh: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall between the entry and living-room leaf swings (three doors leave no other wall). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -12031,10 +12035,14 @@
       </c>
       <c r="S171" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T171" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Teresa Vale: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall beside the switch (the only wall both leaf swings and the route leave clear; two metres from the door rather than the dossier's 0.9). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -14661,10 +14669,14 @@
       </c>
       <c r="S206" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T206" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Mina Vale: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the south wall, clear of the entry leaf's swing and the living-room opening. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -16009,10 +16021,14 @@
       </c>
       <c r="S224" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T224" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Lena Ortiz: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall beside the switch (the only wall both leaf swings and the route leave clear; two metres from the door rather than the dossier's 0.9). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -17193,10 +17209,14 @@
       </c>
       <c r="S240" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T240" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Juno Kells: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the west wall, clear of the entry leaf's quarter turn and the route line. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -18431,10 +18451,14 @@
       </c>
       <c r="S257" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T257" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="inlineStr">
+        <is>
+          <t>Kept: no slice touches the restricted interiors; the ducts capture at 1fadb5ad shows the same empty, lit room with its ceiling branch (implementation/ducts/images/F02_D_RESTRICTED_OV.jpg).</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -19903,10 +19927,14 @@
       </c>
       <c r="S277" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T277" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Malcolm Reed: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the south wall, clear of the entry leaf's swing and the living-room opening. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -21029,10 +21057,14 @@
       </c>
       <c r="S292" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T292" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Omar Bell: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall beside the switch (the only wall both leaf swings and the route leave clear; two metres from the door rather than the dossier's 0.9). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -22201,10 +22233,14 @@
       </c>
       <c r="S308" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T308" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Rhea Sato: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall between the entry and living-room leaf swings (three doors leave no other wall). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -23431,10 +23467,14 @@
       </c>
       <c r="S325" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T325" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>Kept: unchanged by every slice; captured empty at 1fadb5ad (implementation/ducts).</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -25097,10 +25137,14 @@
       </c>
       <c r="S348" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T348" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Peter Wren: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall beside the switch (the only wall both leaf swings and the route leave clear; two metres from the door rather than the dossier's 0.9). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -26417,10 +26461,14 @@
       </c>
       <c r="S366" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T366" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for the player: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the south wall, clear of the entry leaf's swing and the living-room opening. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -27973,10 +28021,14 @@
       </c>
       <c r="S388" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T388" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Cam Ortiz and Noel Price: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the west wall, clear of the entry leaf's quarter turn and the route line. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -29195,10 +29247,14 @@
       </c>
       <c r="S405" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T405" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for the Transient Guests: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the north wall between the entry and living-room leaf swings (three doors leave no other wall). Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -31693,10 +31749,14 @@
       </c>
       <c r="S440" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T440" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T440" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Nadia Quell: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the east wall opposite the entry door. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -33035,10 +33095,14 @@
       </c>
       <c r="S459" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T459" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T459" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Cal Dwyer: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the east wall between the entry and bath leaf swings. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -34327,10 +34391,14 @@
       </c>
       <c r="S477" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T477" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Iris Bell: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the west wall, clear of the entry leaf's quarter turn and the route line. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -35723,10 +35791,14 @@
       </c>
       <c r="S497" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T497" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T497" s="2" t="inlineStr">
+        <is>
+          <t>Kept as authored; captured at 1fadb5ad with its ceiling branch and register (implementation/ducts/images/F05_D_RESTRICTED_OV.jpg).</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -36837,10 +36909,14 @@
       </c>
       <c r="S512" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T512" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T512" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Sacha Reed: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the east wall opposite the entry door. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -38035,10 +38111,14 @@
       </c>
       <c r="S529" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T529" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T529" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Jonah Price: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the east wall between the entry and bath leaf swings. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -38927,10 +39007,14 @@
       </c>
       <c r="S541" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T541" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T541" s="2" t="inlineStr">
+        <is>
+          <t>Entry landing set for Mae Kessler: a hall stand (DomesticObject16: backboard with four iron hooks at 1.65 m, shelf at 1.1 m, plinth with a brass drip tray) on the west wall, clear of the entry leaf's quarter turn and the route line. Deviations: the coir mat and the per-resident hook load wait for a collision-free floor piece and the cloth family. Verified at b8319c79 and e6c97bc1: the twelve rebuilt families pass the fabrication batch with every stand bearing on its floor (implementation/slice8b, after the three D-plan stands were moved inside their vestibules), apartment batch 236 as before, upper lighting 0 failures, both door-route suites and the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12); the vestibule sweeps show the stands (implementation/slice8).</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -40159,10 +40243,14 @@
       </c>
       <c r="S559" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T559" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T559" s="2" t="inlineStr">
+        <is>
+          <t>Kept as authored: no slice touches it; captured empty at b8319c79 (implementation/slice8/images/F06_D_RESTRICTED_OV.jpg).</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -10729,10 +10729,14 @@
       </c>
       <c r="S154" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T154" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>1A_tea_tray (brass tray) with 1A_cup_good and 1A_cup_spare on the side table by the reading chair. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10803,10 +10807,14 @@
       </c>
       <c r="S155" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T155" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>1A_photo_frame (standing frame) on the marking table. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -11883,10 +11891,14 @@
       </c>
       <c r="S169" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T169" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>1A_register_open (sheets) on the study desk; the underlined name is lettering and stays off the texture by rule. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -12573,10 +12585,14 @@
       </c>
       <c r="S178" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T178" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>1D_flask (vacuum flask), 1D_plate and 1D_kettle on the dining table by the window pier; the cloth over the plate waits for the cloth family. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -12664,7 +12680,7 @@
       </c>
       <c r="T179" s="2" t="inlineStr">
         <is>
-          <t>thermos_and_leftovers: mug and rack on the drainboard; kettle, tin and plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+          <t>thermos_and_leftovers: mug and rack on the drainboard; kettle, tin and plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9b).</t>
         </is>
       </c>
     </row>
@@ -12823,10 +12839,14 @@
       </c>
       <c r="S181" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T181" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>1D_alarm_clock on the icebox top of F01_1D_FRIDGE_01 (nickel case, two bells, face turned to the room). Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -15803,10 +15823,14 @@
       </c>
       <c r="S221" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T221" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr">
+        <is>
+          <t>Two identical pencil jars (tins) on 2A_desk beside the existing papers, mug and headphones; erasers, tape reel and pad wait for their forms. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -17513,10 +17537,14 @@
       </c>
       <c r="S244" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T244" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr">
+        <is>
+          <t>Two folded cartons (parcels) and the coffee mug on the rig table; the percolator and the menus wait for their forms. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -17604,7 +17632,7 @@
       </c>
       <c r="T245" s="2" t="inlineStr">
         <is>
-          <t>takeout_plus_coffee: mug and rack on the drainboard; kettle, tin and a second mug on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+          <t>takeout_plus_coffee: mug and rack on the drainboard; kettle, tin and a second mug on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9b).</t>
         </is>
       </c>
     </row>
@@ -21991,10 +22019,14 @@
       </c>
       <c r="S305" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T305" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr">
+        <is>
+          <t>3B_alarm (alarm clock) on 3B_abed_ns; spectacles and torch wait for their forms. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -22393,10 +22425,14 @@
       </c>
       <c r="S310" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T310" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>3D_take_sheets (sheets) and 3D_hydration_tray (brass tray) with a glass (mug) on the edit desk 3D_table; the wireless table and radio came with BW-011. The desk lamp waits for the task-lamp family's floor and desk installations. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -25433,10 +25469,14 @@
       </c>
       <c r="S352" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T352" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>Three paper stacks (4A_staging_a/b, 4A_form_11b) beside the existing briefs on 4A_writing_table. The brass weights, date stamp, ink pad and ruler wait for their forms. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -25569,10 +25609,14 @@
       </c>
       <c r="S354" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T354" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>4A_form_11b (sheets) at the table's end, where the resident would leave it (slice 9). Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -26605,10 +26649,14 @@
       </c>
       <c r="S368" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T368" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>4B_slip_stack (sheets) on the hall stand's shelf; the key nail and the brass weight wait for a wall-mounted form. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -26819,10 +26867,14 @@
       </c>
       <c r="S371" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T371" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>4B_couch_mug and 4B_couch_slip on 4B_coffee; the blanket waits for the cloth family. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -27111,10 +27163,14 @@
       </c>
       <c r="S375" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T375" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>4B_trash: a galvanised can with a lid on the kitchen floor beside the prep cabinet (surface stock standing on the floor plane). The landlord's fan is a V1 BoxFanProp with no V2 slot yet. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -28177,10 +28233,14 @@
       </c>
       <c r="S390" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T390" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>Two placings (plates) and a folded napkin (sheets) on 4C_din_t; the sandwich, bike lamp, card and chalk-line decal wait for their forms. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -28536,7 +28596,7 @@
       </c>
       <c r="T395" s="2" t="inlineStr">
         <is>
-          <t>quick_food_vs_preserved: mug and rack on the drainboard; two tins and a bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7).</t>
+          <t>quick_food_vs_preserved: mug and rack on the drainboard; two tins and a bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9b).</t>
         </is>
       </c>
     </row>
@@ -29531,10 +29591,14 @@
       </c>
       <c r="S409" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T409" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="inlineStr">
+        <is>
+          <t>4D_cartons (parcel) and 4D_stubs (sheets) on 4D_table; the open case waits for the crate family's open variant. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -32091,10 +32155,14 @@
       </c>
       <c r="S445" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T445" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T445" s="2" t="inlineStr">
+        <is>
+          <t>5A_ledger (bound volumes) on 5A_din_t; the supplies tin by the opening waits for a floor stance clear of the route. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -33453,10 +33521,14 @@
       </c>
       <c r="S464" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T464" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T464" s="2" t="inlineStr">
+        <is>
+          <t>5B_solder_tin on 5B_din_t beside the headphones and lead; the cloth mat and chassis wait for their forms. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -38333,10 +38405,14 @@
       </c>
       <c r="S532" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T532" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T532" s="2" t="inlineStr">
+        <is>
+          <t>6B_watercolour (standing frame) at the far corner of 6B_din_t. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -39147,10 +39223,14 @@
       </c>
       <c r="S543" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T543" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T543" s="2" t="inlineStr">
+        <is>
+          <t>6C_glove_tray (brass tray) on the hall stand's shelf; the gloves and the buttonhook wait for the cloth family. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -39213,10 +39293,14 @@
       </c>
       <c r="S544" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T544" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T544" s="2" t="inlineStr">
+        <is>
+          <t>6C_card_a (a card stack beside the existing catalogues) and 6C_object_under_review (a string-tied parcel) on the catalogue table 6C_din_t; the second card and the gloves wait for a smaller card form and the cloth family. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -39345,10 +39429,14 @@
       </c>
       <c r="S546" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T546" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T546" s="2" t="inlineStr">
+        <is>
+          <t>6C_photo_a/b (standing frames) on 6C_cof; the five framed objects on the wall wait for the wall-art hook. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -39403,10 +39491,14 @@
       </c>
       <c r="S547" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T547" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T547" s="2" t="inlineStr">
+        <is>
+          <t>6C_tea_tray with 6C_tea_cup_a/b on 6C_cof. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -40037,10 +40129,14 @@
       </c>
       <c r="S556" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T556" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T556" s="2" t="inlineStr">
+        <is>
+          <t>6C_bed_frame and 6C_hairpin_tin on 6C_bed0_ns; the brooch waits for its form. Verified at dc849111 (slice9e, slice9f) and 266ef28a (slice9g): the thirteen families pass the fabrication batch (24,237 checks, 0 failures; surface stock 3,461 checks with every record bearing on its support, the fifteen prep cabinets with the 1D, 2C and 4C completion copies), apartment batch 236 as before, completion routes 1D 25, 2C 9 and 4C 9 unchanged (the C-plan bath leg), upper lighting 0 failures, upper kitchens 238 as before (the material-binding and three-stance failures are identical at 66994c91, slice9h), the household save owner's 201 controls save and restore (0 failures), the eight-space sweep 0 failures; the resident surfaces are shown in implementation/slice9 (at bc26e9ca) and the kitchens and the 6C vestibule in slice9e.</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -10327,10 +10327,14 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T149" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -10578,7 +10582,7 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>1A_reading_chair (ChairDark, angled 30 degrees to the window with its back to the kitchen door) and 1A_side_table (TableRect08) by the window; 1A_table and 1A_chair moved onto the long wall as the marking table. Deviations: the seating family has no armchair variant and the task-lamp family no floor stand, so the chair is the dark dining chair and the lamp is deferred with the family work. (implementation/slice6/images/F01_A_MAIN_OV.jpg)</t>
+          <t>1A_reading_chair (ChairDark, angled 30 degrees to the window with its back to the kitchen door) and 1A_side_table (TableRect08) by the window; 1A_table and 1A_chair moved onto the long wall as the marking table. Slice 10 replaced the dining chair with the Armchair form (template 5B_radio_chair) reseated at (-14.75, -5.4) facing the window, between the side table and the radiator stance; the floor lamp still waits for the task-lamp family. (implementation/slice6/images/F01_A_MAIN_OV.jpg)</t>
         </is>
       </c>
     </row>
@@ -12129,10 +12133,14 @@
       </c>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T172" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -14771,10 +14779,14 @@
       </c>
       <c r="S207" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T207" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -16127,10 +16139,14 @@
       </c>
       <c r="S225" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T225" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -17315,10 +17331,14 @@
       </c>
       <c r="S241" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T241" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -20037,10 +20057,14 @@
       </c>
       <c r="S278" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T278" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T278" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -21167,10 +21191,14 @@
       </c>
       <c r="S293" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T293" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -22347,10 +22375,14 @@
       </c>
       <c r="S309" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T309" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -25255,10 +25287,14 @@
       </c>
       <c r="S349" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T349" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -26587,10 +26623,14 @@
       </c>
       <c r="S367" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T367" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -28159,10 +28199,14 @@
       </c>
       <c r="S389" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T389" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T389" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -29389,10 +29433,14 @@
       </c>
       <c r="S406" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T406" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -31895,10 +31943,14 @@
       </c>
       <c r="S441" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T441" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T441" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -33245,10 +33297,14 @@
       </c>
       <c r="S460" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T460" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T460" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -33381,10 +33437,14 @@
       </c>
       <c r="S462" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T462" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr">
+        <is>
+          <t>5B_radio_chair: the new Armchair form (sofa recipe at 0.85 m, one cushion, rolled arms) at (-13.8, 5.55) on the window side of the wireless table, facing east along it. The worn-through arm and dished seat are finish work on the cloth and stay open. Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -34545,10 +34605,14 @@
       </c>
       <c r="S478" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T478" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T478" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -37063,10 +37127,14 @@
       </c>
       <c r="S513" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T513" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T513" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -38265,10 +38333,14 @@
       </c>
       <c r="S530" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T530" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T530" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -39165,10 +39237,14 @@
       </c>
       <c r="S542" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T542" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T542" s="2" t="inlineStr">
+        <is>
+          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -15087,10 +15087,14 @@
       </c>
       <c r="S211" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T211" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr">
+        <is>
+          <t>2A_plain_box: a blank card carton (carton form) on 2A_shelf1's middle board, flush with the front edge (the bearing rule refuses a 10 mm overhang; the two lower boards are full of the shelf's own bins and tins), blank face forward. The life profile's hero object conspicuously_unlabeled_box has no instantiating owner, so no INSPECT card is bound; the shelf row it should stand proud of arrives with F02_A_MAIN-001. Verified at ec25cca0 (slice11b; slice11 is the first run, red on the two placements fixed here): the thirteen families pass the fabrication batch (24,724 checks, 0 failures; tables 72, storage 50 and objects 36 actors with the copies, surface stock 3,708 checks with every record bearing on its support, the reel boxes on the clear boards), apartment batch 236 as before, upper lighting 0 failures, the household save owner's 201 controls unchanged (0 failures), the four-space sweep 0 failures; the rooms are shown in implementation/slice11b.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -21351,10 +21355,14 @@
       </c>
       <c r="S295" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T295" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="inlineStr">
+        <is>
+          <t>3B_outgoing_shelf (Shelf01 copy) against the south wall west of the private-hall opening, three wrapped parcels (3B_out_parcel_a/b/c) on its 0.97 m board. 3B_partscrate stays at its anchor as the intake crate (the dossier's move to the vestibule opening collides with the radio stance); paper tags wait for a tag form. Verified at ec25cca0 (slice11b; slice11 is the first run, red on the two placements fixed here): the thirteen families pass the fabrication batch (24,724 checks, 0 failures; tables 72, storage 50 and objects 36 actors with the copies, surface stock 3,708 checks with every record bearing on its support, the reel boxes on the clear boards), apartment batch 236 as before, upper lighting 0 failures, the household save owner's 201 controls unchanged (0 failures), the four-space sweep 0 failures; the rooms are shown in implementation/slice11b.</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -33523,10 +33531,14 @@
       </c>
       <c r="S463" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T463" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T463" s="2" t="inlineStr">
+        <is>
+          <t>5B_deck_table (TableRect05 copy, 1.6 x 0.5 m) along the private-hall opening at the third point of the listening triangle, with 5B_deck (a second DomesticObject04 reel deck bearing on its top) and, on the east wall beside the vestibule opening, two Shelf01 units (5B_tape_shelf_a/b) carrying five rows of fourteen standing reel boxes (boxrow form) and one plain box (reelbox form). Deviations: the deck is passive with no RESIST-REFUSE owner (nothing prompts; the reel is never audible), and the boxes carry seams instead of date tags (no lettering in textures). Verified at ec25cca0 (slice11b; slice11 is the first run, red on the two placements fixed here): the thirteen families pass the fabrication batch (24,724 checks, 0 failures; tables 72, storage 50 and objects 36 actors with the copies, surface stock 3,708 checks with every record bearing on its support, the reel boxes on the clear boards), apartment batch 236 as before, upper lighting 0 failures, the household save owner's 201 controls unchanged (0 failures), the four-space sweep 0 failures; the rooms are shown in implementation/slice11b.</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -38415,10 +38427,14 @@
       </c>
       <c r="S531" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T531" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T531" s="2" t="inlineStr">
+        <is>
+          <t>6B_din_t turned into the desk: moved square to the private-hall opening at (-10.25, 4.4) with 6B_din_dc1 behind it facing the opening and 6B_din_dc2 at its west side, the stances re-seated; 6B_wastebasket (wire basket with crushed paper, basket form) on the floor at the desk's right. Deviations: the task lamp waits for the task-lamp installations; the three draft boxes wait for a bookshelf support in the stock inspector. Verified at ec25cca0 (slice11b; slice11 is the first run, red on the two placements fixed here): the thirteen families pass the fabrication batch (24,724 checks, 0 failures; tables 72, storage 50 and objects 36 actors with the copies, surface stock 3,708 checks with every record bearing on its support, the reel boxes on the clear boards), apartment batch 236 as before, upper lighting 0 failures, the household save owner's 201 controls unchanged (0 failures), the four-space sweep 0 failures; the rooms are shown in implementation/slice11b.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -10659,10 +10659,14 @@
       </c>
       <c r="S153" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T153" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>1A_frame_a/b: the retirement certificate and the permission as two copies of 4A's document frame (completion copies), 0.6 m apart at 1.55 m on the long north wall, symmetrical about the room's centre. Deviation: the marking table is in the study, so the pair centres on the main room's pendant. Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -25587,10 +25591,14 @@
       </c>
       <c r="S353" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T353" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>4A_frame_a/b: two moulded frames (artframe form: dark moulding, linen mat, a document sheet with a brass seal disc and a pen stroke, no lettering) 0.5 m apart above the writing table at 1.5 m. The binder row waits for bookshelf contents (the BookshelfProp panel owns that shelf). Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -26779,10 +26787,14 @@
       </c>
       <c r="S369" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T369" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr">
+        <is>
+          <t>4B_case_wall: a 1.0 x 1.0 m pinboard (DomesticObject17, 24 cards in a grid, one brass pin each) on the vestibule partition beside the terminal desk, centred on the desk's length at 1.4 m. Deviations: the desk stands free of every wall, so the board hangs on the nearest partition behind the desk chair rather than over the desk; it is 1.0 m wide, not 1.4, to stay on the vestibule-owned face clear of the opening casing; strings between cards wait for a thread form. Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -32087,10 +32099,14 @@
       </c>
       <c r="S443" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T443" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T443" s="2" t="inlineStr">
+        <is>
+          <t>5A_plan_wall: a 1.6 x 1.0 m pinboard (DomesticObject18, 20 drifted sheets) on the north wall between the radiator and the bookshelf at 1.4 m. Deviations: the wall opposite the window is two openings and the switch, so the board takes the clear north wall; plan-line decals and red strokes wait for a sheet form (no lettering in textures). Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -34753,10 +34769,14 @@
       </c>
       <c r="S480" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T480" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T480" s="2" t="inlineStr">
+        <is>
+          <t>5C_canvas_a/b: two unframed 0.6 x 0.8 m canvases (artframe form: stretcher with a centre brace, wrapped linen with edge tacks, painted fields in different palettes) 0.3 m apart at 1.5 m on the east wall. Deviation: the wall opposite the window is two openings and the bookshelf, so the pair hangs on the clear east wall north of the radiator. Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16385,10 +16385,14 @@
       </c>
       <c r="S228" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T228" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr">
+        <is>
+          <t>2B_repair_rail (garmentrail form: header board, brackets, rail) on the west wall's segment south of the vestibule opening, rail at 1.7 m, five garments on wooden hangers with paper repair tags: burgundy wool, Cam's maroon jersey, a navy cape, a grey coat and a linen shirt. Deviations: the opening's neighbour wall is the only clear 1 m run (the dossier's spot beside the private-hall opening holds the radio table); the scarlet lining and celluloid collar are colour details the garment form does not carry; the mended armchair waits for the sewing machine, whose placement fixes where it faces (every corner of the room holds a stance or the hall route). Verified at 7c765151 (slice13): the thirteen families pass the fabrication batch (25,479 checks, 0 failures; objects 50 actors, every rail and blanket on its actual wall face, the two closet-shelf items bearing on the clear boards), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before (the kitchen leg), the household save owner 0 failures, the four-space sweep 0 failures; the rooms and native close-ups are in implementation/slice13.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -18453,10 +18457,14 @@
       </c>
       <c r="S256" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T256" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
+          <t>2C_blanket_a/b: two 1.2 x 2.0 m moving blankets (blanket form: batten, bound edges, quilted rows) on the east wall. Deviations: the window and the door wall keep their light and swing; the mic stands, amp, guitar and pedalboard wait for their families. Verified at 7c765151 (slice13): the thirteen families pass the fabrication batch (25,479 checks, 0 failures; objects 50 actors, every rail and blanket on its actual wall face, the two closet-shelf items bearing on the clear boards), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before (the kitchen leg), the household save owner 0 failures, the four-space sweep 0 failures; the rooms and native close-ups are in implementation/slice13.</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -23423,10 +23431,14 @@
       </c>
       <c r="S323" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T323" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>3D_blanket_a/b: two blankets (completion copies of 2C's) on the study's solid east wall. The music stand, mic case, deck and headphones wait for their families (no blanket over the window, so the study keeps its daylight). Verified at 7c765151 (slice13): the thirteen families pass the fabrication batch (25,479 checks, 0 failures; objects 50 actors, every rail and blanket on its actual wall face, the two closet-shelf items bearing on the clear boards), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before (the kitchen leg), the household save owner 0 failures, the four-space sweep 0 failures; the rooms and native close-ups are in implementation/slice13.</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -27799,10 +27811,14 @@
       </c>
       <c r="S383" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T383" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>4B_closet_rail (garmentrail form, four garments, no tags) across the closet's north wall at 1.7 m, clear of the shelf and the door; on 4B_equipment_shelf a capsule tin and a bulb carton on the clear boards. The fuse box and flex coil wait for their forms. Verified at 7c765151 (slice13): the thirteen families pass the fabrication batch (25,479 checks, 0 failures; objects 50 actors, every rail and blanket on its actual wall face, the two closet-shelf items bearing on the clear boards), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before (the kitchen leg), the household save owner 0 failures, the four-space sweep 0 failures; the rooms and native close-ups are in implementation/slice13.</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11353,10 +11353,14 @@
       </c>
       <c r="S162" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T162" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the east wall at (-5.67, -9.28), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route; a completion copy. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -13143,10 +13147,14 @@
       </c>
       <c r="S185" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T185" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the west wall at (13.07, -4.58), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route; a completion copy. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -15613,10 +15621,14 @@
       </c>
       <c r="S218" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T218" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the north wall at (-9.32, 7.58), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -16821,10 +16833,14 @@
       </c>
       <c r="S234" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T234" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the west wall at (13.07, -4.58), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -17951,10 +17967,14 @@
       </c>
       <c r="S249" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T249" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the south wall at (6.67, 6.62), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route; a completion copy. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -20817,10 +20837,14 @@
       </c>
       <c r="S288" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T288" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the north wall at (-9.32, 7.58), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -21931,10 +21955,14 @@
       </c>
       <c r="S303" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T303" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr">
+        <is>
+          <t>A parts crate (a copy of 3B_partscrate) against the east wall at (15.38, -9.43), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -23061,10 +23089,14 @@
       </c>
       <c r="S318" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T318" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the east wall at (-5.87, -9.28), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route; a completion copy. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -26113,10 +26145,14 @@
       </c>
       <c r="S360" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T360" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the east wall at (15.38, -8.98), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -27383,10 +27419,14 @@
       </c>
       <c r="S377" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T377" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the west wall at (-10.83, 5.97), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -28959,10 +28999,14 @@
       </c>
       <c r="S399" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T399" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the south wall at (6.67, 6.62), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route; a completion copy. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -30243,10 +30287,14 @@
       </c>
       <c r="S417" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T417" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T417" s="2" t="inlineStr">
+        <is>
+          <t>A parts crate (a copy of 3B_partscrate) against the east wall at (-5.87, -9.28), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route; a completion copy. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -32753,10 +32801,14 @@
       </c>
       <c r="S452" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T452" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T452" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the east wall at (-5.87, -8.48), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -34193,10 +34245,14 @@
       </c>
       <c r="S472" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T472" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T472" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the north wall at (-10.83, 11.38), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -35345,10 +35401,14 @@
       </c>
       <c r="S488" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T488" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T488" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the south wall at (6.67, 6.62), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -37751,10 +37811,14 @@
       </c>
       <c r="S521" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T521" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T521" s="2" t="inlineStr">
+        <is>
+          <t>A gear crate (a copy of 6A_gearcrate) against the east wall at (-5.87, -8.48), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -38891,10 +38955,14 @@
       </c>
       <c r="S537" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T537" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T537" s="2" t="inlineStr">
+        <is>
+          <t>A lidded wicker laundry hamper (hamper form) with a linen corner caught under the lid against the north wall at (-10.83, 11.38), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -39985,10 +40053,14 @@
       </c>
       <c r="S552" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T552" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T552" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised boot tray with a pair of rubber galoshes and dried mud (boottray form) against the south wall at (6.67, 6.62), clear of every door and opening approach (each opening's span plus 0.15 m, 1.0 m deep), the stances and a 0.85 m route. The hamper's cane panels read as a lidded box rather than a woven basket and the galoshes are plain blocks; finer weave and boot forms are later art. Verified at 2152694f (slice14b) and 4fc1b18d (slice14c, after 2A's and 3A's objects moved to the north end wall out of the door route): the thirteen families pass the fabrication batch (25,826 checks, 0 failures; every hall object bearing inside its hall), apartment batch 236 as before, the apartment door route 45 waypoints and the 4B route 32 with 0 failures, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting 0 failures, upper furniture 444 identical to slice 13 (slice14base), the eighteen-hall sweep 0 failures; captures in implementation/slice14b and slice14c.</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -15025,10 +15025,14 @@
       </c>
       <c r="S210" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T210" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr">
+        <is>
+          <t>2A_caption_wall: a 1.2 x 0.9 m pinboard (24 cards in rows) on the west wall between the two windows. Deviations: it hangs above 2A_shelf1 (bottom 1.62 m, centre 2.07 m) because the shelf stands 1.6 m tall on that wall; the red threads and the one deliberately blank card wait for a thread form and a card-level distinction. Verified at 260cffe6 (slice15): the thirteen families pass the fabrication batch (26,116 checks, 0 failures; objects 78 actors, every frame, canvas and board bearing on its actual wall face), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; captures in implementation/slice15.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -17523,10 +17527,14 @@
       </c>
       <c r="S243" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T243" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr">
+        <is>
+          <t>2C_album_a/b: two photographs (artframe form, photo style: moulding, linen mat, a toned print) 0.5 m apart at 1.5 m on the window wall west of the window, nothing between them. Verified at 260cffe6 (slice15): the thirteen families pass the fabrication batch (26,116 checks, 0 failures; objects 78 actors, every frame, canvas and board bearing on its actual wall face), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; captures in implementation/slice15.</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -20323,10 +20331,14 @@
       </c>
       <c r="S281" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T281" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="inlineStr">
+        <is>
+          <t>3A_diagram (a copy of 4A's document frame standing for the propagation diagram) and 3A_portrait (photo style, the sepia plate) 0.4 m apart at 1.5 m on the north wall between the kitchen opening and the private-hall door, clear of the plants. The diagram's line drawing is a blank sheet (no lettering or line decals in textures). Verified at 260cffe6 (slice15): the thirteen families pass the fabrication batch (26,116 checks, 0 failures; objects 78 actors, every frame, canvas and board bearing on its actual wall face), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; captures in implementation/slice15.</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -22645,10 +22657,14 @@
       </c>
       <c r="S312" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T312" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>3D_image_a/b/c: three photographs (completion copies of 2C's) at 1.5 m on the long north wall, 2.3 m apart, the middle one over the chaise. Verified at 260cffe6 (slice15): the thirteen families pass the fabrication batch (26,116 checks, 0 failures; objects 78 actors, every frame, canvas and board bearing on its actual wall face), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; captures in implementation/slice15.</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -33743,10 +33759,14 @@
       </c>
       <c r="S465" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T465" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T465" s="2" t="inlineStr">
+        <is>
+          <t>5B_work_a/b: two canvases (copies of 5C's diptych forms) 1.0 m apart at 1.5 m on the window wall south of the window, off the window's centre line. Verified at 260cffe6 (slice15): the thirteen families pass the fabrication batch (26,116 checks, 0 failures; objects 78 actors, every frame, canvas and board bearing on its actual wall face), apartment batch 236 as before, upper lighting 0 failures, completion route 3D 16 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; captures in implementation/slice15.</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11739,10 +11739,14 @@
       </c>
       <c r="S167" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T167" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>On 1A_bedside: folded spectacles (spectacles form) in the back strip and the red pencil (pencil form) along the front edge, beside the nightstand's own glass. The dosing spoon waits for a spoon form. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -21075,10 +21079,14 @@
       </c>
       <c r="S291" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T291" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="inlineStr">
+        <is>
+          <t>3A_seed_catalogue (booklet form) on 3A_bed0_ns's front strip. The seedling tray on the north sill waits for a sill support in the stock inspector. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -26535,10 +26543,14 @@
       </c>
       <c r="S365" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T365" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="inlineStr">
+        <is>
+          <t>4A_pocketbook: an overfilled wallet with a folded note's corner showing (wallet form) on 4A_bed0_ns. The brown sack suit waits for wardrobe garment sets. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -29361,10 +29373,14 @@
       </c>
       <c r="S404" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T404" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>4C_gloves (a pair, gloves form) and 4C_condition_card (booklet form) on 4C_bed1_ns. The slippers under the bed wait for a slipper form. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -33101,10 +33117,14 @@
       </c>
       <c r="S456" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T456" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T456" s="2" t="inlineStr">
+        <is>
+          <t>5A_fold_rule (folding rule form, four leaves and brass rivets) and 5A_notebook (booklet form) on 5A_bed0_ns. The reading lamp waits for the task-lamp installations. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -34923,10 +34943,14 @@
       </c>
       <c r="S481" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T481" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T481" s="2" t="inlineStr">
+        <is>
+          <t>5C_hammer (hammer form) and a tin of tacks on 5C_din_t, beside the solvents and studies. The half-stretched canvas and the stretcher stack wait for a canvas-in-progress form. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -38111,10 +38135,14 @@
       </c>
       <c r="S525" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T525" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T525" s="2" t="inlineStr">
+        <is>
+          <t>6A_empty_case: an open leather case with its lining showing (case form) on 6A_bed0_ns. The strap on the bedpost waits for a cloth strap form. Verified at 82e2fbb9 (slice16) and 42a4a0db (slice16c, the same runtime tree with the surface-stock close-ups made selectable): the thirteen families pass the fabrication batch (26,426 checks, 0 failures; 175 stock assemblies, every new piece bearing on its nightstand or table top clear of the baked book and glass), apartment batch 236 as before, completion routes 1A 15 and 4C 9 as before, upper lighting and the household save owner 0 failures, the seven-space sweep 0 failures; close-ups in implementation/slice16c (1A's nightstand has no clear camera station, so its spectacles and pencil rest on the bearing check alone).</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16237,10 +16237,14 @@
       </c>
       <c r="S226" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T226" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr">
+        <is>
+          <t>2B_client_chair (a ChairOak copy) in the vestibule corner north of the opening, facing into the vestibule, clear of the entry-leaf sweep and the route to the main room (the first placement, south of the opening, stood in the door route: slice17); 2B_finished_parcel (parcel form) on its seat. Verified at 7eeaa0ef (slice17b): the thirteen families pass the fabrication batch (26,568 checks, 0 failures; tables 73, seating 52, objects 79, stock 178, the parcel bearing on the chair seat and the pail on the floor), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, completion route 4D 12 waypoints as before, upper lighting and the household save owner 0 failures, the four-space sweep 0 failures; captures in implementation/slice17b.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -17043,10 +17047,14 @@
       </c>
       <c r="S237" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T237" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
+          <t>2B_bedside (a Nightstand01 copy) at the head of the bed on the door side, with 2B_photo (standing frame form) in the clear back strip beside the nightstand's own book and glass. The mirror waits for the mirror family's wall variant. Verified at 7eeaa0ef (slice17b): the thirteen families pass the fabrication batch (26,568 checks, 0 failures; tables 73, seating 52, objects 79, stock 178, the parcel bearing on the chair seat and the pail on the floor), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, completion route 4D 12 waypoints as before, upper lighting and the household save owner 0 failures, the four-space sweep 0 failures; captures in implementation/slice17b.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -20779,10 +20787,14 @@
       </c>
       <c r="S287" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T287" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="inlineStr">
+        <is>
+          <t>3A_compost_pail (the galvanised can form) on the floor at the east end of the sink support, clear of the tap and stove stances. Deviation: beside the sink support rather than under it (the frame's underside is not a clear bearing), galvanised rather than enamel. Verified at 7eeaa0ef (slice17b): the thirteen families pass the fabrication batch (26,568 checks, 0 failures; tables 73, seating 52, objects 79, stock 178, the parcel bearing on the chair seat and the pail on the floor), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, completion route 4D 12 waypoints as before, upper lighting and the household save owner 0 failures, the four-space sweep 0 failures; captures in implementation/slice17b.</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -29611,10 +29623,14 @@
       </c>
       <c r="S407" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T407" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T407" s="2" t="inlineStr">
+        <is>
+          <t>4D_case (new suitcase form: a leather case on its long edge with two straps, brass feet and a handle) in the vestibule's north-west corner, clear of the three doors' approaches. The gladstone and the rules card on the door back wait for their forms. Verified at 7eeaa0ef (slice17b): the thirteen families pass the fabrication batch (26,568 checks, 0 failures; tables 73, seating 52, objects 79, stock 178, the parcel bearing on the chair seat and the pail on the floor), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, completion route 4D 12 waypoints as before, upper lighting and the household save owner 0 failures, the four-space sweep 0 failures; captures in implementation/slice17b.</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16331,10 +16331,14 @@
       </c>
       <c r="S227" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T227" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>2B_sewing_machine (new sewingmachine form: cast-iron legs, rails and treadle on an axle, an oak top and drawer, a black japanned head with its needle, needle plate and handwheel) under the east window with the treadle toward the room. Deviation: passive; the treadle OPERATE owner (treadle turns, needle drops) waits for a mechanism pass. Verified at d0108d15 (slice18): the thirteen families pass the fabrication batch (26,770 checks, 0 failures; objects 83 actors, every new piece standing on its floor inside its room and clear of its neighbours), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, upper lighting and the household save owner 0 failures, the three-space sweep 0 failures; native close-ups in implementation/slice18.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -21353,10 +21357,14 @@
       </c>
       <c r="S294" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T294" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>3B_teardown (new teardown form: a newspaper sheet, an open chassis with three empty valve sockets, three loose valves standing on the sheet, a saucer of screws) on the floor north of the parts crate, beside the hall opening's approach. Passive, never a live receiver; the INSPECT card waits for the matrix pass. Verified at d0108d15 (slice18): the thirteen families pass the fabrication batch (26,770 checks, 0 failures; objects 83 actors, every new piece standing on its floor inside its room and clear of its neighbours), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, upper lighting and the household save owner 0 failures, the three-space sweep 0 failures; native close-ups in implementation/slice18.</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -36041,10 +36049,14 @@
       </c>
       <c r="S496" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T496" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T496" s="2" t="inlineStr">
+        <is>
+          <t>5C_easel (new easel form: splayed front legs and a back leg on foot pads, a ledge holding a blank canvas under the top clamp) by the window east of the stool, the canvas facing the stool so the window is on the painter's left; 5C_failed_canvases (new canvasstack form: six canvases standing face to the wall, stretcher backs to the room, a pencil mark on each) west of the door, outside its swing. The pigment table and stool were already placed; the drying rack, wash jar and drop cloth wait for their forms. Verified at d0108d15 (slice18): the thirteen families pass the fabrication batch (26,770 checks, 0 failures; objects 83 actors, every new piece standing on its floor inside its room and clear of its neighbours), apartment batch 236 as before, the apartment door route 45 and the 4B route 32 waypoints with 0 failures, upper lighting and the household save owner 0 failures, the three-space sweep 0 failures; native close-ups in implementation/slice18.</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -20207,10 +20207,14 @@
       </c>
       <c r="S279" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T279" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T279" s="2" t="inlineStr">
+        <is>
+          <t>3A_prop_shelf_s/_n: two low oak shelves (Shelf09 1.5 m and Shelf10 1.2 m, two boards, 0.72 m, so they stand under the 0.75 m sills) under the two west windows either side of the potting bench, each with two rows of lidded glass seed jars (seedjars form); the north row lacks one jar at its end (seedjarsgap form). Deviations: two shelves rather than one 2.4 m span because the potting bench stands between the windows; jars hold no soil or seedlings yet (no soil or plant key in the stock family). Verified at 7813b06c (slice19): the thirteen families pass the fabrication batch (27,146 checks, 0 failures; storage 52, objects 84, stock 187, every jar, cover and fold bearing on its board), apartment batch 236 as before, completion route 4C 9 waypoints as before, upper lighting and the household save owner 0 failures, the three-space sweep 0 failures; close-ups in implementation/slice19.</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -28484,7 +28488,7 @@
       </c>
       <c r="T391" s="2" t="inlineStr">
         <is>
-          <t>4C_museum_shelf (Shelf01) on the window wall beside the window; the covered objects, cloth and the courier corner's floor stock stay with the desktop_stock items. (implementation/slice6/images/F04_C_MAIN_OV.jpg)</t>
+          <t>4C_museum_shelf (Shelf01) on the window wall beside the window; the courier corner's floor stock stays with the desktop_stock items. (implementation/slice6/images/F04_C_MAIN_OV.jpg) Slice 19 adds Noel's museum bay on it: three cloth-covered objects and a folded cloth (covered and foldedcloth forms), verified at 7813b06c (implementation/slice19/images/4C_covered_a_stock.jpg).</t>
         </is>
       </c>
     </row>
@@ -40561,10 +40565,14 @@
       </c>
       <c r="S558" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T558" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T558" s="2" t="inlineStr">
+        <is>
+          <t>Three cloth-covered objects (covered form: an object under a linen drape) on the existing 6C_archive_shelf_01/02 boards, and 6C_card_cabinet (new cardcabinet form: twelve drawers with brass pulls and blank label frames, one drawer with a brass lock plate for the provenance drawer) against the south wall west of the door. Deviations: the cabinet stands by the door because the archive table holds the window; the locked drawer is passive (its RESIST-REFUSE owner waits for the matrix pass). Verified at 7813b06c (slice19): the thirteen families pass the fabrication batch (27,146 checks, 0 failures; storage 52, objects 84, stock 187, every jar, cover and fold bearing on its board), apartment batch 236 as before, completion route 4C 9 waypoints as before, upper lighting and the household save owner 0 failures, the three-space sweep 0 failures; close-ups in implementation/slice19.</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -14947,10 +14947,14 @@
       </c>
       <c r="S209" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T209" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
+          <t>Rows of seven labelled box files (fileboxes form: cloth-covered boxes in navy, green, burgundy and brown, a blank paper label and a brass pull on each) on the clear upper boards of 2A_shelf0, 2A_shelf1 and 2A_shelf2, labels facing the room, so the three units read as matching labelled storage. Deviations: the units keep their oak frames (the BW-003 posts already replaced the wire) and their own bins and tins on the lower boards; the labels are blank (no lettering in textures). Verified at ccdf39bf (slice20): the thirteen families pass the fabrication batch (27,601 checks, 0 failures; objects 86, stock 192, the rail and print line on their actual wall faces, the box files on the clear boards), apartment batch 236 as before, upper lighting and the household save owner 0 failures, the two-space sweep 0 failures; close-ups in implementation/slice20.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -37397,10 +37401,14 @@
       </c>
       <c r="S514" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T514" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T514" s="2" t="inlineStr">
+        <is>
+          <t>6A_backdrop_rail (new backdroprail form: header strip on rear battens, two brackets, a rail and a paper roll with its sheet hanging almost to the floor) on the west wall south of the window, the rail at 2.2 m, clear of the tripod, softboxes and crate. The charging bench and the folding chair wait for a work-table copy and a folding-chair seating variant. Verified at ccdf39bf (slice20): the thirteen families pass the fabrication batch (27,601 checks, 0 failures; objects 86, stock 192, the rail and print line on their actual wall faces, the box files on the clear boards), apartment batch 236 as before, upper lighting and the household save owner 0 failures, the two-space sweep 0 failures; close-ups in implementation/slice20.</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -37463,10 +37471,14 @@
       </c>
       <c r="S515" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T515" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T515" s="2" t="inlineStr">
+        <is>
+          <t>6A_print_line (new printline form: two hook plates, a string at 1.9 m and six pegged contact sheets, each a grid of small dark frames, no lettering) on the south wall east of the bed door. The hero contact sheet above a bench waits for the charging bench. Verified at ccdf39bf (slice20): the thirteen families pass the fabrication batch (27,601 checks, 0 failures; objects 86, stock 192, the rail and print line on their actual wall faces, the box files on the clear boards), apartment batch 236 as before, upper lighting and the household save owner 0 failures, the two-space sweep 0 failures; close-ups in implementation/slice20.</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -8609,10 +8609,14 @@
       </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T124" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>F01_lobby_board: a 1.2 x 0.9 m noticeboard (pinboard form, 23 notices in rows, one brass pin each, no lettering) on the south wall between the west window and the inner door, its lower edge above the dado cap at 1.42 m. Deviation: the notices are blank cards in rows (the drifted layout collapses into streaks), and the board is a passive pinboard rather than the 23-piece authored LobbyBulletinBoard owner. Verified at 9120c99a (slice21: reading furniture 25 and public furnishings 29 waypoints with 0 failures and the blockout suite passing, as at 858fb707 in slice21base; apartment batch 236 as before) and at 85f7dfc0 (slice21c, after the board moved above the dado and the boards took the card grid): the thirteen families pass the fabrication batch (27,682 checks, 0 failures; every board and frame on its actual wall face), public furnishings 29 waypoints with 0 failures, apartment batch 236, the lobby sweep 0 failures; captures in implementation/slice21, slice21b and slice21c.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8683,10 +8687,14 @@
       </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T125" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>F01_lobby_photo: the 1928 photograph (a copy of the photograph frame) at 1.5 m beside the inner door. The sealed Vantry reference clock over the core opening waits for a V2 clock owner (ClockProp is mounted only by the V1 building). Verified at 9120c99a (slice21: reading furniture 25 and public furnishings 29 waypoints with 0 failures and the blockout suite passing, as at 858fb707 in slice21base; apartment batch 236 as before) and at 85f7dfc0 (slice21c, after the board moved above the dado and the boards took the card grid): the thirteen families pass the fabrication batch (27,682 checks, 0 failures; every board and frame on its actual wall face), public furnishings 29 waypoints with 0 failures, apartment batch 236, the lobby sweep 0 failures; captures in implementation/slice21, slice21b and slice21c.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -9335,10 +9343,14 @@
       </c>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T135" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>F01_common_armchair (an Armchair copy) in the common room's south-west window corner, facing into the room, clear of the reading table, its chairs and the bookcases. The minutes, jug and glasses wait for the reading table to become a stock support; the floor lamp waits for the task-lamp installations. Verified at 9120c99a (slice21: reading furniture 25 and public furnishings 29 waypoints with 0 failures and the blockout suite passing, as at 858fb707 in slice21base; apartment batch 236 as before) and at 85f7dfc0 (slice21c, after the board moved above the dado and the boards took the card grid): the thirteen families pass the fabrication batch (27,682 checks, 0 failures; every board and frame on its actual wall face), public furnishings 29 waypoints with 0 failures, apartment batch 236, the lobby sweep 0 failures; captures in implementation/slice21, slice21b and slice21c.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -32232,7 +32244,7 @@
       </c>
       <c r="T443" s="2" t="inlineStr">
         <is>
-          <t>5A_plan_wall: a 1.6 x 1.0 m pinboard (DomesticObject18, 20 drifted sheets) on the north wall between the radiator and the bookshelf at 1.4 m. Deviations: the wall opposite the window is two openings and the switch, so the board takes the clear north wall; plan-line decals and red strokes wait for a sheet form (no lettering in textures). Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
+          <t>5A_plan_wall: a 1.6 x 1.0 m pinboard (DomesticObject18, 20 sheets; in rows since slice 21, the drifted layout collapsing into streaks) on the north wall between the radiator and the bookshelf at 1.4 m. Deviations: the wall opposite the window is two openings and the switch, so the board takes the clear north wall; plan-line decals and red strokes wait for a sheet form (no lettering in textures). Verified at 76d0a584 (slice12) with the apartment batch at 394a9c3c (slice12b): the thirteen families pass the fabrication batch (25,164 checks, 0 failures; objects 44 actors, every board, canvas and frame bearing on its actual wall face), apartment batch 236 with failure labels identical to slice 11 once its category roster holds the original V1 set, upper lighting 0 failures, completion route 1A 15 waypoints as before, the household save owner 0 failures, the five-space sweep 0 failures; the rooms and native close-ups are in implementation/slice12.</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -12789,10 +12789,14 @@
       </c>
       <c r="S180" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T180" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>1D_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -15497,10 +15501,14 @@
       </c>
       <c r="S216" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T216" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr">
+        <is>
+          <t>2A_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -16733,10 +16741,14 @@
       </c>
       <c r="S232" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T232" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
+          <t>2B_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -17797,10 +17809,14 @@
       </c>
       <c r="S246" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T246" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="inlineStr">
+        <is>
+          <t>2C_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -21809,10 +21825,14 @@
       </c>
       <c r="S300" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T300" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="inlineStr">
+        <is>
+          <t>3B_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -22943,10 +22963,14 @@
       </c>
       <c r="S315" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T315" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T315" s="2" t="inlineStr">
+        <is>
+          <t>3D_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -26069,10 +26093,14 @@
       </c>
       <c r="S358" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T358" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>4A_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -27273,10 +27301,14 @@
       </c>
       <c r="S374" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T374" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>4B_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -28861,10 +28893,14 @@
       </c>
       <c r="S396" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T396" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T396" s="2" t="inlineStr">
+        <is>
+          <t>4C_drip_tray: a dry, dusty zinc drip pan (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -28923,10 +28959,14 @@
       </c>
       <c r="S397" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T397" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>The dry tray: 4C_drip_tray is dry and dusty (driptraydry form) under the icebox. The copper kettle on the range waits for the stove as a stock support. Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -30091,10 +30131,14 @@
       </c>
       <c r="S413" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T413" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T413" s="2" t="inlineStr">
+        <is>
+          <t>4D_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -32733,10 +32777,14 @@
       </c>
       <c r="S450" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T450" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T450" s="2" t="inlineStr">
+        <is>
+          <t>5A_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -35283,10 +35331,14 @@
       </c>
       <c r="S485" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T485" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T485" s="2" t="inlineStr">
+        <is>
+          <t>5C_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -37418,7 +37470,7 @@
       </c>
       <c r="T514" s="2" t="inlineStr">
         <is>
-          <t>6A_backdrop_rail (new backdroprail form: header strip on rear battens, two brackets, a rail and a paper roll with its sheet hanging almost to the floor) on the west wall south of the window, the rail at 2.2 m, clear of the tripod, softboxes and crate. The charging bench and the folding chair wait for a work-table copy and a folding-chair seating variant. Verified at ccdf39bf (slice20): the thirteen families pass the fabrication batch (27,601 checks, 0 failures; objects 86, stock 192, the rail and print line on their actual wall faces, the box files on the clear boards), apartment batch 236 as before, upper lighting and the household save owner 0 failures, the two-space sweep 0 failures; close-ups in implementation/slice20.</t>
+          <t>6A_backdrop_rail (new backdroprail form: header strip on rear battens, two brackets, a rail and a paper roll with its sheet hanging almost to the floor) on the west wall south of the window, the rail at 2.2 m, clear of the tripod, softboxes and crate (narrowed to 1.2 m in slice 22, implementation/slice22b, after the upper-kitchen suite found the paper inside the tripod stance's capsule). The charging bench and the folding chair wait for a work-table copy and a folding-chair seating variant. Verified at ccdf39bf (slice20): the thirteen families pass the fabrication batch (27,601 checks, 0 failures; objects 86, stock 192, the rail and print line on their actual wall faces, the box files on the clear boards), apartment batch 236 as before, upper lighting and the household save owner 0 failures, the two-space sweep 0 failures; close-ups in implementation/slice20.</t>
         </is>
       </c>
     </row>
@@ -37775,10 +37827,14 @@
       </c>
       <c r="S519" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T519" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T519" s="2" t="inlineStr">
+        <is>
+          <t>6A_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -38927,10 +38983,14 @@
       </c>
       <c r="S535" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T535" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T535" s="2" t="inlineStr">
+        <is>
+          <t>6B_drip_tray: a zinc drip pan holding a skin of water (driptray form) on the floor under the icebox, between its feet with the front lip showing, clear of the door stance and the door's swing. The ice card in the window pane waits for a window-pane support (the panes belong to the shell, not a furniture actor). Verified at 4444e1e1 (slice22) and db14e977 (slice22b, the 6A backdrop narrowed): the thirteen families pass the fabrication batch (28,045 checks, 0 failures; 206 stock assemblies, every pan bearing on the floor between its icebox's feet), apartment batch 236 as before, the six completion routes unchanged (1A 15, 1D 25, 2C 9, 3D 16, 4C 9, 4D 12), upper lighting and the household save owner 0 failures, upper kitchens 238 with the baseline's labels, the fourteen-kitchen sweep 0 failures; close-ups in implementation/slice22.</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -625,10 +625,14 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Five wicker baskets (hamper copies) along the north wall either side of the wet-stack pier, clear of the washers and the wringer swing (one first stood inside the pier: slice23c moved it). The chalked floor numbers, the folding table and Mina's uniform stack wait for a decal pass, a work-table copy and a folded-uniform form. Verified at 8f72926b (slice23: basement route 88 and ground 11 waypoints, laundry input 17, laundry apparatus, fittings, receiving and trade 0 failures, identical at 09e583ee in slice23base; Mina's laundry routine passing on both under the long runner in slice23mina and slice23mina_base; apartment batch 236; fabrication 28,403 checks with 0 failures in slice23b) and at 1cddce25 (slice23c, the basket moved: fabrication, laundry route, apparatus and fittings 0 failures, the laundry sweep 0 failures); captures in implementation/slice23 and slice23c.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1941,10 +1945,14 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>One household object against the back of sixteen bays, keyed to the bay labels: suitcases for 1A, 3D, 4A, 5A and 6B; boot trays for 1D and 3A; hampers for 2A, 4C and 6C; parts crates for 2B, 3B, 4B and 5B; 6A's gear crate; 5C's failed canvases face to the wall. 2C's and 4D's bays stay empty (padlocked). Each stands clear of the folded gate and the aisle. Deviations: one object per bay rather than a set; no padlock form yet. Verified at 8f72926b (slice23: basement route 88 and ground 11 waypoints, laundry input 17, laundry apparatus, fittings, receiving and trade 0 failures, identical at 09e583ee in slice23base; Mina's laundry routine passing on both under the long runner in slice23mina and slice23mina_base; apartment batch 236; fabrication 28,403 checks with 0 failures in slice23b) and at 1cddce25 (slice23c, the basket moved: fabrication, laundry route, apparatus and fittings 0 failures, the laundry sweep 0 failures); captures in implementation/slice23 and slice23c.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -14885,10 +14885,14 @@
       </c>
       <c r="S208" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T208" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>2A_out_tray: a dark wooden out-tray holding a stack of filed receipts (outtray form) square on the hall stand's shelf. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -23633,10 +23637,14 @@
       </c>
       <c r="S324" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T324" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>3D_card_index: a completion copy of 6C's card-index cabinet in the study's south-west corner, clear of the storage door's sweep, the window and the blankets. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -28025,10 +28033,14 @@
       </c>
       <c r="S384" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T384" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>4B_old_cap: the previous tenant's service cap (cap form: navy crown, bakelite peak and band) on the closet shelf's upper board beside the bulb carton. Deviation: the upper board, not the top, which carries the frame's rail caps. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -32217,10 +32229,14 @@
       </c>
       <c r="S442" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T442" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T442" s="2" t="inlineStr">
+        <is>
+          <t>5A_torch (torch form: nickel barrel, head and lens, a bakelite switch) on the hall stand's shelf (held by the bearing check; the vestibule gives the close-up camera no clear station). The chalk swing-limit arc waits for a floor decal pass. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -33587,10 +33603,14 @@
       </c>
       <c r="S461" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T461" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T461" s="2" t="inlineStr">
+        <is>
+          <t>5B_battery_case (batterycase form: a wooden case with two glass cells and brass terminals) on the floor west of the switch, where the signal-outlet plate sits, clear of the switch stance and the main opening. The cloth lead to the plate waits for a lead form. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -17518,7 +17518,7 @@
       </c>
       <c r="T242" s="2" t="inlineStr">
         <is>
-          <t>2C_rig_table (TableRect05) on the window wall facing the vestibule opening with 2C_din_dc2 as the operator's chair; 2C_din_t and 2C_din_dc1 moved against the kitchen-side wall as the late-meal surface, stances moved with them. The mixer (signal family), reel deck, headphones and the hook strip stay open. (implementation/slice6/images/F02_C_MAIN_OV.jpg)</t>
+          <t>2C_rig_table (TableRect05) on the window wall facing the vestibule opening with 2C_din_dc2 as the operator's chair; 2C_din_t and 2C_din_dc1 moved against the kitchen-side wall as the late-meal surface, stances moved with them. (implementation/slice6/images/F02_C_MAIN_OV.jpg) Slice 25 adds 2C_deck (a reel deck copy) on the rig table between the cartons and the mug, and 2C_cable_hooks (new hookstrip form: a batten with five hooks and taped cable loops) on the window wall beside the rig at 1.5 m (implementation/slice25). The mixer and headphones wait for the signal family.</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29794,7 @@
       </c>
       <c r="T408" s="2" t="inlineStr">
         <is>
-          <t>4D_settee (Sofa195) on the long wall (the window wall carries the radiator), 4D_lamp_table (TableRect08) beside it, 4D_chair2 (ChairDark) at the dining table; the wireless table and radio from BW-011. The landlord's lamp and the print wait for the task-lamp and wall-art hooks. (implementation/slice6/images/F04_D_MAIN_OV.jpg)</t>
+          <t>4D_settee (Sofa195) on the long wall (the window wall carries the radiator), 4D_lamp_table (TableRect08) beside it, 4D_chair2 (ChairDark) at the dining table; the wireless table and radio from BW-011. (implementation/slice6/images/F04_D_MAIN_OV.jpg) Slice 25 hangs 4D_print (a photograph-frame copy) over the settee at 1.5 m (implementation/slice25); the landlord's lamp waits for the task-lamp family.</t>
         </is>
       </c>
     </row>
@@ -38407,10 +38407,14 @@
       </c>
       <c r="S527" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T527" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T527" s="2" t="inlineStr">
+        <is>
+          <t>Three archive crates (parts-crate copies, open-topped) under the desk wall against the south wall, clear of the desk's legs, the chair and its stance; the three copies in two locations read as the crates under the desk and the drawers above. Verified at 8877d9df (slice25): the thirteen families pass the fabrication batch (28,681 checks, 0 failures; objects 116, the strip and print on their actual wall faces, the crates inside the study clear of the desk, the deck bearing on the rig table), apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion routes 2C 9 and 4D 12 as before, upper lighting and the household save owner 0 failures, upper kitchens 206 with the baseline's stance labels, the three-space sweep 0 failures; captures in implementation/slice25.</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -28745,10 +28745,14 @@
       </c>
       <c r="S394" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T394" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>Both actors were absent, not misplaced: 4C_story_colorboard's anchor had no furniture record and F04_4C_BOOKSHELF_01 was missing from the bookshelf roster (as was 2C's F02_2C_BOOKSHELF_01). Slice 26 mounts the colour board as a completion copy of 5C's and adds both shelves to the roster (plain cases, Noel Price's and Juno Kells' libraries), registered with the household save owner (203 controls). Verified at WIP c9bc2317 + 432ad0a5 (implementation/slice26): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures once 6C is kept last in the manifest (its suite blanks the last record's canonical book); completion 2C and 4C 9 waypoints with their one pre-existing kitchen-leg failure; upper lighting 0 failures; F04_C_MAIN_DT1 shows the board, F04_C_MAIN_RV and F02_C_MAIN_RV show the new cases.</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -20523,10 +20523,14 @@
       </c>
       <c r="S283" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T283" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="inlineStr">
+        <is>
+          <t>The overview now reads a horticulturist's room: the propagation shelves and seed-jar rows under both west windows (slice 19), the specimen plant in its pot and the potting bench, beside the wall pieces of slice 15 (F03_A_MAIN_OV). Verified at WIP ed0359c3 (implementation/slice27b): fabrication batch 0 failures (surface stock bearings include the sectional case's top cap); apartment batch 236 (the branch baseline); bookshelves 144 checks, 0 failures with the ledger seated on the case; upper kitchens 206 (the branch baseline); four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -20773,10 +20777,14 @@
       </c>
       <c r="S286" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T286" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="inlineStr">
+        <is>
+          <t>3A's kitchen window is on the west wall, not over the sink, so the empty memorial pot (terracotta, dry soil, a chalk mark on the rim facing the room) stands at the back of the sink's drainboard under the wall cupboard and keeps the sink's detail view (implementation/slice27b/images/3A_memorial_pot_stock.jpg). It is passive stock: the INSPECT card waits for an inspect owner on surface stock. Verified at WIP ed0359c3 (implementation/slice27b): fabrication batch 0 failures (surface stock bearings include the sectional case's top cap); apartment batch 236 (the branch baseline); bookshelves 144 checks, 0 failures with the ledger seated on the case; upper kitchens 206 (the branch baseline); four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -28157,10 +28165,14 @@
       </c>
       <c r="S386" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T386" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>Kept exactly: no slice touches 4B_wake_bed or 4B_wake_nightstand. OrisonV2WakeReconstructionTest is unchanged: at 7478bd9c (before slice 26) and at slice 26's WIP c9bc2317 it passes the same 33 checks and then trips its own 150 s watchdog, a pre-existing timeout (implementation/slice27b/receipts, wake_*). Verified at WIP ed0359c3 (implementation/slice27b): fabrication batch 0 failures (surface stock bearings include the sectional case's top cap); apartment batch 236 (the branch baseline); bookshelves 144 checks, 0 failures with the ledger seated on the case; upper kitchens 206 (the branch baseline); four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -38353,10 +38365,14 @@
       </c>
       <c r="S526" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T526" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T526" s="2" t="inlineStr">
+        <is>
+          <t>V2 instances no monitor in 6A (the only MonitorProp anchors are F02_A_MONITOR_01 and F04_B_MONITOR_01), so nothing is removed; the desk wall gains a glass-plate box, a loupe and a print rack beside the existing headphones, cans, papers and mug (6A_deskwall_stock, F06_A_STUDY_DT1). Verified at WIP ed0359c3 (implementation/slice27b): fabrication batch 0 failures (surface stock bearings include the sectional case's top cap); apartment batch 236 (the branch baseline); bookshelves 144 checks, 0 failures with the ledger seated on the case; upper kitchens 206 (the branch baseline); four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -39763,10 +39779,14 @@
       </c>
       <c r="S545" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T545" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T545" s="2" t="inlineStr">
+        <is>
+          <t>The 1912 prospectus is already Mae's canonical book inside the sectional case (OrisonV2BookshelvesTest, Mae keeps canonical prospectus). The never-opened ledger now lies on the case's top under a dust film that stops short of one end; the anchor adapter hands passive stock seated on an anchor to the consumer that replaces it, so the ledger belongs to the bookcase (6C_ledger_stock, F06_C_MAIN_OV). Verified at WIP ed0359c3 (implementation/slice27b): fabrication batch 0 failures (surface stock bearings include the sectional case's top cap); apartment batch 236 (the branch baseline); bookshelves 144 checks, 0 failures with the ledger seated on the case; upper kitchens 206 (the branch baseline); four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -8967,10 +8967,14 @@
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T129" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>The watchman's chair (a ChairDark copy) is pulled up to the desk mass facing the lobby opening, a grey coat hangs on a hook between the mail door and the lobby wall, and the night watch's iron camp cot stands folded on end against the core wall with its blanket strapped on. Not made: the desk lamp, because a task lamp needs an acoustic graph node (orison_v2_task_lamp_installations.gd) that this pass does not author. Verified at WIP c6e01928 (implementation/slice28b): fabrication 0 failures, apartment batch 236, M08E with only its pre-existing route failure, M08F 29 checks, mail route 16, public doors 17, public furnishings 29, ground and wall-mount suites unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -9161,10 +9165,14 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T132" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>The operator's chair (a ChairOak copy) is pushed aside north of the house board, clear of the board's approach; the headset hangs on a brass hook beside the board with its cord looped below, and a coil of cord lies on the floor south of the board (a copy of 6A's cable coil). Not made: the extensions card, which is lettering and needs a Label3D owner. Verified at WIP c6e01928 with the same runs as F01_WATCH-001 (implementation/slice28b).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -9285,10 +9293,14 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T134" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>The parcel racks carry a load each, built into the public furnishings library and seated in the rack's own body (still two racks, four furnishing bodies): eight string-tied brown-paper parcels by size, one of them 6C's slatted auction crate, 2A's bundle of caption envelopes, and on the north rack's chest-height shelf the parcel book, a brass spring scale and a stamp pad with its rubber stamp (implementation/slice28b/images: parcel_racks_clear, F01_PACKAGE_OV). Verified at WIP c6e01928 (implementation/slice28b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); M08E with only its pre-existing boiler-to-radiator route failure; M08F 29 checks; mail route 16, public doors 17 and public furnishings 29 waypoints, 0 failures; ground and wall-mount suites 0 failures; the three-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1149,10 +1149,14 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>The firing tools: a coal shovel leaning on the west wall south of the fire door (outside its swing), the clinker rake on two nails at 1.3 m north of the door, and a lidded, ribbed ash can by the west wall with an oil can standing on a folded rag beside it (implementation/slice29/images: B1_boiler_ash_can_native, B1_boiler_rake_native, B1_BOILER_ROOM_RV). The ash can stands by the wall rather than under the ash door so the firing and ash door swings, the control aisle and the damper route stay clear; the ring decal is not made. Verified at WIP d53988d8 (implementation/slice29): fabrication batch 0 failures; apartment batch 236 (the branch baseline); boiler door swing 0, boiler route 17, basement route 88 and foundation 11 waypoints with 0 failures; boiler body, instruments, pipework and breeching 0 failures; household state 154 checks, 0 failures; the two-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1355,10 +1359,14 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>The Vantry signal frame hangs on the wall opposite the fuse panel (east of the door, clear of its swing): six bakelite terminal strips with brass terminals and blank tag cards on a board, cloth leads dressed into a bundle and a trunk cleated up the wall to the ceiling (B1_signal_frame_native, B1_ELECTRICAL_OV). Not made: the INSPECT owner; the frame is ambient. Verified at WIP d53988d8 (implementation/slice29): fabrication 0 failures, apartment batch 236, the eight boiler and basement suites unchanged (door swing, boiler route 17, basement route 88, body, instruments, pipework, breeching, foundation 11), household state 154 checks, 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1479,10 +1487,14 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Steel conduit rises from a floor flange into the fuse panel's backing box and leaves its top for a junction box under the ceiling, each run saddled to the wall, clear of the panel's door and working front (B1_fuse_conduit_native). Verified at WIP d53988d8 (implementation/slice29): fabrication batch 0 failures; apartment batch 236 (the branch baseline); boiler door swing 0, boiler route 17, basement route 88 and foundation 11 waypoints with 0 failures; boiler body, instruments, pipework and breeching 0 failures; household state 154 checks, 0 failures; the two-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -18137,10 +18137,14 @@
       </c>
       <c r="S250" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T250" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr">
+        <is>
+          <t>Juno's second wardrobe is the session archive: a wardrobe variant (Wardrobe13, on 5C_w1_wardrobe's case) adds two shelves to the original middle shelf and stands grey reel boxes spine-out with coloured tape on each, and omits the rail; both leaves keep their hinges and 92-degree swing (implementation/slice30b/images/Wardrobe13_open, a native render with the leaves open). Verified at WIP 0efdc84b (implementation/slice30b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; completion 2C 9 waypoints with its one pre-existing kitchen-leg failure; upper kitchens 206 (the branch baseline); the two-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -32915,10 +32919,14 @@
       </c>
       <c r="S451" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T451" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T451" s="2" t="inlineStr">
+        <is>
+          <t>Nadia's corrected floor plan is pinned to the icebox's food door: 5A's icebox has its own variant (FridgeIceboxPlan) whose sheet, ruled walls, copper-inked room and four brass pins belong to the door, so the sheet swings with the leaf and the ice door is untouched (implementation/slice30b/images/F05_A_KITCHEN_OV). The sheet sits on the food door's raised panel (0.43 to 0.83 m) because 1.2 m falls on the ice door; INSPECT stays with the fridge card. Verified at WIP 0efdc84b (implementation/slice30b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; completion 2C 9 waypoints with its one pre-existing kitchen-leg failure; upper kitchens 206 (the branch baseline); the two-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11191,10 +11191,14 @@
       </c>
       <c r="S159" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T159" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn's seven-day medication organizer, two compartments open, stands on the sink's drainboard ribs beside the dish rack: 1A's kitchen has no other free counter (no prep cabinet; the stove and the monitor-top fridge) (1A_medication_organizer_stock, F01_A_KITCHEN_DT1). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -13125,10 +13129,14 @@
       </c>
       <c r="S184" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T184" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>1D's bedside is a Nightstand01 completion copy at the head of the bed under the window, the bed chair moved to the window corner to make room; on it a saucer of wax ear plugs and the fob watch hung on its little brass stand, beside the nightstand's own glass (implementation/slice31b/images/F01_D_BED_DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -23517,10 +23525,14 @@
       </c>
       <c r="S322" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T322" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>3D's bedside is a Nightstand02 completion copy at the bed's head (as 1A's), carrying the tuning fork on its chain beside the nightstand's glass; Rhea's burgundy wool scarf hangs over the head post nearest it, folded over the turned finial (F03_D_BED_DT2). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -29459,10 +29471,14 @@
       </c>
       <c r="S403" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T403" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr">
+        <is>
+          <t>A ChairOak completion copy stands east of 4C's bed with Noel's maroon jersey folded on the seat, one sleeve over the front edge and a pale mended patch on the shoulder (4C_jersey_stock, F04_C_BED1_DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -35963,10 +35979,14 @@
       </c>
       <c r="S493" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T493" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T493" s="2" t="inlineStr">
+        <is>
+          <t>A ChairOak copy (5C_bed_chair) stands at the foot of Iris's bed with her navy overalls folded on the seat, both buckled straps over the edge; a small study canvas lies face down on the nightstand, stretcher bars up (5C_overalls_stock, F05_C_BED1_DT2/DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -761,10 +761,14 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Omar's deep-service evidence: an oil can standing on a folded rag by the first washer, a spare drive belt looped over a nail on the west wall between the washers, and a folded wooden stepladder leaning on the east wall south of the switch (implementation/slice32/images: B1_laundry_stepladder_native, B1_LAUNDRY views). Verified at WIP 87b953dc (implementation/slice32): fabrication batch 0 failures; apartment batch 236 on the long runner; laundry route 17, basement route 88, public doors 17, public furnishings 29 and wall mounts 4 waypoints with 0 failures; laundry apparatus and fittings, ground 0 failures; M08E with only its pre-existing route failure; Mina's laundry routine completes with no failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8493,10 +8497,14 @@
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T122" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>A cast-iron umbrella stand with its drip tray, two furled umbrellas and a walking stick stands in the vestibule's north-west corner, clear of both doors and the street-to-lobby route. Not made: the flush cast-iron grate mat (a floor inlay this pass does not cut) and the directory board. Verified at WIP 87b953dc (implementation/slice32): fabrication batch 0 failures; apartment batch 236 on the long runner; laundry route 17, basement route 88, public doors 17, public furnishings 29 and wall mounts 4 waypoints with 0 failures; laundry apparatus and fittings, ground 0 failures; M08E with only its pre-existing route failure; Mina's laundry routine completes with no failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8773,10 +8781,14 @@
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T126" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>A brass spittoon stands by the west bench's door end, clear of the radiator front and the arrival route. Not made: the worn patch on the bench (a texture change) and the dish of gloves on the radiator (the stock inspector has no radiator support). Verified at WIP 87b953dc (implementation/slice32): fabrication batch 0 failures; apartment batch 236 on the long runner; laundry route 17, basement route 88, public doors 17, public furnishings 29 and wall mounts 4 waypoints with 0 failures; laundry apparatus and fittings, ground 0 failures; M08E with only its pre-existing route failure; Mina's laundry routine completes with no failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -10203,10 +10215,14 @@
       </c>
       <c r="S147" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T147" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>The staff restroom's roller towel on its bracket on the west wall, a galvanised bucket with the mop standing in it in the north-west corner (the handle resting on the wall), and a bar of carbolic in a wall soap dish beside the basin (F01_restroom_* native captures, F01_STAFF_RESTROOM views). Verified at WIP 87b953dc (implementation/slice32): fabrication batch 0 failures; apartment batch 236 on the long runner; laundry route 17, basement route 88, public doors 17, public furnishings 29 and wall mounts 4 waypoints with 0 failures; laundry apparatus and fittings, ground 0 failures; M08E with only its pre-existing route failure; Mina's laundry routine completes with no failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -15335,10 +15335,14 @@
       </c>
       <c r="S213" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T213" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr">
+        <is>
+          <t>Two piped linen cushions lie on the ends of 2A's sofa seat (2A_cushion_a_stock). Not made: the 2.4 by 1.6 m rug, which would run under the coffee table and the deck in the most strictly checked flat. Verified at WIP 32156acb (implementation/slice33): fabrication batch 0 failures; apartment batch 236 on the long runner; bookshelves 144 checks, 0 failures with the print seated on the repaired case; upper kitchens 206 and upper furniture 488 (both unchanged from slice 31's runs); upper lighting 0 failures; roof route 53 waypoints, 0 failures; the three-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -37713,10 +37717,14 @@
       </c>
       <c r="S516" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T516" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T516" s="2" t="inlineStr">
+        <is>
+          <t>Sacha's editorial sequence: three small photographic prints in a row on the main room's north wall between the radiator and the bookcase, the middle one hung higher (copies of 2C_album_a; implementation/slice33/images: F06_A_MAIN views). Verified at WIP 32156acb (implementation/slice33): fabrication batch 0 failures; apartment batch 236 on the long runner; bookshelves 144 checks, 0 failures with the print seated on the repaired case; upper kitchens 206 and upper furniture 488 (both unchanged from slice 31's runs); upper lighting 0 failures; roof route 53 waypoints, 0 failures; the three-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -37771,10 +37779,14 @@
       </c>
       <c r="S517" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T517" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T517" s="2" t="inlineStr">
+        <is>
+          <t>The one picture of a plant: a small standing frame on the repaired bookcase's top board, which the surface-stock context inspector now names as a support (6A_plant_print_stock). Verified at WIP 32156acb (implementation/slice33): fabrication batch 0 failures; apartment batch 236 on the long runner; bookshelves 144 checks, 0 failures with the print seated on the repaired case; upper kitchens 206 and upper furniture 488 (both unchanged from slice 31's runs); upper lighting 0 failures; roof route 53 waypoints, 0 failures; the three-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -41119,10 +41131,14 @@
       </c>
       <c r="S563" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T563" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T563" s="2" t="inlineStr">
+        <is>
+          <t>Roof-use evidence inside the public bulkhead: a coil of washing line, a galvanised watering can and a gardening trug stand on the west landing north of the door, between the wall and the roof route (ROOF_bulkhead_* native captures). Not made: the chalk tally on the wall (lettering-like marks need a decal owner). Verified at WIP 32156acb (implementation/slice33): fabrication batch 0 failures; apartment batch 236 on the long runner; bookshelves 144 checks, 0 failures with the print seated on the repaired case; upper kitchens 206 and upper furniture 488 (both unchanged from slice 31's runs); upper lighting 0 failures; roof route 53 waypoints, 0 failures; the three-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -4727,10 +4727,14 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>Kept: no subway or kiosk source or export has changed since e63ce4f6 (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6247,10 +6251,14 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T87" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>Kept: none of the funeral parlour's sources or exports has changed since e63ce4f6; the bier stays empty (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7069,10 +7077,14 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T100" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>Kept: the pawn clock wall's sources and export are unchanged since e63ce4f6; the dials keep their geometric hour marks and no numerals (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7193,10 +7205,14 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T102" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>Kept: the radio service shop's sources and exports are unchanged since e63ce4f6 (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -11343,10 +11359,14 @@
       </c>
       <c r="S161" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T161" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>Kept: F01_1A_FRIDGE_01 is FridgeMonitor at e63ce4f6 and at this slice (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -12041,10 +12061,14 @@
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T170" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn's trunk of lesson plans (an iron-banded wooden trunk, a larger variant of the suitcase form) stands against the study's north wall clear of the storage door, and two tea tins sit on the study desk beside her open register (1A_lesson_trunk_native, 1A_tea_tin_a_stock). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -15397,10 +15421,14 @@
       </c>
       <c r="S214" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T214" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>Kept: 2A_deck and 2A_projector_stand are unmoved and domestic_projectors.json is unchanged since e63ce4f6; the projector stands at yaw 0 and throws along -z toward the south pier, while the caption board hangs on the west window wall, outside that throw (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -21671,10 +21699,14 @@
       </c>
       <c r="S297" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T297" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="inlineStr">
+        <is>
+          <t>Kept: household_radios.json, domestic_projectors.json and F03_B_LAMP_01's installation are unchanged since e63ce4f6 (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -31207,10 +31239,14 @@
       </c>
       <c r="S427" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T427" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T427" s="2" t="inlineStr">
+        <is>
+          <t>Kept: none of the twelve stair family sources or exports has changed since e63ce4f6; no baked wear was added (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -41407,10 +41443,14 @@
       </c>
       <c r="S567" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T567" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T567" s="2" t="inlineStr">
+        <is>
+          <t>Chimney-sweep evidence inside the service bulkhead: a tied soot sack on the landing and the sweep's rod bundle with its brush head leaning on the west wall north of the door, clear of the roof route (ROOF_service_* native captures). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -42639,10 +42679,14 @@
       </c>
       <c r="S585" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T585" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T585" s="2" t="inlineStr">
+        <is>
+          <t>Kept empty: no anchor lies in ROOF_DECK_NORTHEAST at e63ce4f6 or at this slice (implementation/slice34/receipts/keep_audit.receipt.json). Verified at WIP 974ee6d2 (implementation/slice34): fabrication batch 0 failures; apartment batch 236 on the long runner; completion 1A 15 waypoints with its pre-existing kitchen-leg failure; roof route 53 waypoints, 0 failures; the two-space sweep 0 failures; the keep audit (receipts/keep_audit.receipt.json) holds for all nine keep items.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16049,10 +16049,14 @@
       </c>
       <c r="S222" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T222" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr">
+        <is>
+          <t>2A's bedroom pinboard (DomesticObject00) is filled to a full grid of 24 cards (implementation/slice35b/images: F02_A_BED_DT1). Not made: the two deliberately overlapping cards; the pinboard form lays a neat grid. Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -29305,10 +29309,14 @@
       </c>
       <c r="S400" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T400" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="inlineStr">
+        <is>
+          <t>4C's two wardrobes hold different residents' clothes: Cam's (Wardrobe15) hangs maroon jersey and Noel's (Wardrobe08, now used only by 4C_w1) indigo drill; jersey_maroon and drill_indigo are tinted aliases of the catalogue linen (Wardrobe15_open, Wardrobe08_open). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -35759,10 +35767,14 @@
       </c>
       <c r="S489" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T489" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T489" s="2" t="inlineStr">
+        <is>
+          <t>Iris's second wardrobe is the pigment store: its own variant (Wardrobe14) adds two shelves above the case's middle shelf and stands rows of pigment tins with painted lids, jars of ground colour and rolled canvas, with no rail (implementation/slice35b/images: Wardrobe14_open, F05_C_STUDIO_DT1). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -40451,10 +40463,14 @@
       </c>
       <c r="S553" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T553" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T553" s="2" t="inlineStr">
+        <is>
+          <t>Mae's second wardrobe is the packing store: its variant (Wardrobe12, only 6C_w1's) shelves stacked flat cartons in kraft, folded brown paper and balls of string, with no rail (Wardrobe12_open, F06_C_STUDIO_DT2). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -15671,10 +15671,14 @@
       </c>
       <c r="S217" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T217" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr">
+        <is>
+          <t>Resolved by BW-012 in slice 1: F02_2A_FRIDGE_01 is FridgeIcebox, and the household fridge module passes in this slice's fabrication batch. Not shown: OrisonV2WakeReconstructionTest, which the acceptance names, stops at its own 150 s watchdog after 33 passes on this branch independent of these slices (unchanged since 7478bd9c).</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -22011,10 +22015,14 @@
       </c>
       <c r="S301" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T301" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr">
+        <is>
+          <t>Omar's range (F03_3B_STOVE_01) is HouseholdGasRangeWorkshop: tape residue on the fascia and splashback and a replacement oven panel in another enamel (HouseholdGasRangeWorkshop_closed, F03_B_KITCHEN_DT3). Both marks are too close in tone to read at the detail distance, and slice 37 strengthens them. The named enamel_* recipes are not in owner_finish_profiles.json; the finishes are tinted enamel variants of the stove family. Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -23145,10 +23153,14 @@
       </c>
       <c r="S316" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T316" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="inlineStr">
+        <is>
+          <t>Resolved by BW-012 in slice 1: F03_3D_FRIDGE_01 is FridgeIcebox, and the household fridge module passes in this slice's fabrication batch. Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -35553,10 +35565,14 @@
       </c>
       <c r="S486" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T486" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T486" s="2" t="inlineStr">
+        <is>
+          <t>Iris's range (F05_5C_STOVE_01) is its own variant, HouseholdGasRangePaintFlecked: ochre, viridian and white flecks on the hob, fascia and splashback, colour at the control knobs, and a tin of brushes standing on the cold back burner (implementation/slice36/images: F05_C_KITCHEN_DT1, HouseholdGasRangePaintFlecked_closed). The brush tin is part of the range rather than desktop stock, since the stock inspector has no stove support. Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -39225,10 +39241,14 @@
       </c>
       <c r="S536" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T536" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T536" s="2" t="inlineStr">
+        <is>
+          <t>Jonah's range (F06_6B_STOVE_01) and Juno's (F02_2C_STOVE_01) are HouseholdGasRangeGreasy: yellowed enamel with a grime tide line under the hob and prints at the knobs (implementation/slice36/images: F06_B_KITCHEN_DT1). The yellowed tone reads in the detail view; the grime marks are too faint at that distance, and slice 37 strengthens them. Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -40327,10 +40347,14 @@
       </c>
       <c r="S551" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T551" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T551" s="2" t="inlineStr">
+        <is>
+          <t>Mae's range (F06_6C_STOVE_01) and Evelyn's (F01_1A_STOVE_01) are HouseholdGasRangePristine: bright, clean enamel with no wear marks (F06_C_KITCHEN_DT1, HouseholdGasRangePristine_closed). Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -20557,10 +20557,14 @@
       </c>
       <c r="S282" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T282" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T282" s="2" t="inlineStr">
+        <is>
+          <t>Repotting on 3A's dining table: a folded sheet of unprinted newsprint, a freshly filled pot with its seedling, the emptied smaller pot, a spill of soil and a trowel (F03_A_MAIN_DT2). Not made: moving the table against the inner wall with one chair pulled out; the table keeps its authored place and stance. Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -22015,12 +22019,12 @@
       </c>
       <c r="S301" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>Omar's range (F03_3B_STOVE_01) is HouseholdGasRangeWorkshop: tape residue on the fascia and splashback and a replacement oven panel in another enamel (HouseholdGasRangeWorkshop_closed, F03_B_KITCHEN_DT3). Both marks are too close in tone to read at the detail distance, and slice 37 strengthens them. The named enamel_* recipes are not in owner_finish_profiles.json; the finishes are tinted enamel variants of the stove family. Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+          <t>Omar's range (F03_3B_STOVE_01) is HouseholdGasRangeWorkshop: aged yellow-brown tape residue on the fascia and splashback and a sage replacement oven panel, strengthened in slice 37 so both read at the detail distance (implementation/slice37/images: F03_B_KITCHEN_DT3). The named enamel_* recipes are not in owner_finish_profiles.json; the finishes are tinted enamel variants of the stove family. Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
         </is>
       </c>
     </row>
@@ -28211,10 +28215,14 @@
       </c>
       <c r="S385" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T385" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>Removed: 4B's equipment shelf has its own bare variant (Shelf11), the Shelf01 frame without the painted bins and metal tins it inherited from 3B's tool shelf record; the closet now shows only the capsule tin, bulb carton and cap (implementation/slice37/images: F04_B_CLOSET_OV, F04_B_CLOSET_TH). Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -28347,10 +28355,14 @@
       </c>
       <c r="S387" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T387" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>A pair of work boots kicked off at the alcove bed's foot, one fallen against the other, on the west side clear of the wake route and bedside stance, and a blank work slip on the nightstand (F04_B_ALCOVE_OV). Not made: the thrown-back bedding, which needs a bedding variant of the bed family. Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -32641,10 +32653,14 @@
       </c>
       <c r="S446" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T446" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T446" s="2" t="inlineStr">
+        <is>
+          <t>Six thick uniform code books with blank spines stand between plain steel bookends on top of 5A's plain case (F05_A_MAIN_DT3). Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -32769,10 +32785,14 @@
       </c>
       <c r="S448" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T448" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T448" s="2" t="inlineStr">
+        <is>
+          <t>Identified: the two recesses are the openings to the vestibule and the private hall. With BW-016's room-leaf paints, the reverse view shows both as open doorways with the lit hall beyond, not flat panels (F05_A_MAIN_RV). Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -39011,10 +39031,14 @@
       </c>
       <c r="S533" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T533" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T533" s="2" t="inlineStr">
+        <is>
+          <t>Pale bloom rings, three overlapping per cluster, on 6B's dining table (two clusters), the wireless table's free end and the plain bookcase top; the context inspector now names the plain case's top board as a support (F06_B_MAIN_DT1). Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -39241,12 +39265,12 @@
       </c>
       <c r="S536" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T536" s="2" t="inlineStr">
         <is>
-          <t>Jonah's range (F06_6B_STOVE_01) and Juno's (F02_2C_STOVE_01) are HouseholdGasRangeGreasy: yellowed enamel with a grime tide line under the hob and prints at the knobs (implementation/slice36/images: F06_B_KITCHEN_DT1). The yellowed tone reads in the detail view; the grime marks are too faint at that distance, and slice 37 strengthens them. Verified at WIP 0b562633 (implementation/slice36): fabrication batch 0 failures across 13 modules (the household stove module now walks each range's own assembly and checks that an owner finish replaces the household tone); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 482; upper lighting 0 failures; completion 1A 15 waypoints and 2C 9 waypoints, each with its one pre-existing route failure; the six-kitchen sweep 0 failures; native renders of the four finishes (images: HouseholdGasRange*_closed).</t>
+          <t>Jonah's range (F06_6B_STOVE_01) and Juno's (F02_2C_STOVE_01) are HouseholdGasRangeGreasy: yellowed enamel with a dark grime tide line under the hob, wide prints at the knobs and grease spatter on the splashback, strengthened in slice 37 so the marks read at the detail distance (implementation/slice37/images: F06_B_KITCHEN_DT1). Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16673,10 +16673,14 @@
       </c>
       <c r="S230" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T230" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>Lena's tripod dress form (new dressform object) wears her own printed voile frock with a row of steel pins in the turned-up hem; 2B has no armchair, so it stands by the south window wall east of the hall opening, clear of the radiator stance, and reads in the reverse view (implementation/slice38/images: F02_B_MAIN_RV). Verified at WIP d0986324 (implementation/slice38): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 2C 9 waypoints with its one pre-existing route failure; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -18485,10 +18489,14 @@
       </c>
       <c r="S254" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T254" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
+          <t>Juno's black Bakelite recorder (two reels, a knob, a front grille, a cloth cord) and a mug on 2C's nightstand (F02_C_BED1_OV). Not made: the thrown-back counterpane, which needs a bedding variant of the bed family. Verified at WIP d0986324 (implementation/slice38): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 2C 9 waypoints with its one pre-existing route failure; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16607,10 +16607,14 @@
       </c>
       <c r="S229" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T229" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
+          <t>Lena's cutting kit on the worktable beside the pattern papers and notions: closed tailor's shears, a cake of tailor's chalk, a rolled cloth tape measure with its end run out (blank) and a tomato pincushion with pins (F02_B_MAIN_DT1). Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -17051,10 +17055,14 @@
       </c>
       <c r="S235" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T235" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr">
+        <is>
+          <t>Lena's cloth stands as bolts on both fabric shelves: their own variant (Shelf12) drops the inherited bins and tins and stands five bolts on each of the three lower boards, in wool suiting, voile and burgundy knit with card cores showing (implementation/slice39/images: F02_B_PRIVATE_HALL_TH, F02_B_PRIVATE_HALL_OV). Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -20429,10 +20437,14 @@
       </c>
       <c r="S280" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T280" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="inlineStr">
+        <is>
+          <t>Malcolm's pruning station on the potting bench: a zinc watering tray with two pots standing in water and red-handled secateurs on a square of dark oilcloth (F03_A_MAIN_DT1). Not made: the trug, the soil swept under the bench and the knife-mark line on the bench edge. Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -21661,10 +21673,14 @@
       </c>
       <c r="S296" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T296" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr">
+        <is>
+          <t>Omar's six-drawer fastener cabinet with blank card label frames and nickel pulls, and a bank of eight small lidded tins with blank labels, stand on the third board of both tool shelves (Shelf13), clear of the source bins and tins below (F03_B_MAIN_DT2). Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -27277,10 +27293,14 @@
       </c>
       <c r="S372" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T372" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>Closed against the capture: neither the overview nor the reverse view of 4B's main room shows a featureless white box (F04_B_MAIN_OV, F04_B_MAIN_RV). Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -30069,10 +30089,14 @@
       </c>
       <c r="S410" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T410" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>Closed against the capture: no untextured mass appears in 4D's main room; the pale form in the room is the upholstered settee (F04_D_MAIN_OV, F04_D_MAIN_RV). Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -34499,10 +34523,14 @@
       </c>
       <c r="S471" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T471" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T471" s="2" t="inlineStr">
+        <is>
+          <t>Data and capture agree: both 5B_k_hob_radio anchors sit at table height over 5B_comparison_table, and the kitchen shows the two sets on that table with the range shelf empty (F05_B_KITCHEN_DT1). The table is kept; the ids keep their legacy names because saves and the spatial manifest key on them. Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -35359,10 +35387,14 @@
       </c>
       <c r="S483" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T483" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T483" s="2" t="inlineStr">
+        <is>
+          <t>Identified, nothing to remove: the dark loop on the floor is the shadow of the radiator valve's handwheel thrown by the pendant, and the boxy object is the valve itself; no cable exists (F05_C_STUDIO_OV). Verified at WIP 997a7465 (implementation/slice39): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the eight-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -13013,10 +13013,14 @@
       </c>
       <c r="S182" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T182" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>Identified: the blue-white light is 1D's lit back burner, one of the two households that boot with a ring lit; its gas flame is visible at the burner and lights the splashback (F01_D_KITCHEN_DT1). Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -18431,10 +18435,14 @@
       </c>
       <c r="S253" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T253" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="inlineStr">
+        <is>
+          <t>Measured with BW-005: 2C's branch hangs on a trapeze hanger seated at the slab soffit and ends in the fitted louvred register; a galvanised branch run is correct for the building's ventilation retrofit, so it stays (F02_C_BATH_DT1).</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -27609,10 +27617,14 @@
       </c>
       <c r="S376" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T376" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>Closed against the capture: 4B's range is the native gas range with cream enamel sides and cast-iron spider grates over the rings; no wood grain and no coil burners remain (F04_B_KITCHEN_DT1). Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -30895,10 +30907,14 @@
       </c>
       <c r="S421" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T421" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T421" s="2" t="inlineStr">
+        <is>
+          <t>4D's late-night state: an open leather suitcase on the blanket with a few things packed, and the wardrobe's own variant (Wardrobe16) holding only empty wire hangers (F04_D_BED_OV, Wardrobe16_open). Not made: the mismatched pillows, which need a bedding variant. Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -32755,10 +32771,14 @@
       </c>
       <c r="S447" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T447" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T447" s="2" t="inlineStr">
+        <is>
+          <t>Nadia's architect counterweight lamp now has a black japanned arm, pedestal, counterweight and shade (the catalogue iron_blackened); only the ball joints and the rolled shade lip stay nickel, on its wooden base (implementation/slice40/images: architect_counterweight_front, F05_A_MAIN_DT2). Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -33495,10 +33515,14 @@
       </c>
       <c r="S457" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T457" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T457" s="2" t="inlineStr">
+        <is>
+          <t>An oak-framed glazed case now stands over Nadia's site model on its table, clear of the massing, and her boxwood T-square hangs head-down on a nail on the study wall beside the pinboard (5A_tsquare_native, F05_A_STUDY_DT1). Not made: paper bands on the rolls; the study holds no rolled drawings to band. Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1627,10 +1627,14 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>The basement shop's stock: six kraft bulb cartons on the parts shelf's third board (its own variant, Shelf14), a capsule crate on the floor at the bench's east end, and the SR7 charging case on the floor by the west wall with its cloth lead run up to a wall plate (B1_charging_case_native, B1_MAINTENANCE_SHOP_OV). The bench, a copy of 3B's, already carries a vice at its west end. Not made: the service-round tally board (needs Label3D) and a vice at the door end. Verified at WIP fd1cffd0 (implementation/slice41): fabrication batch 0 failures across 13 modules (the hall file and the charging case captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (unchanged from slice 40); upper lighting 0 failures; basement route 88 waypoints and wall mounts 4 waypoints, 0 failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -26331,10 +26335,14 @@
       </c>
       <c r="S359" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T359" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>4A's toaster is its own variant (ToasterForm) with a blank form taped by two strips to the front half of the lever end, beside the slot; the carriage lever and the browning control on the other end stay clear (ToasterForm_lever_end, a native render of the installed variant). Verified at WIP fd1cffd0 (implementation/slice41): fabrication batch 0 failures across 13 modules (the hall file and the charging case captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (unchanged from slice 40); upper lighting 0 failures; basement route 88 waypoints and wall mounts 4 waypoints, 0 failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -26491,10 +26499,14 @@
       </c>
       <c r="S361" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T361" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="inlineStr">
+        <is>
+          <t>Wren's hall file: a second-hand oak four-drawer vertical file (new verticalfile object, 0.40 x 0.71 x 1.34 m) against the hall's east wall between the switch and the boots, the top drawer not quite shut, nickel pulls, blank brass label frames, finger grime at the top pull and a cup ring on the top; the hall keeps over 2 m clear (implementation/slice41/images: 4A_hall_file_native, F04_A_PRIVATE_HALL_OV). Verified at WIP fd1cffd0 (implementation/slice41): fabrication batch 0 failures across 13 modules (the hall file and the charging case captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (unchanged from slice 40); upper lighting 0 failures; basement route 88 waypoints and wall mounts 4 waypoints, 0 failures; the four-space sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -4417,10 +4417,14 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>Identified: the small bright sphere beside the blade is the moon, already placed on the sky dome among the stars and the Milky Way; it is not a light mesh, so nothing is hidden (facade_blade, city sweep). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -12307,10 +12311,14 @@
       </c>
       <c r="S173" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T173" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>The quiet sign (new quietsign object): a small framed card with one hand-drawn stroke and no lettering at 1.4 m on the vestibule's south wall, beyond the entry leaf's sweep and seen through the door from the service hall, with the brass hook for her fob watch below it (1D_quiet_sign_native). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -12631,10 +12639,14 @@
       </c>
       <c r="S177" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T177" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>Teresa's house bell (new wallbell object): a Bakelite dome on a brass bracket high on the main room's west wall, directly above the switch's signal outlet, its grey cloth flex run down the wall to the outlet with a band of black tape where she tried to cut it; no sound added (implementation/slice42/images: 1D_house_bell_native). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -26097,10 +26109,14 @@
       </c>
       <c r="S356" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T356" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="inlineStr">
+        <is>
+          <t>4A's wireless table reads a radio: Peter's metal-cased three-dial set with the rebuilt cone speaker beside it on its own stand (F04_A_MAIN_RV). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -28863,10 +28879,14 @@
       </c>
       <c r="S393" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T393" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr">
+        <is>
+          <t>Cam's route map over 4C's colour board (its own variant, DomesticObject68): a red thread pinned across the board from stop to stop with blank ticket stubs at alternate stops; no lettering (4C_story_colorboard_native). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -34259,10 +34279,14 @@
       </c>
       <c r="S467" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T467" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr">
+        <is>
+          <t>The domestic radio's cone speaker is rebuilt: a smooth 48-segment open cone in black-lacquered paper with a flipped inner shell so its concave face reads from the front, a japanned rim, a brass dust cap and the drive unit on a rear strut over its own foot; the second stand the V2 radio used to add under it is gone. 5B's horn-and-cone pair reads both speakers (F05_B_MAIN_DT2, F02_B_MAIN_RV). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -34699,10 +34723,14 @@
       </c>
       <c r="S473" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T473" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T473" s="2" t="inlineStr">
+        <is>
+          <t>Cal's hearing aid out for the night on the alcove nightstand: the battery box with brass terminals, the microphone box with its grille and the earpiece, its cord coiled beside them (new hearingaid stock; F05_B_ALCOVE_OV). Not made: a second bedside receiver from the domestic radio family. Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -4681,10 +4681,14 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T62" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>The alley rear door is the same service leaf and now shows its stiles, mid rail and kick plates (alley_0). Not made: the panel field keeps its speckled painted-steel finish. Verified at WIP f611321a (implementation/slice43): fabrication batch 0 failures across 14 modules (work tables included); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (eight fewer of the pre-existing material-binding class, from the headsets); upper lighting 0 failures; public doors 17 waypoints, 0 failures; door casings 107 openings, 0 failures; the eight-space sweep and the 130-station city sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -21825,10 +21829,14 @@
       </c>
       <c r="S298" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T298" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr">
+        <is>
+          <t>Omar's bench cupboard and its lower tray are grey painted iron (the catalogue iron_neutral) instead of blackened iron, so the carcass reads as painted sheet metal (3B_workbench_stock, native 3B_workbench). Not made: the shelving posts and the radio's seat. Verified at WIP f611321a (implementation/slice43): fabrication batch 0 failures across 14 modules (work tables included); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (eight fewer of the pre-existing material-binding class, from the headsets); upper lighting 0 failures; public doors 17 waypoints, 0 failures; door casings 107 openings, 0 failures; the eight-space sweep and the 130-station city sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -22133,10 +22141,14 @@
       </c>
       <c r="S302" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T302" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr">
+        <is>
+          <t>The service leaf's plain face gets flat-bar stiles, a top rail, a mid rail at lock height and kick plates on both faces in the leaf's cast-iron finish, so the kitchen's service door reads as a framed leaf, not a charcoal slab (F03_B_KITCHEN_RV). Verified at WIP f611321a (implementation/slice43): fabrication batch 0 failures across 14 modules (work tables included); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (eight fewer of the pre-existing material-binding class, from the headsets); upper lighting 0 failures; public doors 17 waypoints, 0 failures; door casings 107 openings, 0 failures; the eight-space sweep and the 130-station city sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -38757,10 +38769,14 @@
       </c>
       <c r="S528" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T528" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T528" s="2" t="inlineStr">
+        <is>
+          <t>Sacha's desk wall is an oak top on two solid oak ends (a panel between a plinth and a cap) inside the original slab-support envelope, in place of the white painted slab on black folded pedestals; the headset lies on the desk, band on its side and both cups on their backs with the lead run off across the top, in place of the turned stand (implementation/slice43/images: 6A_deskwall_stock, F06_A_STUDY_OV, native 6A_deskwall). Verified at WIP f611321a (implementation/slice43): fabrication batch 0 failures across 14 modules (work tables included); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (eight fewer of the pre-existing material-binding class, from the headsets); upper lighting 0 failures; public doors 17 waypoints, 0 failures; door casings 107 openings, 0 failures; the eight-space sweep and the 130-station city sweep 0 failures.</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -16147,10 +16147,14 @@
       </c>
       <c r="S223" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T223" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr">
+        <is>
+          <t>Mina's street state: her slate tailor-made jacket with a white collar on a wire hanger over the wardrobe leaf (it swings with the leaf), slate garments inside, a grey cloche on the case top, and the bed squared (F02_A_BED_OV, F02_A_BED_RV). Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -16935,10 +16939,14 @@
       </c>
       <c r="S233" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T233" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
+          <t>Lena's blue enamel stock pot, lid on, on 2B's one lit ring at the back right (a new HouseholdGasRangePot variant of the range; F02_B_KITCHEN_OV, native HouseholdGasRangePot). Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -18019,10 +18027,14 @@
       </c>
       <c r="S247" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T247" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr">
+        <is>
+          <t>Juno's four plain reel boxes stacked on the cold front-left ring of 2C's greasy range, the side she never cooks on (HouseholdGasRangeGreasyTapes; F02_C_KITCHEN_OV). Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -18525,12 +18537,12 @@
       </c>
       <c r="S254" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T254" s="2" t="inlineStr">
         <is>
-          <t>Juno's black Bakelite recorder (two reels, a knob, a front grille, a cloth cord) and a mug on 2C's nightstand (F02_C_BED1_OV). Not made: the thrown-back counterpane, which needs a bedding variant of the bed family. Verified at WIP d0986324 (implementation/slice38): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 2C 9 waypoints with its one pre-existing route failure; the four-space sweep 0 failures.</t>
+          <t>Juno's black Bakelite recorder (two reels, a knob, a front grille, a cloth cord) and a mug on 2C's nightstand (F02_C_BED1_OV). Slice 46 made the bed unmade: the counterpane pushed down past the pillows on a slant (Bed_150_205_unmade; F02_C_BED1_OV). Verified at WIP d0986324 (implementation/slice38): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 486 (unchanged from slice 37); upper lighting 0 failures; completion 2C 9 waypoints with its one pre-existing route failure; the four-space sweep 0 failures. Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
         </is>
       </c>
     </row>
@@ -26055,10 +26067,14 @@
       </c>
       <c r="S355" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T355" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="inlineStr">
+        <is>
+          <t>Both dining chairs tucked square to 4A's round table (F04_A_MAIN_OV). Not made: the radio dial set at one station. Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -28435,12 +28451,12 @@
       </c>
       <c r="S387" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T387" s="2" t="inlineStr">
         <is>
-          <t>A pair of work boots kicked off at the alcove bed's foot, one fallen against the other, on the west side clear of the wake route and bedside stance, and a blank work slip on the nightstand (F04_B_ALCOVE_OV). Not made: the thrown-back bedding, which needs a bedding variant of the bed family. Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove.</t>
+          <t>A pair of work boots kicked off at the alcove bed's foot, one fallen against the other, on the west side clear of the wake route and bedside stance, and a blank work slip on the nightstand (F04_B_ALCOVE_OV). Slice 46 made the thrown-back bedding: the wake bed's blanket thrown back to the foot third in a bundle (bedding variant Bed_135_260_thrown; F04_B_ALCOVE_OV). Verified at WIP 991e7f05 (implementation/slice37): fabrication batch 0 failures across 13 modules; apartment batch 236 on the long runner; household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures with stock on the plain case tops; upper kitchens 206; upper furniture 486 (four more of the pre-existing material-binding class, from new stock meshes on probed tables); upper lighting 0 failures; the eight-space sweep 0 failures. The earned-dream suite stops at its own precondition (no earned input save) before it reaches the alcove. Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
         </is>
       </c>
     </row>
@@ -30951,12 +30967,12 @@
       </c>
       <c r="S421" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T421" s="2" t="inlineStr">
         <is>
-          <t>4D's late-night state: an open leather suitcase on the blanket with a few things packed, and the wardrobe's own variant (Wardrobe16) holding only empty wire hangers (F04_D_BED_OV, Wardrobe16_open). Not made: the mismatched pillows, which need a bedding variant. Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures.</t>
+          <t>4D's late-night state: an open leather suitcase on the blanket with a few things packed, and the wardrobe's own variant (Wardrobe16) holding only empty wire hangers (F04_D_BED_OV, Wardrobe16_open). Slice 46 made the mismatched pillows: one full pillow beside a smaller, flatter one set askew (Bed_150_205_pillows; F04_D_BED_DT2). Verified at WIP da33cf1d (implementation/slice40): fabrication batch 0 failures across 14 modules (task lamps included; the T-square captured natively); apartment batch 236 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488 (two more of the pre-existing material-binding class, from new stock meshes on probed furniture); upper lighting 0 failures; completion 4D 12 waypoints with its one pre-existing route failure; the three-space sweep and a seven-space inspection sweep 0 failures. Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
         </is>
       </c>
     </row>
@@ -36141,10 +36157,14 @@
       </c>
       <c r="S492" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T492" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T492" s="2" t="inlineStr">
+        <is>
+          <t>The sink wall is tiled: it belongs to the public core, whose wall also faces 5C's vestibule and kitchen, and the far-face tile skin now covers every bath span along a dry owner's wall instead of only the first neighbour found. The same change tiles the 2A and 4B sink walls (F05_C_BATH_OV, F02_A_BATH_OV, F04_B_BATH_OV). Verified at WIP 15aee765 (implementation/slice44): fabrication batch 0 failures across 13 modules; apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 2C 9 waypoints and 4D 12, each with its one pre-existing route failure; public doors 17 waypoints, 0 failures; the thirteen-space sweep 0 failures; the bedding test (WIP 777d2ec2) 19 beds and 76 contacts with its one pre-existing failure, no clear inspection stance for 5C_bed0, as at slice 43.</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11539,10 +11539,14 @@
       </c>
       <c r="S163" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T163" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn's medicated routine: a glass with a dosing spoon, two small brown bottles, a powder box and a tin of hairpins (1A_bath_shelf_native). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -13427,10 +13431,14 @@
       </c>
       <c r="S187" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T187" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr">
+        <is>
+          <t>Teresa's: a glass and toothbrush, a tin of pins for the bun, a brown antiseptic bottle (native DomesticObject71). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -15863,10 +15871,14 @@
       </c>
       <c r="S219" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T219" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="inlineStr">
+        <is>
+          <t>Mina's, kept exact: a glass and toothbrush, a cold-cream jar, a powder box and a comb (2A_bath_shelf_native). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -17313,10 +17325,14 @@
       </c>
       <c r="S238" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T238" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr">
+        <is>
+          <t>Lena's: a glass and toothbrush, a cake of soap and the selvedge scrap she ties her hair with (native DomesticObject73). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -18339,10 +18355,14 @@
       </c>
       <c r="S251" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T251" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="inlineStr">
+        <is>
+          <t>Juno's: a glass and toothbrush, a kohl pot with its stick, a brass compact (native DomesticObject74). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -21171,10 +21191,14 @@
       </c>
       <c r="S289" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T289" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="inlineStr">
+        <is>
+          <t>Malcolm's: a glass and toothbrush, a nail brush for the earth under his nails, a shaving mug with its brush, a safety razor (native DomesticObject75). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -22461,10 +22485,14 @@
       </c>
       <c r="S306" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T306" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>Omar's practical set: a glass and toothbrush, a shaving mug, a nail brush, pumice and red carbolic soap (3B_bath_shelf_native). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -23467,10 +23495,14 @@
       </c>
       <c r="S319" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T319" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T319" s="2" t="inlineStr">
+        <is>
+          <t>Rhea's voice care: two glasses (gargle and rinse), a jar of pastilles, an inhaler and a lipstick (native DomesticObject77). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -25709,10 +25741,14 @@
       </c>
       <c r="S350" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T350" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="inlineStr">
+        <is>
+          <t>Wren's japanned umbrella drip tray by 4A's door, let overflow: grey standing water at the rim, a dark water line spread on the oak around it, and his furled umbrella standing in it against the wall (4A_umbrella_tray_native, F04_A_VESTIBULE_TH). Slice 44 placed the tray; its black water read as a floor register until slice 47. Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -26633,10 +26669,14 @@
       </c>
       <c r="S362" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T362" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T362" s="2" t="inlineStr">
+        <is>
+          <t>Peter's, kept exact: a glass and toothbrush, a shaving mug, a safety razor and a comb (native DomesticObject78). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -27977,10 +28017,14 @@
       </c>
       <c r="S380" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T380" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>The player's: a glass and toothbrush, a cake of soap, a comb (native DomesticObject79). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -29523,10 +29567,14 @@
       </c>
       <c r="S401" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T401" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr">
+        <is>
+          <t>Cam's and Noel's, divided: a glass and a soap on each side with a strip of tape between them (4C_bath_shelf_native). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -30765,10 +30813,14 @@
       </c>
       <c r="S418" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T418" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T418" s="2" t="inlineStr">
+        <is>
+          <t>The short-let: two wrapped cakes of hotel soap and a blank house-rules card propped at the back, nothing of anybody's (native DomesticObject81). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -33311,10 +33363,14 @@
       </c>
       <c r="S453" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T453" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T453" s="2" t="inlineStr">
+        <is>
+          <t>Nadia's practical set: a glass and toothbrush, a nail brush, pumice, carbolic soap and a lipstick (native DomesticObject82). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -34841,10 +34897,14 @@
       </c>
       <c r="S474" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T474" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T474" s="2" t="inlineStr">
+        <is>
+          <t>Cal's: a glass and toothbrush, a shaving mug, a safety razor and three hearing-aid cells (native DomesticObject83). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -36025,10 +36085,14 @@
       </c>
       <c r="S490" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T490" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T490" s="2" t="inlineStr">
+        <is>
+          <t>Iris's brush washing: a glass and toothbrush, a turpentine jar, a tin of brushes bristle-up and a nail brush (5C_bath_shelf_native). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -38401,10 +38465,14 @@
       </c>
       <c r="S522" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T522" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T522" s="2" t="inlineStr">
+        <is>
+          <t>Sacha's: a glass and toothbrush, two brown developer bottles and bamboo print tongs, the bath being a darkroom twice a week (native DomesticObject85). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -39647,10 +39715,14 @@
       </c>
       <c r="S539" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T539" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T539" s="2" t="inlineStr">
+        <is>
+          <t>Jonah's: a glass and toothbrush, a shaving mug and a safety razor he rarely uses (native DomesticObject86). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -40741,10 +40813,14 @@
       </c>
       <c r="S554" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T554" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T554" s="2" t="inlineStr">
+        <is>
+          <t>Mae's, kept exact: a glass and toothbrush, a powder box, a tin of hairpins, a lipstick and her buttonhook (native DomesticObject87). An opal glass shelf on two nickel brackets over the basin, between its coved back and the medicine cabinet's lower edge, carries the set (one domestic object per bath; the lavatory has a rolled rim and no flat ledge, and the surface-stock asset is at GitHub's file-size limit, so the set is not desktop stock on the rim). Verified at WIP 093e8d3f (implementation/slice47): fabrication batch 0 failures across the domestic objects and medicine cabinets (5 shelves and the tray captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; completion 1A 15 waypoints and 4D 12, each with its one pre-existing route failure; the nineteen-space sweep 0 failures. The objects context inspector finds all 72 bracket contacts on real wall faces (4B's on the bath's wall extension).</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -955,10 +955,14 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>The basement notice at the stair foot, in the same taped oak frame on the core's north wall: the boiler room for the Superintendent only; the boiler hand-fired morning and night; coal in 6 November 1928; laundry by the rota; MANAGEMENT. No boiler hours are documented, so the notice gives none (B1_PUBLIC_CORE_DT2). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9617,10 +9621,14 @@
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T138" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F01_PUBLIC_CORE_DT1, F01_PUBLIC_NOTICE_native). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -10049,10 +10057,14 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T144" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (F01_SERVICE_CORE_DT1, F01_SERVICE_NOTICE_native). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -13653,10 +13665,14 @@
       </c>
       <c r="S190" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T190" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F02_PUBLIC_CORE_DT1). The landing and the public core share the one board. Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -14097,10 +14113,14 @@
       </c>
       <c r="S196" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T196" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F02_PUBLIC_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -14627,10 +14647,14 @@
       </c>
       <c r="S203" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T203" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (F02_SERVICE_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -18939,10 +18963,14 @@
       </c>
       <c r="S259" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T259" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F03_PUBLIC_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -19087,10 +19115,14 @@
       </c>
       <c r="S261" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T261" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (F03_SERVICE_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -19235,10 +19267,14 @@
       </c>
       <c r="S263" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T263" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F03_PUBLIC_CORE_DT1). The landing and the public core share the one board. Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -24071,10 +24107,14 @@
       </c>
       <c r="S327" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T327" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F04_PUBLIC_CORE_DT1). The landing and the public core share the one board. Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -24705,10 +24745,14 @@
       </c>
       <c r="S336" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T336" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F04_PUBLIC_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -25433,10 +25477,14 @@
       </c>
       <c r="S346" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T346" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (F04_SERVICE_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -31233,10 +31281,14 @@
       </c>
       <c r="S424" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T424" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T424" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F05_PUBLIC_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -31513,10 +31565,14 @@
       </c>
       <c r="S428" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T428" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T428" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (F05_SERVICE_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -36797,10 +36853,14 @@
       </c>
       <c r="S500" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T500" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T500" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (F06_PUBLIC_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -37011,10 +37071,14 @@
       </c>
       <c r="S503" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T503" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T503" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (F06_SERVICE_CORE_DT1). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -41311,10 +41375,14 @@
       </c>
       <c r="S561" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T561" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T561" s="2" t="inlineStr">
+        <is>
+          <t>The 1928 house rules on an oak-framed notice board (0.35 x 0.45 m, centre 1.5 m) on the public core's north wall beside the landing, clear of the C door and the stair: rents to Management, Apartment 5A, on the first; leaks, heat and repairs to the Superintendent, 3B; keep the stair and landings clear; quiet after ten o'clock; signed MANAGEMENT. The words are a shaded Label3D on the paper, so the lamp reads them. The board has no glass (the family has none); kraft tape crosses its top corner where the glass would be cracked (no sweep station frames it; same board as F01_PUBLIC_NOTICE_native). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -41595,10 +41663,14 @@
       </c>
       <c r="S565" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T565" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T565" s="2" t="inlineStr">
+        <is>
+          <t>The service notice, pinned in an oak frame on the service core's south wall above the landing, beside the brass floor plate: service stair for staff, trades and deliveries; coal and ash by the rear apron; the boiler fired by the Superintendent; keep the stair clear; MANAGEMENT. A shaded Label3D on the paper (ROOF_SERVICE_CORE_DT3). Verified at WIP 1acecafb (implementation/slice48): fabrication batch 0 failures (both notice boards captured natively, the words legible under the lamp); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206; upper furniture 488; upper lighting 0 failures; public doors 17 waypoints, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route 1 waypoint with its one failure (it stops one riser above the basement landing, identical at slice 47, 6d62caab); the eighteen-space core sweep 0 failures. The objects context inspector finds every frame on a real core wall face.</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -13817,10 +13817,14 @@
       </c>
       <c r="S192" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T192" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>2A's coir mat squared to the jamb (Mina keeps things exact); from the landing it reads beside 2C's worn mat and the two milk bottles waiting at the core (F02_WEST_HALL_OV, 2A_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -13965,10 +13969,14 @@
       </c>
       <c r="S194" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T194" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>The sealed 2D door's dust mat, new and unmarked, squared at the jamb; read from the hall against 2A's exact coir and 2C's worn mat beyond (F02_SOUTHWEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -14265,10 +14273,14 @@
       </c>
       <c r="S198" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T198" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>Looking down the east hall from the core: 2C's worn mat and milk at the core end, 2B's rag rug of selvedge scraps at the crossing end (F02_EAST_HALL_RV, F02_SERVICE_CROSSING_OV, 2B_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -18885,10 +18897,14 @@
       </c>
       <c r="S258" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T258" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the sealed door's clean dust mat is squared at the jamb on the hall side, and its one-line notice hangs at 1.5 m in the core notice-frame family (slice 48's Label3D form), both read from the hall (F02_SOUTHWEST_HALL_OV). The strip of brown paper over the letter slot is not made: the leaf has no slot owner to carry a decal. Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -19921,10 +19937,14 @@
       </c>
       <c r="S272" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T272" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="inlineStr">
+        <is>
+          <t>3A's coir mat dark with soil off Malcolm's boots (F03_WEST_HALL_OV, 3A_threshold_native); 3D's plain coir at the far end of the southwest hall reads from the same landing. Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -20069,10 +20089,14 @@
       </c>
       <c r="S274" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T274" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="inlineStr">
+        <is>
+          <t>3D's plain coir mat at the hall's door, read from the landing with 3A's soiled mat in the west hall (F03_SOUTHWEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -24325,10 +24349,14 @@
       </c>
       <c r="S330" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T330" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>4B's mat worn flat and dark where every boot lands (the player's door), beside 4C's ribbed rubber mat and two milk bottles at the core (F04_WEST_HALL_OV, 4B_threshold_native, 4C_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -24967,10 +24995,14 @@
       </c>
       <c r="S339" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T339" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>Down the east hall: 4C's ribbed rubber mat and milk pair at the core end, 4A's exact coir mat with the paper folded on it at the crossing end (F04_EAST_HALL_RV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -32157,10 +32189,14 @@
       </c>
       <c r="S436" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T436" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T436" s="2" t="inlineStr">
+        <is>
+          <t>5A's coir mat and 5B's with the morning paper folded on it, two households side by side in the one hall; 5C's paint-flecked mat at the core (F05_WEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -37605,10 +37641,14 @@
       </c>
       <c r="S510" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T510" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T510" s="2" t="inlineStr">
+        <is>
+          <t>6B's worn mat in the hall and 6C's coir mat with a string-tied parcel for the appraiser at the core (F06_WEST_HALL_OV, 6C_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -9695,10 +9695,14 @@
       </c>
       <c r="S139" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T139" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a small canvas of a dusk sky over a field with one post, hung on the wall above the arrival landing (F01_PUBLIC_CORE_RV, F01_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10131,10 +10135,14 @@
       </c>
       <c r="S145" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T145" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed ruled document, wordless, hung on the wall above the arrival landing (F01_SERVICE_CORE_RV, F01_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -13739,10 +13747,14 @@
       </c>
       <c r="S191" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T191" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the landing shares its public core's flights and piece; Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight (F02_LANDING_RV). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -14195,10 +14207,14 @@
       </c>
       <c r="S197" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T197" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a canvas of a pale sky over an ochre field with one green tree, hung on the wall above the arrival landing (F02_PUBLIC_CORE_RV, F02_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -14733,10 +14749,14 @@
       </c>
       <c r="S204" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T204" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed navy-toned photograph, hung on the wall above the arrival landing (F02_SERVICE_CORE_RV, F02_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -19053,10 +19073,14 @@
       </c>
       <c r="S260" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T260" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a sepia photograph in a dark frame, hung on the wall above the arrival landing (F03_PUBLIC_CORE_RV, F03_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -19205,10 +19229,14 @@
       </c>
       <c r="S262" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T262" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed brown-toned photograph, hung on the wall above the arrival landing (F03_SERVICE_CORE_RV, F03_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -19357,10 +19385,14 @@
       </c>
       <c r="S264" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T264" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the landing shares its public core's flights and piece; Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight (F03_LANDING_RV). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -24205,10 +24237,14 @@
       </c>
       <c r="S328" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T328" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the landing shares its public core's flights and piece; Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight (F04_LANDING_RV). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -24847,10 +24883,14 @@
       </c>
       <c r="S337" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T337" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a dark interior canvas, a lit doorway and a lamp, hung on the wall above the arrival landing (F04_PUBLIC_CORE_RV, F04_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -25583,10 +25623,14 @@
       </c>
       <c r="S347" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T347" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed green-toned photograph, hung on the wall above the arrival landing (F04_SERVICE_CORE_RV, F04_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -31387,10 +31431,14 @@
       </c>
       <c r="S425" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T425" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T425" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a long canvas of a pale sky, grey water and a green shore, hung on the wall above the arrival landing (F05_PUBLIC_CORE_RV, F05_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -31671,10 +31719,14 @@
       </c>
       <c r="S429" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T429" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T429" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed ruled certificate, wordless, hung on the wall above the arrival landing (F05_SERVICE_CORE_RV, F05_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -36963,10 +37015,14 @@
       </c>
       <c r="S501" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T501" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T501" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, the prospectus roof-garden plate, hung on the wall above the arrival landing (F06_PUBLIC_CORE_RV, F06_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -37029,10 +37085,14 @@
       </c>
       <c r="S502" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T502" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T502" s="2" t="inlineStr">
+        <is>
+          <t>The prospectus roof-garden plate: a sepia drawing of the roof garden with its figures as silhouettes (a pergola, planting, people at the parapet), framed at 1.6 m on the wall above the F06 arrival landing below the roof flight, in plain paint and print finishes (no gilt tooling, no lettering). Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -37181,10 +37241,14 @@
       </c>
       <c r="S504" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T504" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T504" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed teal-toned photograph, hung on the wall above the arrival landing (F06_SERVICE_CORE_RV, F06_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -41489,10 +41553,14 @@
       </c>
       <c r="S562" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T562" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T562" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a night canvas, a few stars and a low moon over the parapet, hung on the wall above the arrival landing (ROOF_PUBLIC_CORE_RV, ROOF_PUBLIC_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -41777,10 +41845,14 @@
       </c>
       <c r="S566" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T566" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T566" s="2" t="inlineStr">
+        <is>
+          <t>Partial: Every honed tread of this core's flights is dished just behind the nosing on the walking line, deepest at the centre and zero at every edge (visual only: physics keeps the full box), read against the lamp in the reverse view up the flight; and the landing's one piece of its own, a framed burgundy-toned photograph, hung on the wall above the arrival landing (ROOF_SERVICE_CORE_RV, ROOF_SERVICE_CORE_DT1). Rail gold at hand height and paint rubbed at the turn are not yet made. Verified at WIP 14fec84e (implementation/slice50): fabrication batch 0 failures (four landing pieces captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, the honed stair material check (294 stair surfaces), the blockout test, stair ironwork, stair direction (36/36), public doors 17, the remaining upper transfers 28, the basement route 88 and public furnishings 29, all 0 failures; the ground core transfer route's one failure is pre-existing. Two of the three core sweeps (12 spaces) report 0 failures at the WIP; the third (the B1 public core, the F05 service core, both F06 cores and both roof cores) was rerun at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and reports 0 failures (implementation/slice52b, committed with slice 52).</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -24085,10 +24085,14 @@
       </c>
       <c r="S326" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T326" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>Partial: on the core side of the sealed 3C door, an unworn dust mat squared at the jamb and the one-line notice at 1.5 m in the core notice-frame family (3C_threshold_native). The strip of brown paper over the letter slot is not made: the leaf has no slot owner to carry a decal. Verified at WIP 0bac8f87 (implementation/slice51): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, public doors 17, the remaining upper transfers 28 and the apartment door route 45, all 0 failures; the resident key route (86 waypoints, long runner) and the four-space sweep (F03 public core, F05 service crossing, F05 west and east halls) ran at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and both report 0 failures. The fabrication batch captured the 3C threshold and the 5D soot fan natively; its one failure is the capture harness finding no clear standing camera station for the aerial wire in the 1.06 m hall, so the hall sweep's views carry that evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -32389,10 +32393,14 @@
       </c>
       <c r="S438" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T438" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T438" s="2" t="inlineStr">
+        <is>
+          <t>Cal's aerial lead along the hall at 2.0 m on four porcelain insulators, sagging between them, rising to the cornice at the core end and turning into a drilled hole beside 5B's door (F05_WEST_HALL_OV). Verified at WIP 0bac8f87 (implementation/slice51): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, public doors 17, the remaining upper transfers 28 and the apartment door route 45, all 0 failures; the resident key route (86 waypoints, long runner) and the four-space sweep (F03 public core, F05 service crossing, F05 west and east halls) ran at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and both report 0 failures. The fabrication batch captured the 3C threshold and the 5D soot fan natively; its one failure is the capture harness finding no clear standing camera station for the aerial wire in the 1.06 m hall, so the hall sweep's views carry that evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -36805,10 +36813,14 @@
       </c>
       <c r="S498" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T498" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T498" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the soot ghost, stepped bands of soot 0.8 m wide at the top, up the plaster above the replaced door's head on the crossing side, and the same one-line notice beside it (5D_soot_fan_native, F05_SERVICE_CROSSING_TH). The replacement leaf's fresher paint and the scorch at the frame head are not made: the fitted door family has no replacement finish. Verified at WIP 0bac8f87 (implementation/slice51): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, public doors 17, the remaining upper transfers 28 and the apartment door route 45, all 0 failures; the resident key route (86 waypoints, long runner) and the four-space sweep (F03 public core, F05 service crossing, F05 west and east halls) ran at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and both report 0 failures. The fabrication batch captured the 3C threshold and the 5D soot fan natively; its one failure is the capture harness finding no clear standing camera station for the aerial wire in the 1.06 m hall, so the hall sweep's views carry that evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11633,10 +11633,14 @@
       <c r="R164" s="2" t="inlineStr"/>
       <c r="S164" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T164" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F01_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F01_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -13525,10 +13529,14 @@
       <c r="R188" s="2" t="inlineStr"/>
       <c r="S188" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T188" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F01_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F01_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -13903,10 +13911,14 @@
       </c>
       <c r="S193" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T193" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_WEST_HALL_RV, F02_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -14055,10 +14067,14 @@
       </c>
       <c r="S195" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T195" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_SOUTHWEST_HALL_RV, F02_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -14363,10 +14379,14 @@
       </c>
       <c r="S199" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T199" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_EAST_HALL_RV, F02_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -16001,10 +16021,14 @@
       <c r="R220" s="2" t="inlineStr"/>
       <c r="S220" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T220" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -17455,10 +17479,14 @@
       <c r="R239" s="2" t="inlineStr"/>
       <c r="S239" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T239" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -18485,10 +18513,14 @@
       <c r="R252" s="2" t="inlineStr"/>
       <c r="S252" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T252" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -19537,10 +19569,14 @@
       </c>
       <c r="S266" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T266" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_EAST_HALL_RV, F03_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -20043,10 +20079,14 @@
       </c>
       <c r="S273" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T273" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_WEST_HALL_RV, F03_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -20195,10 +20235,14 @@
       </c>
       <c r="S275" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T275" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_SOUTHWEST_HALL_RV, F03_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -21357,10 +21401,14 @@
       <c r="R290" s="2" t="inlineStr"/>
       <c r="S290" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T290" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -22651,10 +22699,14 @@
       <c r="R307" s="2" t="inlineStr"/>
       <c r="S307" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T307" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -23661,10 +23713,14 @@
       <c r="R320" s="2" t="inlineStr"/>
       <c r="S320" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T320" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -24463,10 +24519,14 @@
       </c>
       <c r="S331" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T331" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_WEST_HALL_RV, F04_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -24673,10 +24733,14 @@
       </c>
       <c r="S334" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T334" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_SOUTHWEST_HALL_RV, F04_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -25113,10 +25177,14 @@
       </c>
       <c r="S340" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T340" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_EAST_HALL_RV, F04_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -26871,10 +26939,14 @@
       <c r="R363" s="2" t="inlineStr"/>
       <c r="S363" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T363" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -28219,10 +28291,14 @@
       <c r="R381" s="2" t="inlineStr"/>
       <c r="S381" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T381" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -29769,10 +29845,14 @@
       <c r="R402" s="2" t="inlineStr"/>
       <c r="S402" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T402" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -31015,10 +31095,14 @@
       <c r="R419" s="2" t="inlineStr"/>
       <c r="S419" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T419" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T419" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -31953,10 +32037,14 @@
       </c>
       <c r="S432" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T432" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T432" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F05_EAST_HALL_RV, F05_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -32319,10 +32407,14 @@
       </c>
       <c r="S437" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T437" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T437" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F05_WEST_HALL_RV, F05_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -33589,10 +33681,14 @@
       <c r="R454" s="2" t="inlineStr"/>
       <c r="S454" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T454" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T454" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -35123,10 +35219,14 @@
       <c r="R475" s="2" t="inlineStr"/>
       <c r="S475" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T475" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T475" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -36311,10 +36411,14 @@
       <c r="R491" s="2" t="inlineStr"/>
       <c r="S491" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T491" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T491" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -37483,10 +37587,14 @@
       </c>
       <c r="S507" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T507" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T507" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F06_EAST_HALL_RV, F06_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -37791,10 +37899,14 @@
       </c>
       <c r="S511" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T511" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T511" s="2" t="inlineStr">
+        <is>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F06_WEST_HALL_RV, F06_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -38719,10 +38831,14 @@
       <c r="R523" s="2" t="inlineStr"/>
       <c r="S523" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T523" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T523" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -39969,10 +40085,14 @@
       <c r="R540" s="2" t="inlineStr"/>
       <c r="S540" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T540" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T540" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -41067,10 +41187,14 @@
       <c r="R555" s="2" t="inlineStr"/>
       <c r="S555" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T555" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T555" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6717,10 +6717,14 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T94" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the stool's floor cover becomes a black rubber mat worn to a hollow under the proprietor's feet (fitted_stool); the half-punched punchboard on the counter is the fitted family's own (punchboard). The tile under the mat is not dished: the mat covers it. Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6841,10 +6845,14 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T96" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>The booth's stock, every piece seated on its board: four string-tied bundles of papers, three fanned runs of magazines, cigar boxes with one lid stood open on its cigars, three tobacco tins, and four stacks of papers under wordless grey mastheads; the cigar case shows its cigars (shop_news_cigars_SITE_SHOP_IN0_NEWS_CIGARS, rear_shelves). Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6089,10 +6089,14 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T84" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>The seven wire-bail tins in three sizes, two lids dented and paint run down two, each with a wordless paper label band and a colour stripe; one drawer of the wall stands 0.14 m open on its rail (paint_tins, drawer_wall, shop_hardware_paint_SITE_SHOP_IN1_HARDWARE_PAINT). Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -7365,10 +7365,14 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T104" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>One plate on the portrait rail is a building: a procedural architectural plate, a facade in sepia with its windows in rows, among the sitters (portrait3, portrait_context). Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7431,10 +7435,14 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T105" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>Film stock in three sizes, some turned and one stood on end, every lid with a wordless printed band; a box camera, a closed folding camera and a brass portrait lens under the counter's case glass (rear_shelf_wall, left_column, glazed_tier, shop_photo_supplies_SITE_SHOP_IN0_PHOTO_SUPPLIES, IN1). Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -5829,10 +5829,14 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T80" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the second-hand fire safe carries a blank gold-leaf cartouche and pinstripe (safe_and_padlocks). The roll of picks unrolled on the bench is not made. Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5887,10 +5891,14 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T81" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>The register lies open on the counter, a column of figures as ink strokes on blank rules, a pencil on a string (copy_counter, shop_keys_cut_SITE_SHOP_IN0_KEYS_CUT). Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5953,10 +5961,14 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T82" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the key board's blanks vary by row (bow form, blade length, bitting), the fourth row hangs empty and six more pegs are bare; of the four lock cases one stands open, its cover on the cloth with its screws (key_board, loose_locks, shop_keys_cut_SITE_SHOP_IN1_KEYS_CUT). The table's blocks are not yet picks and blanks. Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -7191,10 +7191,14 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T101" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the open-back set on the bench has a wordless dial with its pointer at the top of the band and a cone speaker on its own foot corded to it (alignment_bench, original_instruments). The low open-channel hiss is not added: the shop ambience owner is unchanged. Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7315,10 +7319,14 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T103" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>Valves are shouldered smoky envelopes on Bakelite bases with a silvered getter flash, the stored ones standing in slatted tube racks; a moving-coil meter and a soldering iron in its stand join the bench; the black floor ring is black rubber-covered wire wound on its own wooden reel (valve_rank, rack_front, upper_valve_rank, two_fixed_reels, shop_radio_service_SITE_SHOP_IN0_RADIO_SERVICE, storm_shop_radio_service_floor_0). Verified at slice 57's WIP 260849e8 (implementation/slice57b), which carries slices 55 and 56 unchanged: the fabrication batch's seven families (photo stock 467, photo counter 148, photo portraits 361, locksmith fittings 943, radio battery 247, radio display 164 and radio wire 126 checks) report 0 failures; the radio apparatus (346), radio bench (155), radio stock (735), radio receiving (586) and photo receiving (792) suites report 0 failures; the city sweep's 130 views report 0 failures. The news receiving suite's one failure there, its keyboard station's standing capsule, is identical at slice 52's WIP 3f3f0d75 before any of these shop slices (receipt base53__news_receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11747,10 +11747,14 @@
       </c>
       <c r="S165" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T165" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn's own brass grab rail on two roses, fixed to the 1A shower's receptor wall at 0.82 m (1A_bath_rail_native). The closed curtain hides it from every sweep station, so it reads only from inside the receptor. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -13643,10 +13647,14 @@
       </c>
       <c r="S189" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T189" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>Partial: a huckaback towel pegged over a cord across the 1D bath window head, the night nurse sleeping by day (1D_window_towel_native, F01_D_BATH_DT2). The soaking bowl of collars and cuffs at the basin is not made. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -31407,10 +31415,14 @@
       </c>
       <c r="S423" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T423" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T423" s="2" t="inlineStr">
+        <is>
+          <t>Two shelves of lost property in 4D's study, nine guests' leavings each tagged with a blank card on a string (4D_lost_shelves_native, F04_D_STUDY_OV); a teleported capture, as the row asks. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -38633,10 +38645,14 @@
       </c>
       <c r="S520" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T520" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T520" s="2" t="inlineStr">
+        <is>
+          <t>Sacha's light table on the prep cabinet beside the toaster: a frosted plate in a timber box with a strip of negatives and a loupe on it, the lamp inside unlit (6A_light_table_native, F06_A_KITCHEN_DT1). Slice 58 named it 6A_light_box, an id slice 38's surface-stock box already owned, and the runtime refused the world; slice 67 renamed it 6A_light_table, moved it to the cabinet's clear front off the plate and dropped its flex. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -703,10 +703,14 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>The laundry rota by the laundry door in the notice-frame family, its words a Label3D the lamp reads, and high on the north wall the brass signal outlet painted over, its cloth lead cut short (B1_painted_outlet_native, B1_LAUNDRY_OV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1429,10 +1433,14 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>A twisted cloth pair on porcelain cleats along the electrical room's wall to the fuse panel, and Omar's shelf of cartridges and chalk (B1_ELECTRICAL_OV, B1_ELECTRICAL_DT1). The fabrication capture found no clear standing station in the narrow room; the sweep views carry it. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1759,10 +1767,14 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the coal shovel leaning by the heap, its pan on the floor and grip on the whitewash (B1_coal_shovel_native), and the dust fanned from the chute mouth (slice 60). The heap's cut face and the chalk tally on a bunker board are not made: no bunker board exists. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1083,10 +1083,14 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Partial: coal dust trodden down the boiler approach, darkening toward the fire door (a projected decal; no sweep station frames it clearly). The fire bucket on its hook is not made: the approach is a 1.2 m route. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1223,10 +1227,14 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Omar's chalked log on the water column: tally groups, ticks and strokes in a working hand, no numerals, a projected decal mounted with the world at 2c25e683. The sweep's detail stations face the boiler front, not the column; a framed capture is open. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1565,10 +1573,14 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>The door's sweep scuffed into a quarter ring on the recess floor and a cartridge fuse dropped in the corner (slice 59) (B1_dropped_cartridge_native). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2171,10 +2183,14 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Coal dust on the three lowest service-stair treads, a projected decal mounted with the world at 2c25e683 (positional_wear.json, 0 refusals). No sweep station frames those treads; a framed capture is open. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -11706,7 +11706,7 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F01_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F01_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F01_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F01_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F01_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F01_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F01_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F01_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="T220" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="T239" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="T252" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F02_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F02_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="T290" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22780,7 @@
       </c>
       <c r="T307" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -23794,7 +23794,7 @@
       </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F03_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F03_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -27020,7 +27020,7 @@
       </c>
       <c r="T363" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -28372,7 +28372,7 @@
       </c>
       <c r="T381" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -29926,7 +29926,7 @@
       </c>
       <c r="T402" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -31176,7 +31176,7 @@
       </c>
       <c r="T419" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F04_D_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F04_D_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -33766,7 +33766,7 @@
       </c>
       <c r="T454" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -35304,7 +35304,7 @@
       </c>
       <c r="T475" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -36496,7 +36496,7 @@
       </c>
       <c r="T491" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F05_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F05_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="T498" s="2" t="inlineStr">
         <is>
-          <t>Partial: the soot ghost, stepped bands of soot 0.8 m wide at the top, up the plaster above the replaced door's head on the crossing side, and the same one-line notice beside it (5D_soot_fan_native, F05_SERVICE_CROSSING_TH). The replacement leaf's fresher paint and the scorch at the frame head are not made: the fitted door family has no replacement finish. Verified at WIP 0bac8f87 (implementation/slice51): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, public doors 17, the remaining upper transfers 28 and the apartment door route 45, all 0 failures; the resident key route (86 waypoints, long runner) and the four-space sweep (F03 public core, F05 service crossing, F05 west and east halls) ran at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and both report 0 failures. The fabrication batch captured the 3C threshold and the 5D soot fan natively; its one failure is the capture harness finding no clear standing camera station for the aerial wire in the 1.06 m hall, so the hall sweep's views carry that evidence.</t>
+          <t>Partial: the soot ghost, stepped bands of soot 0.8 m wide at the top, up the plaster above the replaced door's head on the crossing side, and the same one-line notice beside it (5D_soot_fan_native, F05_SERVICE_CROSSING_TH). The replacement leaf's fresher paint and the scorch at the frame head are not made: the fitted door family has no replacement finish. Verified at WIP 0bac8f87 (implementation/slice51): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks, public doors 17, the remaining upper transfers 28 and the apartment door route 45, all 0 failures; the resident key route (86 waypoints, long runner) and the four-space sweep (F03 public core, F05 service crossing, F05 west and east halls) ran at slice 52's WIP 3f3f0d75, which carries this slice unchanged, and both report 0 failures. The fabrication batch captured the 3C threshold and the 5D soot fan natively; its one failure is the capture harness finding no clear standing camera station for the aerial wire in the 1.06 m hall, so the hall sweep's views carry that evidence. Slice 61 replaces the stepped soot bands with a soft projected fan licking up from the door head (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -38920,7 +38920,7 @@
       </c>
       <c r="T523" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_A_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_A_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -40174,7 +40174,7 @@
       </c>
       <c r="T540" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_B_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_B_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>
@@ -41276,7 +41276,7 @@
       </c>
       <c r="T555" s="2" t="inlineStr">
         <is>
-          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>Partial: a darkened grout-and-water ring round the shower receptor's lip and the mop-shadow corner farthest from the door, both soft projected wear (F06_C_BATH_OV; a frame difference against slice 47's view isolates the ring at the receptor's base). Paint lifted below the register is not made: the bath's vent register hangs from its duct at 2.6 m with no wall below it (F06_C_BATH_DT1). The water line under the curtain hem follows in slice 61. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 61 adds the water line on the floor under the curtain hem, a ragged damp band with a darker drying edge, mounted with the world at 2c25e683 (implementation/slice67); a frame difference against slice 52's view picks it out along the hem, faint at production light.</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6959,10 +6959,14 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T97" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>The jeweller's beam balance in its glazed case, the loupe on a cord and the pledge ledger on the counter, from the pawn fittings family (balance, ledger_loupe). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7017,10 +7021,14 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T98" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>A wedding ring half out of a small envelope on the window deck between the watch tray and the field glasses (window_watch). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7083,10 +7091,14 @@
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T99" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the safe's painted name panel above its dial, blank, an enamelled field inside a gold line. The two bulbs in the counter cage remain the cell's sphere globes. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -9561,10 +9561,14 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T136" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>Both reading-room bookcases hold their books in runs of varied length with gaps between, short piles lying flat, and a top shelf of bound magazine volumes in one cloth with blank bands where the years would be lettered (build_reading_furniture.py; reading furniture 25 waypoints, 0 failures). The sweep shows the two cases only small and dark at the room's far end (F01_COMMON_B_RV); a framed capture is open. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6257,10 +6257,14 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T86" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>The register lies open on the lectern at the day's page: blank rules and one signature stroke (book). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6381,10 +6385,14 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T88" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>The chair rows stay arranged but two chairs sit a few degrees off their marks and one is pulled back where someone stood; the alcove drapes were already pleated cloth (SITE_SHOP_IN0_FUNERAL_PARLOUR_fitted). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6501,10 +6509,14 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T90" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>The third stool's vinyl top is worn through to the cord (storm_shop_luncheonette_floor_0_fitted). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -3937,10 +3937,14 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>Election broadsides pasted on both street-end hoardings: a portrait silhouette over a star inside a printed border, no lettering. The hoardings stand at the street's far ends and no city station frames them; a framed capture is open. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4123,10 +4127,14 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the pavement's ground marks feather out to their quad edges, so no stain ends in a hard dark rectangle (city sweep route stations). They are not yet clipped to the slab joints. Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -19611,10 +19611,14 @@
       </c>
       <c r="S265" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T265" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
+          <t>No apartment door opens on the east hall itself; its thresholds are 3B's ribbed rubber mat at the service crossing (new) and the sealed 3C door's dust mat at the core, read with 3A's and 3D's from the landing (3B_threshold_native, F03_EAST_HALL_RV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -24775,10 +24779,14 @@
       </c>
       <c r="S333" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T333" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>The 4D short-let's new coir mat with a handbill pushed under the door that nobody picked up, read from the landing with 4B's worn mat (4D_threshold_native, F04_SOUTHWEST_HALL_OV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -28173,10 +28181,14 @@
       </c>
       <c r="S378" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T378" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>A bound jute runner centred along the alcove approach, worn through to the boards where the turn from the hall meets the way to the alcove, its strands loose across the hole (4B_alcove_runner_native, F04_B_ALCOVE_APPROACH_OV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -32083,10 +32095,14 @@
       </c>
       <c r="S431" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T431" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T431" s="2" t="inlineStr">
+        <is>
+          <t>No apartment door opens on the east hall; at its ends 5C's paint-flecked mat at the core and the sealed 5D's unworn dust mat at the crossing (new), with 5A's and 5B's read from the landing (5D_threshold_native, F05_EAST_HALL_RV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -35845,10 +35861,14 @@
       </c>
       <c r="S482" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T482" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T482" s="2" t="inlineStr">
+        <is>
+          <t>Iris's paint rag folded over 5C's radiator to dry, mid-length so the supply valve and the air vent stay in reach, oxblood paint on its fall; visual only (F05_C_MAIN_DT3). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -37633,10 +37653,14 @@
       </c>
       <c r="S506" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T506" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T506" s="2" t="inlineStr">
+        <is>
+          <t>No apartment door opens on the east hall; at its ends 6C's coir mat and the appraiser's parcel at the core and the landlord's padlocked storage at the crossing; 6A's coir mat (new) and 6B's worn mat read from the landing (6A_threshold_native, F06_EAST_HALL_RV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -41657,10 +41681,14 @@
       </c>
       <c r="S560" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T560" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T560" s="2" t="inlineStr">
+        <is>
+          <t>A galvanised hasp across the latch stile and casing at 1.2 m with its staple and a black padlock, and the old brass escutcheon plate above at 1.5 m, on the landlord's storage door's crossing face; the leaf stays locked (F06_SERVICE_CROSSING_TH, F06_EAST_HALL_RV). Verified at slice 67's WIP 2c25e683 (implementation/slice67), which carries slices 58 to 66 with slice 67's fixes: from slice 58 the world refused to compose (slice 58's light box reused an id slice 38's surface stock owned) until slice 67 renamed it. At 2c25e683 the fabrication batch's ten families (12,295 checks) report one failure, the capture harness finding no clear camera station for the B1 cleat run; apartment batch 204 on the long runner, as before; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, 0 failures; the remaining transfers, apartment door, first upper hall, 4B door and rear wing A routes, the basement route (88), basement ground, boiler service, reading furniture, shop seating, funeral fittings, completion heating, radiator ties, ventilation, door casings (107 openings), hardware drawers (1,309 checks), street boundary, passage visibility, commensal, the street boundary route and the resident key route (86 waypoints, long runner), all 0 failures; twelve sweeps (55 spaces) and the city sweep's 130 views, 0 failures. The coal delivery route's stop at the lobby's inner door and the Vantry gateway suite's five kiosk-count failures are identical at slice 57's 260849e8 (base58), and the news receiving station failure is identical before slice 53.</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6137,12 +6137,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>The seven wire-bail tins in three sizes, two lids dented and paint run down two, each with a wordless paper label band and a colour stripe; one drawer of the wall stands 0.14 m open on its rail (paint_tins, drawer_wall, shop_hardware_paint_SITE_SHOP_IN1_HARDWARE_PAINT). Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies.</t>
+          <t>The seven wire-bail tins in three sizes, two lids dented and paint run down two, each with a wordless paper label band and a colour stripe; one drawer of the wall stands 0.14 m open on its rail (paint_tins, drawer_wall, shop_hardware_paint_SITE_SHOP_IN1_HARDWARE_PAINT). Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies. Slice 67 teaches the drawer suite the open drawer; hardware drawers pass, 1,309 checks, 0 failures at 2c25e683 (implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>Partial: the stool's floor cover becomes a black rubber mat worn to a hollow under the proprietor's feet (fitted_stool); the half-punched punchboard on the counter is the fitted family's own (punchboard). The tile under the mat is not dished: the mat covers it. Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies.</t>
+          <t>Partial: the stool's floor cover becomes a black rubber mat worn to a hollow under the proprietor's feet (fitted_stool); the half-punched punchboard on the counter is the fitted family's own (punchboard). The tile under the mat is not dished: the mat covers it. Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies. Slice 67 restores the stool's datum (the worn mat's top is the original height, worn to its pale canvas ply on the counter side) and the news fittings pass, 670 checks, 0 failures at 2c25e683 (implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>The booth's stock, every piece seated on its board: four string-tied bundles of papers, three fanned runs of magazines, cigar boxes with one lid stood open on its cigars, three tobacco tins, and four stacks of papers under wordless grey mastheads; the cigar case shows its cigars (shop_news_cigars_SITE_SHOP_IN0_NEWS_CIGARS, rear_shelves). Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies.</t>
+          <t>The booth's stock, every piece seated on its board: four string-tied bundles of papers, three fanned runs of magazines, cigar boxes with one lid stood open on its cigars, three tobacco tins, and four stacks of papers under wordless grey mastheads; the cigar case shows its cigars (shop_news_cigars_SITE_SHOP_IN0_NEWS_CIGARS, rear_shelves). Run at slice 54's WIP 22b1aa9a (implementation/slice54b), which carries slice 53 unchanged: the city sweep's 130 views report 0 failures and the IN0/IN1 stations show the shops. At that WIP the news fittings module reports 4 failures (slice 53 sank the worn hollow below the datum the stool's four feet stand on) and the hardware drawer suite 1 (its face probe did not know the open drawer). Slice 67 fixes both; these rows are upgraded when it verifies. Slice 67 restores the stool's datum (the worn mat's top is the original height, worn to its pale canvas ply on the counter side) and the news fittings pass, 670 checks, 0 failures at 2c25e683 (implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -14023,12 +14023,12 @@
       </c>
       <c r="S193" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T193" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_WEST_HALL_RV, F02_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_WEST_HALL_RV, F02_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="S195" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T195" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_SOUTHWEST_HALL_RV, F02_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_SOUTHWEST_HALL_RV, F02_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -14491,12 +14491,12 @@
       </c>
       <c r="S199" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T199" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_EAST_HALL_RV, F02_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F02_EAST_HALL_RV, F02_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -19685,12 +19685,12 @@
       </c>
       <c r="S266" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T266" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_EAST_HALL_RV, F03_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_EAST_HALL_RV, F03_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -20195,12 +20195,12 @@
       </c>
       <c r="S273" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T273" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_WEST_HALL_RV, F03_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_WEST_HALL_RV, F03_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="S275" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T275" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_SOUTHWEST_HALL_RV, F03_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F03_SOUTHWEST_HALL_RV, F03_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -24635,12 +24635,12 @@
       </c>
       <c r="S331" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T331" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_WEST_HALL_RV, F04_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_WEST_HALL_RV, F04_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -24853,12 +24853,12 @@
       </c>
       <c r="S334" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T334" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_SOUTHWEST_HALL_RV, F04_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_SOUTHWEST_HALL_RV, F04_SOUTHWEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -25297,12 +25297,12 @@
       </c>
       <c r="S340" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T340" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_EAST_HALL_RV, F04_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F04_EAST_HALL_RV, F04_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -32169,12 +32169,12 @@
       </c>
       <c r="S432" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T432" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F05_EAST_HALL_RV, F05_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F05_EAST_HALL_RV, F05_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -32539,12 +32539,12 @@
       </c>
       <c r="S437" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T437" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F05_WEST_HALL_RV, F05_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F05_WEST_HALL_RV, F05_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -37727,12 +37727,12 @@
       </c>
       <c r="S507" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T507" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F06_EAST_HALL_RV, F06_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F06_EAST_HALL_RV, F06_EAST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>
@@ -38039,12 +38039,12 @@
       </c>
       <c r="S511" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T511" s="2" t="inlineStr">
         <is>
-          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F06_WEST_HALL_RV, F06_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering.</t>
+          <t>The dulled walking line down the hall's middle, foot scuffs on the floor at each apartment door, the mop-shadow corner farthest from the core and the porter's trolley rub on the long wall at 0.6 m, 0.9 m in from the core (F06_WEST_HALL_RV, F06_WEST_HALL_OV); the scuffs sit on the actual door positions. The marks render (a frame difference against slice 49's views traces the path down the centre and the scuffs at the doors) but read faintly at production light; strengthening them is open. Verified at WIP 3f3f0d75 (implementation/slice52): apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both unchanged; upper lighting 9,257 checks and public doors 17, both 0 failures; the first bath sweep (six baths) 0 failures; the remaining twelve baths, the thirteen upper halls and slice 50's third core group were rerun at the same WIP in five sweeps, all 0 failures (implementation/slice52b); four earlier sweep runs that ran at another WIP are superseded and not cited. The decals are projected (Godot Decal nodes) from game/data/orison_v2/positional_wear.json onto the inherited finishes: no collision, no owner, no lettering. Slice 67 strengthens the walking line, door scuffs and trolley rub to read at production light (verified at 2c25e683, implementation/slice67).</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -9255,10 +9255,14 @@
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T131" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>Partial: two boxes overfull (2C, 4D), their letters drawn into the window cards, and two doors ajar on a letter (1D, 5B); the mail bank suite passes. No sweep station frames the bank closely enough to read its eighteen windows; a close capture is open. Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -10609,10 +10613,14 @@
       </c>
       <c r="S150" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T150" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn's corrected notice pinned inside 1A's entry leaf at 1.5 m, clear of the knob: a sheet struck through in red pencil with a correction slip pasted over it, no lettering; the leaf's opener reads the record's leaf_notice (F01_A_VESTIBULE_RV, crops/1A_corrected_notice). Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -42483,10 +42491,14 @@
       </c>
       <c r="S571" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T571" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T571" s="2" t="inlineStr">
+        <is>
+          <t>The house tank's body takes the tank-staves finish: upright timber staves where the review saw brick, on its timber legs and cradle (ROOF_DECK_WEST_DT2, crops/tank_staves). Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6071,10 +6071,14 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T83" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the brass counter bell and the night-service card (Label3D: NIGHT SERVICE RING BELL STOP) at the counter's north end read in the service-counter capture (crops/hardware_bell_card). The open box of carbon transmitter capsules sits on the north rack's third shelf at the counter end and passes the stock checks, but no capture frames it. Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6463,10 +6463,14 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T89" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>The menu board in three columns of white push-in letters (slice 70, Label3D), two sugar shakers and a jar of pickled eggs in the cell's own glass on the counter (slice 71), under the diner overhead family's ceiling fan (menu_face, fan_canopy, crops/diner_shakers_eggs). Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1717,10 +1717,14 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>The toolboard is a shadow board: a painted outline behind every tool and one outline empty on its peg, the screwdriver out on a job (b1_toolboard_native, crops/toolboard_silhouettes). Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -901,10 +901,14 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>The nook's reader: a book left open face down on the north seat's cushion, its covers tented over the spine, beside the mug and the pile on the table; built in the cushion's own assembly so the table's sixty retained volumes stay as they were (B1_NOOK_LAMP_context, crops/nook_tented_book). Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -5683,10 +5683,14 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T77" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>Already present in the cobbler fittings family and captured at 088f987a: the slanted rack of iron lasts and shoes on the party wall and the low waiting seat by the door (last_rack, waiting_seat). Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5807,10 +5811,14 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T79" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the floor's dust is a warm leather dust instead of near-black and the dark pairs are brown leather with form (floor_dust, last_rack, shoe_rack). The red cube, the second cage bulb over the bench and the ladder are not done. Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -5493,10 +5493,14 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T74" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>The ticket halves on the wire in four ages of paper, fresh to a year old, and the top parcel row the oldest, its wrapping darker (tickets, parcel_wall); tinted catalogue paper keys. Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1857,10 +1857,14 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>The chute's lower lip rests on a timber bearer laid across a boarded bunker round the heap: side walls of four horizontal boards from the south wall, a front board gate in slotted posts worked down to two boards with the lifted pair standing against the wall, in coal-dusted dark wood (B1_COAL_ROOM_OV, B1_COAL_ROOM_DT2, coal_bunker, delivery_chute_and_bunker). The coal delivery route predated the vestibule leaves and stopped at the inner door; it now opens both, and the coal heap suite runs end to end. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1919,10 +1923,14 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Partial: the heap is the fabricated mound (coal_heap.glb with collision on its own slope; all fourteen old heap boxes retired), now held in slice 76's boarded bunker. Grime on the whitewash beyond slice 60's chute fan is not done. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -835,10 +835,14 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>The laundry's water, slices 77 and 78. The washers: cold and hot mains out of the west wall through flanges, on clips above the hanging belt, a drop and brass bib cock at each machine with a rubber hose to its own fill cock, and a cast-iron floor gully taking each drain hose (washer_supply). The rinse tubs: cold and hot out of the west wet stack's face to a pair of long-reach bibs over each tub's back rim, and a cast-iron waste taking both brass drain tails back into the stack (rinse_taps, B1_LAUNDRY views). The context inspector now treats a solid riser's faces as walls. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -9225,10 +9225,14 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T130" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>The night watch's kettle: a cast-iron gas ring with a cream enamel kettle on a deal shelf on iron brackets, on the wall the watch room shares with the lobby, fed by a rubber tube from a brass cock on a gas pipe out of the wall (F01_watch_kettle_native, watch_kettle); and the tour card on the north wall near the key guard, its words a Label3D naming the patrol boxes (F01_WATCH views). Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -9299,12 +9299,12 @@
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>Partial: two boxes overfull (2C, 4D), their letters drawn into the window cards, and two doors ajar on a letter (1D, 5B); the mail bank suite passes. No sweep station frames the bank closely enough to read its eighteen windows; a close capture is open. Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline.</t>
+          <t>Partial: two boxes overfull (2C, 4D), their letters drawn into the window cards, and two doors ajar on a letter (1D, 5B); the mail bank suite passes. No sweep station frames the bank closely enough to read its eighteen windows; a close capture is open. Verified at slice 75's WIP 088f987a (implementation/slice68), which carries slices 68 to 75. At 088f987a the fabrication batch's domestic objects and reading nook (11,108 checks) report 0 failures; the mail bank suite passes; wall mounts, roof drainage, public doors (17 waypoints), door casings (107 openings), the apartment door route (45), the golden repair route (94), hardware stock (1,418 checks), hardware drawers (1,309), diner overhead (99), diner counter (160), diner till (130), cobbler fittings (753), laundry fittings (1,139), laundry trade (347) and the laundry route (17), all 0 failures; the roof route 53 waypoints, 0 failures on the long runner after its 180 s run hit the ceiling; three sweeps (nine spaces) and the city sweep's 130 views, 0 failures. The completion interiors suite's one route failure, at 1A's fridge, is identical at the merge-base baseline. A close capture from the mail room at 1d65072d (implementation/slice80, mail_bank_room) reads the bank: card windows on the box doors, the two overfull boxes with letters showing, the two doors ajar on a letter and the empty recesses.</t>
         </is>
       </c>
     </row>
@@ -9431,10 +9431,14 @@
       </c>
       <c r="S133" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T133" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>Checked from the mail room's side: the bank's face, its eighteen windows and the slot, faces into the mail room toward its door (mail_bank_room), and the porter board faces into the watch room (F01_WATCH_OV); V1's backs-to-the-corridor facing does not reproduce in V2. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1029,10 +1029,14 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Still present at 088f987a (B1_PUBLIC_CORE_DT1): a hard bright line at the pier and wall seam beside the stair foot, light through a gap in the shell. Deferred to a shell-joint pass.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1305,10 +1309,14 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a lighting-budget decision. Lit, two cage bulbs exceed the 16/16 budget the row names; the unlit warm-emissive alternative needs an emissive finish, and neither the material catalogue nor the fixed-lighting or domestic families carries one.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2079,10 +2087,14 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Chain-link reads only through an alpha-scissor finish, which the material catalogue does not have; a new catalogue material comes first (RUL-008).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2639,10 +2651,14 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: shell work in the blockout and stair generators. The service halls are 1.2 m routes edge to edge, so risers need a chase rather than the hall; the service lift landing and a service stair finish distinct from the public marble are generator changes, as is the dado. The 17 maintenance-evidence rows on the spine wait on it.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2705,10 +2721,14 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Window treatments for every apartment window need blind and curtain variants in the window joinery family and a per-unit state driven by the sleep schedules; CITY_FACADE-001 waits on the same family.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2771,10 +2791,14 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Elsewhere in this pass slice 44 gave three households their bedding states and slice 61 put a water line under every curtain hem; the slack variant across the completion beds, the curtains' drawn and gathered variation with hems, flush cabinet mirrors and the receptor hems remain.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3179,10 +3203,14 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a shell pass. The white brick is the face of retained masonry and the wet stack where no plaster finish quad is emitted (the B1 laundry's stack shows it too); the fix is the shell builder's side-aware plaster emission.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3479,10 +3507,14 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Mouldings and hardware for the completion wardrobes, nightstands, wall cupboards and the sixteen base cabinets are a casework family pass across F04 and F05.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3545,10 +3577,14 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The terrazzo aggregate scale is in the catalogue's terrazzo maps; re-authoring them at 5 to 15 mm chips with brass strips is a material-catalogue change.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3615,10 +3651,14 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the material catalogue has no linoleum; a battleship-linoleum entry comes before the kitchen floor variant.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3755,10 +3795,14 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>Open. At 088f987a the city sweep's rear stations still show ten of eleven rear rooms bare, with the shared brown cubes and an empty shelf; only the funeral parlour reads (site_rear_*_floor_0). The trade receiving families exist (the laundry receiver is captured by its own suite) but none is framed in its rear cell. Re-anchoring them and a cage bulb per rear room are deferred to a rear-room pass.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3899,10 +3943,14 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Ash cans need a street-furniture owner inside the street's route and containment tests, and the droppings' fly shimmer is gated on the commensals ruling (C2).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4019,10 +4067,14 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: a steam plume is a WeatherFX billboard, outside this pass's static families.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4081,10 +4133,14 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: sound only (the acoustic and weather bed); no visual dossier change.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4217,10 +4273,14 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a city-shell pass: the closure masses, alley walls and their finishes are the city generator's geometry. Brick maps, window grids and cornices on every closure mass are open.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4283,10 +4343,14 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>Measured, deferred. The city sweep with the simulated storm (WEATHER_SIMULATE=storm, WEATHER_SEED 7) at 129e02d3 renders the same as the clear sweep, a mean pixel difference of 0.12 in 255 on facade_front_wide (implementation/slice81, both sweeps 130 views, 0 failures): the V2 runtime composes no weather owner, so the brief's quiet storm (live rain, near rain suppressed, the puddle pass) is V1's weather, not yet ported. The dry road and clear sky are therefore what V2 ships, not a capture accident; the storm's port is the open work.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4349,10 +4413,14 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-007: ice cards and curtain states need the window joinery family's states.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4415,10 +4483,14 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T57" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: positional wear on the front door's handle, lock, bell push, mat and stone is a facade wear pass.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4547,10 +4619,14 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: rut and leaf-litter decals on the alley ground are an alley wear pass.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4605,10 +4681,14 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a city-shell pass: the closure masses, alley walls and their finishes are the city generator's geometry. One lit pane on the north neighbour's back is a shell emissive.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4675,10 +4755,14 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a city-shell pass: the closure masses, alley walls and their finishes are the city generator's geometry. Painted cast-iron leaders with stain fans, coping on the wall tops and a finished closing plane are open.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4861,10 +4945,14 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T64" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the reflected train light and the stirring scrap are lighting and weather effects.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4919,10 +5007,14 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T65" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: a second station at the kerb opposite the kiosk is a sweep addition; not a defect until seen closer, as the row says.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4993,10 +5085,14 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T66" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5063,10 +5159,14 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5121,10 +5221,14 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T68" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5183,10 +5287,14 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T69" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5257,10 +5365,14 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5319,10 +5431,14 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T71" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>Checked: at the sweep's hour the passage hours director reports OPEN with ten grilles folded (sweep_city log: [PASSAGE HOURS] OPEN; 10 grilles folded; 10 close after 02:00, the hardware store keeps night service), and the shop interior stations show lit, trading shops. The director's clock binding is correct.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5385,10 +5501,14 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T72" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the parcel shelf, the ghost sign on the throat's brick and the anachronistic tube are passage additions for a later pass.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5443,10 +5563,14 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T73" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the directory's extra line is a passage directory change for a later pass.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5567,10 +5691,14 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T75" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the gas ring's glow, a steam billboard and a wet floor mask are effects.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5633,10 +5761,14 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T76" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The garments on the rail are the fitted family's flat shirt boards; cloth-batch garments with folds need the cloth pipeline. The parcel wall is the laundry trade family's wrapped parcels (slice 75 aged its top row).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5761,10 +5893,14 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T78" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: a dust film with a clean rectangle under the ledger is a cobbler counter wear pass.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6243,10 +6379,14 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T85" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Free-standing caskets need new source records, and the shops' source layout is in the protected building_layout.json (RUL-004).</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6627,10 +6767,14 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T91" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The register now reads with its keys in the diner till family (counter_service at 088f987a); the cream pole and the black cabinet remain to be identified and modelled (diner_backbar.md's cooler).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6693,10 +6837,14 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T92" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a lighting-budget decision: the carboy backlight is a practical light.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6759,10 +6907,14 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T93" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the show-globe glazing (with -001), nickel fountain taps and drawer slips are a druggist fittings pass.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6883,10 +7035,14 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T95" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>Deferred for canon: the headline is the election result in telegram grammar, and the Bible does not yet fix the line; slice 65's broadsides are wordless.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7645,10 +7801,14 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T106" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7707,10 +7867,14 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T107" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7765,10 +7929,14 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T108" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: gated on an owner ruling on Prohibition (the row's own condition).</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7827,10 +7995,14 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T109" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7897,10 +8069,14 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T110" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7955,10 +8131,14 @@
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T111" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8013,10 +8193,14 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T112" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8071,10 +8255,14 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T113" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: gated on an owner ruling on Prohibition (the row's own condition).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8137,10 +8325,14 @@
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T114" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -8203,10 +8395,14 @@
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T115" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -8269,10 +8465,14 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T116" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8335,10 +8535,14 @@
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T117" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8401,10 +8605,14 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T118" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a bar pass. The bar's fittings are native fabrications bound to source censuses by SHA-256 (bar_furniture, bar_pool, bar_stage, bar_instruments); each addition is a census re-capture and refabrication, the path slice 80 took for the signal register.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8479,10 +8687,14 @@
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T119" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The aprons are city-owned exterior ground inside the front entry route and containment tests; no static-object family mounts there yet.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8537,10 +8749,14 @@
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T120" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with CITY_SHOP_NEWS_CIGARS-002 for the election canon, and the apron owner.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8603,10 +8819,14 @@
       </c>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T121" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The rear apron is city-owned ground inside the service alley's route test; no static-object family mounts there yet.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -9015,10 +9235,14 @@
       </c>
       <c r="S127" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T127" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>Closed: no teal order-board slabs and no floating nameplates in any lobby tile at 088f987a (F01_LOBBY OV, RV, TH, DT1 to DT3); the V1 rows do not reproduce in V2.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9077,10 +9301,14 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T128" s="2" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>Closed: no yellow numbered placard and no white brick patch in the lobby at 088f987a (F01_LOBBY_OV, F01_LOBBY_RV).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -9699,10 +9927,14 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T137" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>Deferred to a city-shell pass: the closure masses, alley walls and their finishes are the city generator's geometry. The reading room's windows look onto the light court's unfinished face.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9995,10 +10227,14 @@
       </c>
       <c r="S141" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T141" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10073,10 +10309,14 @@
       </c>
       <c r="S142" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T142" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10139,10 +10379,14 @@
       </c>
       <c r="S143" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T143" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006: the dumbwaiter stands on the 1.2 m route and there is no floor outside it for a sack truck and crates.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10353,10 +10597,14 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T146" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006: the service core's door leaf and landing panel are the spine's finish.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -11333,10 +11581,14 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T158" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>Deferred for an owner restatement. The row's title asks for monitor-top electric evidence, but its construction (an ice card in the kitchen window, a zinc drip tray with a tide line) is icebox evidence, and this household's fridge is a FridgeMonitor in household_fridges.json; a monitor-top unit takes no ice. The icebox households already have their drip pans (slice 18).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -14629,10 +14881,14 @@
       </c>
       <c r="S200" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T200" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -14707,10 +14963,14 @@
       </c>
       <c r="S201" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T201" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -14785,10 +15045,14 @@
       </c>
       <c r="S202" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T202" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -14999,10 +15263,14 @@
       </c>
       <c r="S205" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T205" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006: the plain service stair and the service lift landing are generator changes.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -15565,10 +15833,14 @@
       </c>
       <c r="S212" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T212" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The radio's table, the projector stand and the deck on the coffee table are placed, and a cable form with clips along the skirting from each device to the plate beside the switch is a follow-up.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -19885,10 +20157,14 @@
       </c>
       <c r="S268" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T268" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -19943,10 +20219,14 @@
       </c>
       <c r="S269" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T269" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006: the crossing's ceiling planes are the spine's shell geometry.</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -20021,10 +20301,14 @@
       </c>
       <c r="S270" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T270" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -20099,10 +20383,14 @@
       </c>
       <c r="S271" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T271" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -20469,10 +20757,14 @@
       </c>
       <c r="S276" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T276" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="inlineStr">
+        <is>
+          <t>Identified, deferred. A node probe of the hall's upper volume at b2cf2b70 finds no pipe, only walls, ceilings and 3D's vestibule; the diagonal is the picture rail on the west wall, which stops mid-wall short of 3D's door casing and reads as a loose rod in perspective (f03sw_rail). Ending it at the casing is a millwork-pass item.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -21179,10 +21471,14 @@
       </c>
       <c r="S285" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T285" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr">
+        <is>
+          <t>Deferred for an owner restatement. The row's title asks for monitor-top electric evidence, but its construction (an ice card in the kitchen window, a zinc drip tray with a tide line) is icebox evidence, and this household's fridge is a FridgeMonitor in household_fridges.json; a monitor-top unit takes no ice. The icebox households already have their drip pans (slice 18).</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -25201,10 +25497,14 @@
       </c>
       <c r="S338" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T338" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the landing doors' painted-steel finish, sight glass and sill belong to the lift (elevator.gd), and the brick around them is BW-015's plaster emission.</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -25497,10 +25797,14 @@
       </c>
       <c r="S342" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T342" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -25563,10 +25867,14 @@
       </c>
       <c r="S343" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T343" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T343" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006: the crossing's wainscot relief and floor strip are spine finish.</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -25641,10 +25949,14 @@
       </c>
       <c r="S344" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T344" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -25719,10 +26031,14 @@
       </c>
       <c r="S345" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T345" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -27653,10 +27969,14 @@
       </c>
       <c r="S370" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T370" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The clock needs its hold-E winding verb and a WorkOrders binding; the interaction carrier audit holds clock_prop's "Hold E" prompt as an open violation awaiting K2, so a new winding owner waits on that ruling.</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -28311,10 +28631,14 @@
       </c>
       <c r="S379" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T379" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>Not a defect: V2's light switch family is a toggle by design (light_switch.md: a toggle collar and a porcelain-tipped TogglePivot), and both 4B plates are that family, so the closet switch matches the room switches.</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -31773,10 +32097,14 @@
       </c>
       <c r="S426" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T426" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T426" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: carrying the hall terrazzo and base to 5C's sill is a floor-coverage pass.</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -32073,10 +32401,14 @@
       </c>
       <c r="S430" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T430" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T430" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -32307,10 +32639,14 @@
       </c>
       <c r="S433" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T433" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T433" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -32365,10 +32701,14 @@
       </c>
       <c r="S434" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T434" s="2" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T434" s="2" t="inlineStr">
+        <is>
+          <t>The peephole is the brass lens cylinder of door_prop.gd, and the white disc is the lamp's specular on brass, as BW-014 measured; not a defect. The wall joint goes with BW-006's spine finish.</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -32443,10 +32783,14 @@
       </c>
       <c r="S435" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T435" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T435" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -33117,10 +33461,14 @@
       </c>
       <c r="S444" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T444" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T444" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. Moving the plantable to the window moves four bound families with it: its native work-table fit and seated surface stock, and the counterweight lamp's installation and supply cord plan (task_lamp_installations, task_lamp_supply); the cord must be re-planned from a window-side outlet first.</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -34971,10 +35319,14 @@
       </c>
       <c r="S469" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T469" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T469" s="2" t="inlineStr">
+        <is>
+          <t>Deferred for an owner restatement. The row's title asks for monitor-top electric evidence, but its construction (an ice card in the kitchen window, a zinc drip tray with a tide line) is icebox evidence, and this household's fridge is a FridgeMonitor in household_fridges.json; a monitor-top unit takes no ice. The icebox households already have their drip pans (slice 18).</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -35037,10 +35389,14 @@
       </c>
       <c r="S470" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T470" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T470" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. 5B's fridge contents are the larder copied from fridge_prop.gd's LARDER, which the household fridges family pins by SHA-256 (mechanism_sha256); batteries and film change the pinned mechanism source.</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -37171,10 +37527,14 @@
       </c>
       <c r="S499" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T499" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T499" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The strip and the louvred box are ventilation-family registers, and that family's 23 registers are pinned as a set; BW-005 measured the branches as seated. Removing this one is a ventilation-family change.</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -37631,10 +37991,14 @@
       </c>
       <c r="S505" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T505" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T505" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -37865,10 +38229,14 @@
       </c>
       <c r="S508" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T508" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T508" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -37943,10 +38311,14 @@
       </c>
       <c r="S509" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T509" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T509" s="2" t="inlineStr">
+        <is>
+          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -39097,10 +39469,14 @@
       </c>
       <c r="S524" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T524" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T524" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the mirror renders black without a reflection source in the bath, and the moon's dither through the glass is the sky shader behind the glazing; both are rendering passes.</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -41025,10 +41401,14 @@
       </c>
       <c r="S550" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T550" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T550" s="2" t="inlineStr">
+        <is>
+          <t>Deferred for an owner restatement. The row's title asks for monitor-top electric evidence, but its construction (an ice card in the kitchen window, a zinc drip tray with a tide line) is icebox evidence, and this household's fridge is a FridgeMonitor in household_fridges.json; a monitor-top unit takes no ice. The icebox households already have their drip pans (slice 18).</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -42329,10 +42709,14 @@
       </c>
       <c r="S568" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T568" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T568" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -42415,10 +42799,14 @@
       </c>
       <c r="S569" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T569" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T569" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -42477,10 +42865,14 @@
       </c>
       <c r="S570" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T570" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T570" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -42605,10 +42997,14 @@
       </c>
       <c r="S572" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T572" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T572" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the ventilator housings are the owner JSON's A06 item.</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -42683,10 +43079,14 @@
       </c>
       <c r="S573" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T573" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T573" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -42745,10 +43145,14 @@
       </c>
       <c r="S574" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T574" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T574" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -42823,10 +43227,14 @@
       </c>
       <c r="S575" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T575" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T575" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -42885,10 +43293,14 @@
       </c>
       <c r="S576" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T576" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T576" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: gated on the commensals ruling (C2), and on the roof support path.</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -42963,10 +43375,14 @@
       </c>
       <c r="S577" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T577" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T577" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -43021,10 +43437,14 @@
       </c>
       <c r="S578" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T578" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T578" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -43099,10 +43519,14 @@
       </c>
       <c r="S579" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T579" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T579" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -43157,10 +43581,14 @@
       </c>
       <c r="S580" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T580" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T580" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -43219,10 +43647,14 @@
       </c>
       <c r="S581" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T581" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T581" s="2" t="inlineStr">
+        <is>
+          <t>Deferred: the chimney's bonded joints and stone coping are a roof plant pass (chimney_crown.md).</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -43297,10 +43729,14 @@
       </c>
       <c r="S582" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T582" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T582" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
@@ -43355,10 +43791,14 @@
       </c>
       <c r="S583" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T583" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T583" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -43433,10 +43873,14 @@
       </c>
       <c r="S584" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="T584" s="2" t="inlineStr"/>
+          <t>deferred</t>
+        </is>
+      </c>
+      <c r="T584" s="2" t="inlineStr">
+        <is>
+          <t>Deferred. The roof decks are the sloped membrane with its authored falling field, and the domestic-object inspector seats feet on a flat level datum (inspect_domestic_objects_context.py), so roof objects need a sloped-deck support path first.</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -20301,12 +20301,12 @@
       </c>
       <c r="S270" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F03_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls, and its purpose names bypass and inspection clearance around continuous risers. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
+          <t>Maintenance evidence on the F03 service spine, outside the route: a painted band round each riser at 1.55 m in its service colour (heat ochre, telephone green, electric sky) with a blank kraft tag on a brass wire (no lettering, a deviation from the row's Label3D tags), a brass drain cock low on the heat stack, a slatted crate (a copy of 3B_partscrate) in the dead-end pocket south of the cluster and a hose coiled in five turns on an iron bracket on the east wall beside it (domestic objects risermarks and hosecoil); chalk on the stack, a drip ring under the cock and a boot scuff where the super stands (positional wear). Every riser fitting stands under 0.08 m proud, so the 1.28 m bypass west of the cluster keeps the 1.2 m route. Verified at 9535800b (implementation/slice85): the domestic-objects fabrication module 10,218 checks with every new support seated on a riser or wall face by ray (its one failure, the harness finding no clear camera station for F03's hose in the 0.98 m pocket, is the B1_rinse_taps class); the node probe's route boxes hold only the shell before and after, and the objects only in the cluster, east-half and pocket boxes; the vertical route walks the F03-F06 halls past them (124 waypoints, 0 failures; the F04-F06 halls walked for the first time); blockout, ConnectedWorld and the apartment batch's labels unchanged. The threshold view from the crossing shows the marked pipes and the clear bypass (images/F03_TH, F03_POCKET; lamp-off frames record the hall's darkness).</t>
         </is>
       </c>
     </row>
@@ -25949,12 +25949,12 @@
       </c>
       <c r="S344" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T344" s="2" t="inlineStr">
         <is>
-          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F04_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
+          <t>Maintenance evidence on the F04 service spine, outside the route: a painted band round each riser at 1.55 m in its service colour (heat ochre, telephone green, electric sky) with a blank kraft tag on a brass wire (no lettering, a deviation from the row's Label3D tags), a brass drain cock low on the heat stack, a slatted crate (a copy of 3B_partscrate) in the dead-end pocket south of the cluster and a hose coiled in five turns on an iron bracket on the east wall beside it (domestic objects risermarks and hosecoil); chalk on the stack, a drip ring under the cock and a boot scuff where the super stands (positional wear). Every riser fitting stands under 0.08 m proud, so the 1.28 m bypass west of the cluster keeps the 1.2 m route. Verified at 9535800b (implementation/slice85): the domestic-objects fabrication module 10,218 checks with every new support seated on a riser or wall face by ray (its one failure, the harness finding no clear camera station for F03's hose in the 0.98 m pocket, is the B1_rinse_taps class); the node probe's route boxes hold only the shell before and after, and the objects only in the cluster, east-half and pocket boxes; the vertical route walks the F03-F06 halls past them (124 waypoints, 0 failures; the F04-F06 halls walked for the first time); blockout, ConnectedWorld and the apartment batch's labels unchanged. The threshold view from the crossing shows the marked pipes and the clear bypass (images/F04_TH, F04_POCKET; lamp-off frames record the hall's darkness).</t>
         </is>
       </c>
     </row>
@@ -32401,12 +32401,12 @@
       </c>
       <c r="S430" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T430" s="2" t="inlineStr">
         <is>
-          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F05_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
+          <t>Maintenance evidence on the F05 service spine, outside the route: a painted band round each riser at 1.55 m in its service colour (heat ochre, telephone green, electric sky) with a blank kraft tag on a brass wire (no lettering, a deviation from the row's Label3D tags), a brass drain cock low on the heat stack, a slatted crate (a copy of 3B_partscrate) in the dead-end pocket south of the cluster and a hose coiled in five turns on an iron bracket on the east wall beside it (domestic objects risermarks and hosecoil); chalk on the stack, a drip ring under the cock and a boot scuff where the super stands (positional wear). Every riser fitting stands under 0.08 m proud, so the 1.28 m bypass west of the cluster keeps the 1.2 m route. Verified at 9535800b (implementation/slice85): the domestic-objects fabrication module 10,218 checks with every new support seated on a riser or wall face by ray (its one failure, the harness finding no clear camera station for F03's hose in the 0.98 m pocket, is the B1_rinse_taps class); the node probe's route boxes hold only the shell before and after, and the objects only in the cluster, east-half and pocket boxes; the vertical route walks the F03-F06 halls past them (124 waypoints, 0 failures; the F04-F06 halls walked for the first time); blockout, ConnectedWorld and the apartment batch's labels unchanged. The threshold view from the crossing shows the marked pipes and the clear bypass (images/F05_TH, F05_POCKET; lamp-off frames record the hall's darkness).</t>
         </is>
       </c>
     </row>
@@ -37991,12 +37991,12 @@
       </c>
       <c r="S505" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T505" s="2" t="inlineStr">
         <is>
-          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F06_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
+          <t>Maintenance evidence on the F06 service spine, outside the route: a painted band round each riser at 1.55 m in its service colour (heat ochre, telephone green, electric sky) with a blank kraft tag on a brass wire (no lettering, a deviation from the row's Label3D tags), a brass drain cock low on the heat stack, a slatted crate (a copy of 3B_partscrate) in the dead-end pocket south of the cluster and a hose coiled in five turns on an iron bracket on the east wall beside it (domestic objects risermarks and hosecoil); chalk on the stack, a drip ring under the cock and a boot scuff where the super stands (positional wear). Every riser fitting stands under 0.08 m proud, so the 1.28 m bypass west of the cluster keeps the 1.2 m route. Verified at 9535800b (implementation/slice85): the domestic-objects fabrication module 10,218 checks with every new support seated on a riser or wall face by ray (its one failure, the harness finding no clear camera station for F03's hose in the 0.98 m pocket, is the B1_rinse_taps class); the node probe's route boxes hold only the shell before and after, and the objects only in the cluster, east-half and pocket boxes; the vertical route walks the F03-F06 halls past them (124 waypoints, 0 failures; the F04-F06 halls walked for the first time); blockout, ConnectedWorld and the apartment batch's labels unchanged. The threshold view from the crossing shows the marked pipes and the clear bypass (images/F06_TH, F06_POCKET; lamp-off frames record the hall's darkness).</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>The laundry's water, slices 77 and 78. The washers: cold and hot mains out of the west wall through flanges, on clips above the hanging belt, a drop and brass bib cock at each machine with a rubber hose to its own fill cock, and a cast-iron floor gully taking each drain hose (washer_supply). The rinse tubs: cold and hot out of the west wet stack's face to a pair of long-reach bibs over each tub's back rim, and a cast-iron waste taking both brass drain tails back into the stack (rinse_taps, B1_LAUNDRY views). The context inspector now treats a solid riser's faces as walls. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+          <t>The laundry's water, slices 77 and 78. The washers: cold and hot mains out of the west wall through flanges, on clips above the hanging belt, a drop and brass bib cock at each machine with a rubber hose to its own fill cock, and a cast-iron floor gully taking each drain hose (washer_supply). The rinse tubs: cold and hot out of the west wet stack's face to a pair of long-reach bibs over each tub's back rim, and a cast-iron waste taking both brass drain tails back into the stack (rinse_taps, B1_LAUNDRY views). The context inspector now treats a solid riser's faces as walls. Verified at slice 80's WIP 1d65072d and its predecessor 129e02d3 (implementation/slice80), which differs from it in six files (the lobby box's anchor and name, the patrol suite and two V1 watch tests), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d keeps slice 35's severities on all 49 gates; against the merge-base the candidate verifier then found two new systemic review findings, cleared by slice 82 (5467439f).</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Deferred to a lighting-budget decision. Lit, two cage bulbs exceed the 16/16 budget the row names; the unlit warm-emissive alternative needs an emissive finish, and neither the material catalogue nor the fixed-lighting or domestic families carries one.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note deferred it to a 16/16 lighting budget): on desktop there is no 16/16 budget to exceed. The V2 runtime root composes LightRig, whose per-frame light budget has been off on desktop since 2026-08-08 (light_rig.gd; only shadow casters stay capped, at 32), and BW-017's twelve hall domes already rely on that; mobile keeps its caps (ACTIVE_N_MOBILE 12, SHADOW_N_MOBILE 4). The open work is the two cage bulbs over the firing aisle from the fixed-lighting family's cage_bulb_rise assemblies, rebuilt into that family as slice 3 did, then its fabrication module and a capture of the firing aisle.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>The chute's lower lip rests on a timber bearer laid across a boarded bunker round the heap: side walls of four horizontal boards from the south wall, a front board gate in slotted posts worked down to two boards with the lifted pair standing against the wall, in coal-dusted dark wood (B1_COAL_ROOM_OV, B1_COAL_ROOM_DT2, coal_bunker, delivery_chute_and_bunker). The coal delivery route predated the vestibule leaves and stopped at the inner door; it now opens both, and the coal heap suite runs end to end. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+          <t>The chute's lower lip rests on a timber bearer laid across a boarded bunker round the heap: side walls of four horizontal boards from the south wall, a front board gate in slotted posts worked down to two boards with the lifted pair standing against the wall, in coal-dusted dark wood (B1_COAL_ROOM_OV, B1_COAL_ROOM_DT2, coal_bunker, delivery_chute_and_bunker). The coal delivery route predated the vestibule leaves and stopped at the inner door; it now opens both, and the coal heap suite runs end to end. Verified at slice 80's WIP 1d65072d and its predecessor 129e02d3 (implementation/slice80), which differs from it in six files (the lobby box's anchor and name, the patrol suite and two V1 watch tests), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d keeps slice 35's severities on all 49 gates; against the merge-base the candidate verifier then found two new systemic review findings, cleared by slice 82 (5467439f).</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Partial: the heap is the fabricated mound (coal_heap.glb with collision on its own slope; all fourteen old heap boxes retired), now held in slice 76's boarded bunker. Grime on the whitewash beyond slice 60's chute fan is not done. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+          <t>Partial: the heap is the fabricated mound (coal_heap.glb with collision on its own slope; all fourteen old heap boxes retired), now held in slice 76's boarded bunker. Grime on the whitewash beyond slice 60's chute fan is not done. Verified at slice 80's WIP 1d65072d and its predecessor 129e02d3 (implementation/slice80), which differs from it in six files (the lobby box's anchor and name, the patrol suite and two V1 watch tests), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d keeps slice 35's severities on all 49 gates; against the merge-base the candidate verifier then found two new systemic review findings, cleared by slice 82 (5467439f).</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>At the family recipes: TableRound03/TableRound10 carry an Edwardian turned oak column on a cruciform base of capped feet (column, feet and base in the variant's wood; worktop unchanged); Sofa195/Sofa210 carry rolled arms over the padded arm; Shelf01/02/04/07 stand on square oak posts with oak rails. Plans record column=turned, arms=rolled, posts=oak. The slab seat cushions and the shelves' painted-bin and tin stock (source surfaces) stay as they were. Verified at 4e589c0c: fabrication batch of the twelve rebuilt families exit 0 (tables 64, seating 43, storage 45 instances), upper lighting 9,257 checks with 0 failures, ten-room sweep with 0 failures; native captures of 2A_din_t, 2A_sofa, 2A_shelf0 and 5A_planshelf and the room overviews are under implementation/slice34.</t>
+          <t>At the family recipes: TableRound03/TableRound10 carry an Edwardian turned oak column on a cruciform base of capped feet (column, feet and base in the variant's wood; worktop unchanged); Sofa195/Sofa210 carry rolled arms over the padded arm; Shelf01/02/04/07 stand on square oak posts with oak rails. Plans record column=turned, arms=rolled, posts=oak. The slab seat cushions and the shelves' painted-bin and tin stock (source surfaces) stay as they were. Verified at 4e589c0c: fabrication batch of the twelve rebuilt families exit 0 (tables 64, seating 43, storage 45 instances), upper lighting 9,257 checks with 0 failures, ten-room sweep with 0 failures; native captures of 2A_din_t, 2A_sofa, 2A_shelf0 and 5A_planshelf and the room overviews are under implementation/slice4.</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Deferred: shell work in the blockout and stair generators. The service halls are 1.2 m routes edge to edge, so risers need a chase rather than the hall; the service lift landing and a service stair finish distinct from the public marble are generator changes, as is the dado. The 17 maintenance-evidence rows on the spine wait on it.</t>
+          <t>Deferred: shell work in the blockout and stair generators. Corrected (follow-ups): F01's and F02's service halls, the F02-F06 south halls and the crossings are 1.2 m routes edge to edge, so risers there need a chase rather than the hall; F03-F06's main halls are 2.4 m (x 7.1 to 9.5) with the risers in their east half, so their rows can proceed without the chase. The service lift landing and a service stair finish distinct from the public marble are generator changes, as is the dado. The maintenance-evidence rows on the 1.2 m parts of the spine wait on it.</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Twelve flush domes (flush_dome_rise100 at 2.9 m) on the west and east public halls of F02-F06 (two on the 6.1 m halls of F05/F06), each hall on a landlord's switch beside the stair end or the unit door jamb; blockout anchors, room_lighting records, fixed_lighting plan instances and mirror; family rebuilt. Landings and cores (open stair voids) still have no practical: they need a wall sconce placed against the stair geometry and stay open. Verified at 4e589c0c: upper lighting 9,257 checks, 0 failures (the first run's four F05_C standing-capsule failures cleared with the 5C wardrobe and pigment-table moves); the hall sweep overviews show the domes lit and the switches on the wainscot (implementation/slice3b).</t>
+          <t>Twelve flush domes (flush_dome_rise100 at 2.9 m) on the west and east public halls of F02-F06 (two on the 6.1 m halls of F05/F06), each hall on a landlord's switch beside the stair end or the unit door jamb; blockout anchors, room_lighting records, fixed_lighting plan instances and mirror; family rebuilt. Landings and cores (open stair voids) still have no practical: they need a wall sconce placed against the stair geometry and stay open. Verified at 4e589c0c: upper lighting 9,257 checks, 0 failures (the first run's four F05_C standing-capsule failures cleared with the 5C wardrobe and pigment-table moves); the hall sweep overviews show the domes lit and the switches on the wainscot (implementation/slice3b; the 4e589c0c upper-lighting receipt is implementation/slice4/receipts/upper_lighting.log.receipt.json).</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>Measured, deferred. The city sweep with the simulated storm (WEATHER_SIMULATE=storm, WEATHER_SEED 7) at 129e02d3 renders the same as the clear sweep, a mean pixel difference of 0.12 in 255 on facade_front_wide (implementation/slice81, both sweeps 130 views, 0 failures): the V2 runtime composes no weather owner, so the brief's quiet storm (live rain, near rain suppressed, the puddle pass) is V1's weather, not yet ported. The dry road and clear sky are therefore what V2 ships, not a capture accident; the storm's port is the open work.</t>
+          <t>Measured, deferred. The city sweep with the simulated storm (WEATHER_SIMULATE=storm, WEATHER_SEED 7) at 129e02d3 renders the same as the clear sweep (implementation/slice81, both sweeps 130 views, 0 failures). From the lane PNGs, which stay outside the packet (C:/ov/envimpl_out/slice81), the mean absolute difference is 0.15 in 255 over the three channels on facade_front_wide (0.12 on red and green) and 0.50 on route_orison_to_shop_bodega_1; the packet's JPEG pairs (images/, the storm frame as *_storm.jpg) give 0.35 and 0.86, which is compression noise. No receipt records the weather setting: the V2 runtime composes no weather owner, so the brief's quiet storm (live rain, near rain suppressed, the puddle pass) is V1's weather, not yet ported. The dry road and clear sky are therefore what V2 ships, not a capture accident; the storm's port is the open work.</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note said the bodega has no V2 fittings family): the family exists. orison_v2_bodega_fittings.gd, mounted by the V2 runtime root since 3fb4df4b (2026-10-05, before the dossier's merge-base), swaps the meshes of the 58 TEMPLATE_BODEGA_CELL_V1 nodes in its REPLACE_IDS (aisle goods, counter tins and packets, window crates and baskets, racks and shelves, counter and scale, cooler, practical shades, handcart) from bodega_fittings.glb after checking the digest of the whole exterior_geometry.json; placement, collision and stock visibility stay with the template. The valve-sleeve card and the battery card are new objects with no template node to take a mesh, so the family needs owned assemblies first: new forms in its build script and a runtime path that places them and gives them collision, which the family lacks today (it only re-meshes template nodes). Slices 53 and 54 extended news_fittings and hardware_drawers, which already mount records through orison_v2_shop_seating.</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note said the bodega has no V2 fittings family): the family exists. orison_v2_bodega_fittings.gd, mounted by the V2 runtime root since 3fb4df4b (2026-10-05, before the dossier's merge-base), swaps the meshes of the 58 TEMPLATE_BODEGA_CELL_V1 nodes in its REPLACE_IDS (aisle goods, counter tins and packets, window crates and baskets, racks and shelves, counter and scale, cooler, practical shades, handcart) from bodega_fittings.glb after checking the digest of the whole exterior_geometry.json; placement, collision and stock visibility stay with the template. The back notions counter with its fuses, washers, wire, tape and second ledger is a new assembly with no template node, so the family needs owned assemblies first: new forms in its build script and a runtime path that places them and gives them collision, which the family lacks today (it only re-meshes template nodes). Slices 53 and 54 extended news_fittings and hardware_drawers, which already mount records through orison_v2_shop_seating. It must also leave the 30-waypoint receiving route (OrisonV2BodegaReceivingRouteTest) clear.</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note said the bodega has no V2 fittings family): the family exists. orison_v2_bodega_fittings.gd, mounted by the V2 runtime root since 3fb4df4b (2026-10-05, before the dossier's merge-base), swaps the meshes of the 58 TEMPLATE_BODEGA_CELL_V1 nodes in its REPLACE_IDS (aisle goods, counter tins and packets, window crates and baskets, racks and shelves, counter and scale, cooler, practical shades, handcart) from bodega_fittings.glb after checking the digest of the whole exterior_geometry.json; placement, collision and stock visibility stay with the template. The chalked sale card, the credit ledger and the derby on its nail are new objects with no template node, so the family needs owned assemblies first: new forms in its build script and a runtime path that places them and gives them collision, which the family lacks today (it only re-meshes template nodes). Slices 53 and 54 extended news_fittings and hardware_drawers, which already mount records through orison_v2_shop_seating.</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note said the bodega has no V2 fittings family): the family exists. orison_v2_bodega_fittings.gd, mounted by the V2 runtime root since 3fb4df4b (2026-10-05, before the dossier's merge-base), swaps the meshes of the 58 TEMPLATE_BODEGA_CELL_V1 nodes in its REPLACE_IDS (aisle goods, counter tins and packets, window crates and baskets, racks and shelves, counter and scale, cooler, practical shades, handcart) from bodega_fittings.glb after checking the digest of the whole exterior_geometry.json; placement, collision and stock visibility stay with the template. The family already replaces the cooler's body, frame, glow backing and trims; the two film tins on its lowest shelf are new objects with no template node, so the family needs owned assemblies first: new forms in its build script and a runtime path that places them and gives them collision, which the family lacks today (it only re-meshes template nodes). Slices 53 and 54 extended news_fittings and hardware_drawers, which already mount records through orison_v2_shop_seating.</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>Deferred. The bodega has no V2 fittings family to carry new stock or replace its stand-ins: its interior is the passage's generic shelf stock, so the cards, notions counter, ledger and register need a bodega family first.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note said the interior is the passage's generic shelf stock and the bodega has no V2 fittings family): the stock the review saw is that family's own output. orison_v2_bodega_fittings.gd, mounted since 3fb4df4b (2026-10-05, before the dossier's merge-base), already replaces the aisle goods, counter tins and packets, window crates and baskets and the three ceiling shades, and the packet's bodega_stock capture shows its rimmed tins and basketed cabbages. The row is a rework of that family: varied stock forms (printed bands and seams, torn flaps, burlap sacks, varied produce), a period register on counter_till (a template node the family does not replace today) and opal pendants or a trough reflector for the ceiling fitting. The pinned template digest and the 24.8 MB bodega_fittings.glb bound that slice.</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>Deferred to a lighting-budget decision: the carboy backlight is a practical light.</t>
+          <t>Deferred. Corrected reason (follow-ups; the earlier note deferred it to a lighting-budget decision): on desktop there is no 16/16 budget to exceed. The V2 runtime root composes LightRig, whose per-frame light budget has been off on desktop since 2026-08-08 (light_rig.gd; only shadow casters stay capped, at 32), and BW-017's twelve hall domes already rely on that; mobile keeps its caps (ACTIVE_N_MOBILE 12, SHADOW_N_MOBILE 4). The open work is the practical itself, and it is more than a lamp: orison_v2_druggist_carboys.gd turns shadow casting off on the carboy glass, so the glass throws no coloured light of its own; the colour on the terrazzo must come from a tinted light (or a projector) behind the carboys, judged at the pavement-through-glass station.</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>The night watch's kettle: a cast-iron gas ring with a cream enamel kettle on a deal shelf on iron brackets, on the wall the watch room shares with the lobby, fed by a rubber tube from a brass cock on a gas pipe out of the wall (F01_watch_kettle_native, watch_kettle); and the tour card on the north wall near the key guard, its words a Label3D naming the patrol boxes (F01_WATCH views). Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+          <t>The night watch's kettle: a cast-iron gas ring with a cream enamel kettle on a deal shelf on iron brackets, on the wall the watch room shares with the lobby, fed by a rubber tube from a brass cock on a gas pipe out of the wall (F01_watch_kettle_native, watch_kettle); and the tour card on the north wall near the key guard, its words a Label3D naming the patrol boxes (F01_WATCH views). Verified at slice 80's WIP 1d65072d and its predecessor 129e02d3 (implementation/slice80), which differs from it in six files (the lobby box's anchor and name, the patrol suite and two V1 watch tests), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d keeps slice 35's severities on all 49 gates; against the merge-base the candidate verifier then found two new systemic review findings, cleared by slice 82 (5467439f).</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>Checked from the mail room's side: the bank's face, its eighteen windows and the slot, faces into the mail room toward its door (mail_bank_room), and the porter board faces into the watch room (F01_WATCH_OV); V1's backs-to-the-corridor facing does not reproduce in V2. Verified at slice 80's WIP 1d65072d and its runtime-identical predecessor 129e02d3 (implementation/slice80), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d matches slice 35's on all 49 gates.</t>
+          <t>Checked from the mail room's side: the bank's face, its eighteen windows and the slot, faces into the mail room toward its door (mail_bank_room), and the porter board faces into the watch room (F01_WATCH_OV); V1's backs-to-the-corridor facing does not reproduce in V2. Verified at slice 80's WIP 1d65072d and its predecessor 129e02d3 (implementation/slice80), which differs from it in six files (the lobby box's anchor and name, the patrol suite and two V1 watch tests), which carry slices 76 to 80. The patrol stations suite reports seven boxes, seven marks and seven delivered, 0 failures, and V1's watch register (87/87), watch pair (118/118) and tour key (65/65) suites pass; the fabrication batch's domestic objects and service instruments (12,350 checks) report two capture-harness refusals and no fabrication failure (the tour card is not its notice variant's first instance; the tubs leave no clear camera station in front of the rinse taps); the coal heap route 36 waypoints with 9 heap contacts, the laundry route 17 waypoints, the blockout and M08F suites, all 0 failures; four sweeps (twelve spaces), 0 failures. The M08E spatial suite's one failure and the mail access route's one failure are identical at slice 75's 088f987a (base80). The static gate board at 1d65072d keeps slice 35's severities on all 49 gates; against the merge-base the candidate verifier then found two new systemic review findings, cleared by slice 82 (5467439f).</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+          <t>Deferred with BW-006. Corrected reason (follow-ups; the earlier note said 1.2 m): F01_CORE_TO_SERVICE is 2.0 m across (z -1.0 to 1.0) and 2.9 m long (x 5.4 to 8.3) in orison_v2_blockout.json, and no riser stands in it: the riser cluster is beyond, at x 8.45 to 9.3 in F01_SERVICE_HALL, whose 1.2 m is the whole route. The crate and hose could stand here outside a 1.2 m route; the marked pipes and the cluster wall belong to the hall, which waits on BW-006's chase. A node probe of the passage and a family for the forms come first.</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="T159" s="2" t="inlineStr">
         <is>
-          <t>Evelyn's seven-day medication organizer, two compartments open, stands on the sink's drainboard ribs beside the dish rack: 1A's kitchen has no other free counter (no prep cabinet; the stove and the monitor-top fridge) (1A_medication_organizer_stock, F01_A_KITCHEN_DT1). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+          <t>Evelyn's seven-day medication organizer, two compartments open, stands on the sink's drainboard ribs beside the dish rack: 1A's kitchen has no other free counter (no prep cabinet; the stove and the monitor-top fridge) (1A_medication_organizer_stock, F01_A_KITCHEN_DT1). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing failures (3D's kitchen leg at the fridge in the kitchen-hall opening, 4C's leg into the bathroom, blocked by the open bath-door leaf); upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="T179" s="2" t="inlineStr">
         <is>
-          <t>thermos_and_leftovers: mug and rack on the drainboard; kettle, tin and plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9b).</t>
+          <t>thermos_and_leftovers: mug and rack on the drainboard; kettle, tin and plate on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9e, where 1D's completion route and the fabrication batch pass; implementation/slice9b holds the six runs at ae5f26f6 that the runtime refused at startup with 'invalid preparation cabinet mechanism', before the fix).</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="T184" s="2" t="inlineStr">
         <is>
-          <t>1D's bedside is a Nightstand01 completion copy at the head of the bed under the window, the bed chair moved to the window corner to make room; on it a saucer of wax ear plugs and the fob watch hung on its little brass stand, beside the nightstand's own glass (implementation/slice31b/images/F01_D_BED_DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+          <t>1D's bedside is a Nightstand01 completion copy at the head of the bed under the window, the bed chair moved to the window corner to make room; on it a saucer of wax ear plugs and the fob watch hung on its little brass stand, beside the nightstand's own glass (implementation/slice31b/images/F01_D_BED_DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing failures (3D's kitchen leg at the fridge in the kitchen-hall opening, 4C's leg into the bathroom, blocked by the open bath-door leaf); upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="T192" s="2" t="inlineStr">
         <is>
-          <t>2A's coir mat squared to the jamb (Mina keeps things exact); from the landing it reads beside 2C's worn mat and the two milk bottles waiting at the core (F02_WEST_HALL_OV, 2A_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>2A's coir mat squared to the jamb (Mina keeps things exact); from the landing it reads beside 2C's worn mat and the two milk bottles waiting at the core (F02_WEST_HALL_OV, 2A_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="T194" s="2" t="inlineStr">
         <is>
-          <t>The sealed 2D door's dust mat, new and unmarked, squared at the jamb; read from the hall against 2A's exact coir and 2C's worn mat beyond (F02_SOUTHWEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>The sealed 2D door's dust mat, new and unmarked, squared at the jamb; read from the hall against 2A's exact coir and 2C's worn mat beyond (F02_SOUTHWEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="T198" s="2" t="inlineStr">
         <is>
-          <t>Looking down the east hall from the core: 2C's worn mat and milk at the core end, 2B's rag rug of selvedge scraps at the crossing end (F02_EAST_HALL_RV, F02_SERVICE_CROSSING_OV, 2B_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>Looking down the east hall from the core: 2C's worn mat and milk at the core end, 2B's rag rug of selvedge scraps at the crossing end (F02_EAST_HALL_RV, F02_SERVICE_CROSSING_OV, 2B_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="T222" s="2" t="inlineStr">
         <is>
-          <t>2A's bedroom pinboard (DomesticObject00) is filled to a full grid of 24 cards (implementation/slice35b/images: F02_A_BED_DT1). Not made: the two deliberately overlapping cards; the pinboard form lays a neat grid. Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+          <t>2A's bedroom pinboard (DomesticObject00) is filled to a full grid of 24 cards (implementation/slice35b/images: F02_A_BED_DT1). Not made: the two deliberately overlapping cards; the pinboard form lays a neat grid. Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing bath-door-leaf failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17686,7 @@
       </c>
       <c r="T236" s="2" t="inlineStr">
         <is>
-          <t>2B_fabric_shelf_01/02 posts are oak (BW-003). (implementation/slice34)</t>
+          <t>2B_fabric_shelf_01/02 posts are oak (BW-003). (implementation/slice4)</t>
         </is>
       </c>
     </row>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="T245" s="2" t="inlineStr">
         <is>
-          <t>takeout_plus_coffee: mug and rack on the drainboard; kettle, tin and a second mug on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9b).</t>
+          <t>takeout_plus_coffee: mug and rack on the drainboard; kettle, tin and a second mug on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9e, where 1D's completion route and the fabrication batch pass; implementation/slice9b holds the six runs at ae5f26f6 that the runtime refused at startup with 'invalid preparation cabinet mechanism', before the fix).</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="T250" s="2" t="inlineStr">
         <is>
-          <t>Juno's second wardrobe is the session archive: a wardrobe variant (Wardrobe13, on 5C_w1_wardrobe's case) adds two shelves to the original middle shelf and stands grey reel boxes spine-out with coloured tape on each, and omits the rail; both leaves keep their hinges and 92-degree swing (implementation/slice30b/images/Wardrobe13_open, a native render with the leaves open). Verified at WIP 0efdc84b (implementation/slice30b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; completion 2C 9 waypoints with its one pre-existing kitchen-leg failure; upper kitchens 206 (the branch baseline); the two-room sweep 0 failures.</t>
+          <t>Juno's second wardrobe is the session archive: a wardrobe variant (Wardrobe13, on 5C_w1_wardrobe's case) adds two shelves to the original middle shelf and stands grey reel boxes spine-out with coloured tape on each, and omits the rail; both leaves keep their hinges and 92-degree swing (implementation/slice30b/images/Wardrobe13_open, a native render with the leaves open). Verified at WIP 0efdc84b (implementation/slice30b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; completion 2C 9 waypoints with its one failure at the private hall's bath-door leaf, as at the merge-base; upper kitchens 206 (the branch baseline); the two-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -19394,7 +19394,7 @@
       </c>
       <c r="T258" s="2" t="inlineStr">
         <is>
-          <t>Partial: the sealed door's clean dust mat is squared at the jamb on the hall side, and its one-line notice hangs at 1.5 m in the core notice-frame family (slice 48's Label3D form), both read from the hall (F02_SOUTHWEST_HALL_OV). The strip of brown paper over the letter slot is not made: the leaf has no slot owner to carry a decal. Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>Partial: the sealed door's clean dust mat is squared at the jamb on the hall side, and its one-line notice hangs at 1.5 m in the core notice-frame family (slice 48's Label3D form), both read from the hall (F02_SOUTHWEST_HALL_OV). The strip of brown paper over the letter slot is not made: the leaf has no slot owner to carry a decal. Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F03_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls, and its purpose names bypass and inspection clearance around continuous risers. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
         </is>
       </c>
     </row>
@@ -20470,7 +20470,7 @@
       </c>
       <c r="T272" s="2" t="inlineStr">
         <is>
-          <t>3A's coir mat dark with soil off Malcolm's boots (F03_WEST_HALL_OV, 3A_threshold_native); 3D's plain coir at the far end of the southwest hall reads from the same landing. Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>3A's coir mat dark with soil off Malcolm's boots (F03_WEST_HALL_OV, 3A_threshold_native); 3D's plain coir at the far end of the southwest hall reads from the same landing. Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -20626,7 +20626,7 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>3D's plain coir mat at the hall's door, read from the landing with 3A's soiled mat in the west hall (F03_SOUTHWEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>3D's plain coir mat at the hall's door, read from the landing with 3A's soiled mat in the west hall (F03_SOUTHWEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="T322" s="2" t="inlineStr">
         <is>
-          <t>3D's bedside is a Nightstand02 completion copy at the bed's head (as 1A's), carrying the tuning fork on its chain beside the nightstand's glass; Rhea's burgundy wool scarf hangs over the head post nearest it, folded over the turned finial (F03_D_BED_DT2). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+          <t>3D's bedside is a Nightstand02 completion copy at the bed's head (as 1A's), carrying the tuning fork on its chain beside the nightstand's glass; Rhea's burgundy wool scarf hangs over the head post nearest it, folded over the turned finial (F03_D_BED_DT2). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing failures (3D's kitchen leg at the fridge in the kitchen-hall opening, 4C's leg into the bathroom, blocked by the open bath-door leaf); upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="T330" s="2" t="inlineStr">
         <is>
-          <t>4B's mat worn flat and dark where every boot lands (the player's door), beside 4C's ribbed rubber mat and two milk bottles at the core (F04_WEST_HALL_OV, 4B_threshold_native, 4C_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>4B's mat worn flat and dark where every boot lands (the player's door), beside 4C's ribbed rubber mat and two milk bottles at the core (F04_WEST_HALL_OV, 4B_threshold_native, 4C_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="T339" s="2" t="inlineStr">
         <is>
-          <t>Down the east hall: 4C's ribbed rubber mat and milk pair at the core end, 4A's exact coir mat with the paper folded on it at the crossing end (F04_EAST_HALL_RV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>Down the east hall: 4C's ribbed rubber mat and milk pair at the core end, 4A's exact coir mat with the paper folded on it at the crossing end (F04_EAST_HALL_RV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -25954,7 +25954,7 @@
       </c>
       <c r="T344" s="2" t="inlineStr">
         <is>
-          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F04_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29734,7 @@
       </c>
       <c r="T394" s="2" t="inlineStr">
         <is>
-          <t>Both actors were absent, not misplaced: 4C_story_colorboard's anchor had no furniture record and F04_4C_BOOKSHELF_01 was missing from the bookshelf roster (as was 2C's F02_2C_BOOKSHELF_01). Slice 26 mounts the colour board as a completion copy of 5C's and adds both shelves to the roster (plain cases, Noel Price's and Juno Kells' libraries), registered with the household save owner (203 controls). Verified at WIP c9bc2317 + 432ad0a5 (implementation/slice26): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures once 6C is kept last in the manifest (its suite blanks the last record's canonical book); completion 2C and 4C 9 waypoints with their one pre-existing kitchen-leg failure; upper lighting 0 failures; F04_C_MAIN_DT1 shows the board, F04_C_MAIN_RV and F02_C_MAIN_RV show the new cases.</t>
+          <t>Both actors were absent, not misplaced: 4C_story_colorboard's anchor had no furniture record and F04_4C_BOOKSHELF_01 was missing from the bookshelf roster (as was 2C's F02_2C_BOOKSHELF_01). Slice 26 mounts the colour board as a completion copy of 5C's and adds both shelves to the roster (plain cases, Noel Price's and Juno Kells' libraries), registered with the household save owner (203 controls). Verified at WIP c9bc2317 + 432ad0a5 (implementation/slice26): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; bookshelves 144 checks, 0 failures once 6C is kept last in the manifest (its suite blanks the last record's canonical book); completion 2C and 4C 9 waypoints with their one failure at the private hall's bath-door leaf, as at the merge-base for 2C; upper lighting 0 failures; F04_C_MAIN_DT1 shows the board, F04_C_MAIN_RV and F02_C_MAIN_RV show the new cases.</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="T395" s="2" t="inlineStr">
         <is>
-          <t>quick_food_vs_preserved: mug and rack on the drainboard; two tins and a bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9b).</t>
+          <t>quick_food_vs_preserved: mug and rack on the drainboard; two tins and a bread board on the prep cabinet. Surface-stock records on the sink or prep cabinet support, within the dossier's eight-piece cap; grease film, scorch ring and oilcloth wear stay with the finish pass. Verified at 333c8041: the surface-stock fabrication validator passes 2,644 checks with the 107 records mounted (implementation/slice7/receipts/fabrication_shots__batch.json), the prep-cabinet and toaster validators stay clean, the apartment batch keeps the slice-2 count (236) and upper lighting 0 failures; the kitchen sweeps show the pieces (implementation/slice7). Slice 9 found this home had the prep cabinet anchor but no cabinet consumer, so its cabinet pieces hung in the air; the cabinet is now mounted as a completion copy and the pieces stand on it (implementation/slice9e, where 1D's completion route and the fabrication batch pass; implementation/slice9b holds the six runs at ae5f26f6 that the runtime refused at startup with 'invalid preparation cabinet mechanism', before the fix).</t>
         </is>
       </c>
     </row>
@@ -30190,7 +30190,7 @@
       </c>
       <c r="T400" s="2" t="inlineStr">
         <is>
-          <t>4C's two wardrobes hold different residents' clothes: Cam's (Wardrobe15) hangs maroon jersey and Noel's (Wardrobe08, now used only by 4C_w1) indigo drill; jersey_maroon and drill_indigo are tinted aliases of the catalogue linen (Wardrobe15_open, Wardrobe08_open). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+          <t>4C's two wardrobes hold different residents' clothes: Cam's (Wardrobe15) hangs maroon jersey and Noel's (Wardrobe08, now used only by 4C_w1) indigo drill; jersey_maroon and drill_indigo are tinted aliases of the catalogue linen (Wardrobe15_open, Wardrobe08_open). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing bath-door-leaf failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
         </is>
       </c>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="T403" s="2" t="inlineStr">
         <is>
-          <t>A ChairOak completion copy stands east of 4C's bed with Noel's maroon jersey folded on the seat, one sleeve over the front edge and a pale mended patch on the shoulder (4C_jersey_stock, F04_C_BED1_DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+          <t>A ChairOak completion copy stands east of 4C's bed with Noel's maroon jersey folded on the seat, one sleeve over the front edge and a pale mended patch on the shoulder (4C_jersey_stock, F04_C_BED1_DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing failures (3D's kitchen leg at the fridge in the kitchen-hall opening, 4C's leg into the bathroom, blocked by the open bath-door leaf); upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -32406,7 +32406,7 @@
       </c>
       <c r="T430" s="2" t="inlineStr">
         <is>
-          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F05_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
         </is>
       </c>
     </row>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="T436" s="2" t="inlineStr">
         <is>
-          <t>5A's coir mat and 5B's with the morning paper folded on it, two households side by side in the one hall; 5C's paint-flecked mat at the core (F05_WEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>5A's coir mat and 5B's with the morning paper folded on it, two households side by side in the one hall; 5C's paint-flecked mat at the core (F05_WEST_HALL_OV). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -33980,7 +33980,7 @@
       </c>
       <c r="T451" s="2" t="inlineStr">
         <is>
-          <t>Nadia's corrected floor plan is pinned to the icebox's food door: 5A's icebox has its own variant (FridgeIceboxPlan) whose sheet, ruled walls, copper-inked room and four brass pins belong to the door, so the sheet swings with the leaf and the ice door is untouched (implementation/slice30b/images/F05_A_KITCHEN_OV). The sheet sits on the food door's raised panel (0.43 to 0.83 m) because 1.2 m falls on the ice door; INSPECT stays with the fridge card. Verified at WIP 0efdc84b (implementation/slice30b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; completion 2C 9 waypoints with its one pre-existing kitchen-leg failure; upper kitchens 206 (the branch baseline); the two-room sweep 0 failures.</t>
+          <t>Nadia's corrected floor plan is pinned to the icebox's food door: 5A's icebox has its own variant (FridgeIceboxPlan) whose sheet, ruled walls, copper-inked room and four brass pins belong to the door, so the sheet swings with the leaf and the ice door is untouched (implementation/slice30b/images/F05_A_KITCHEN_OV). The sheet sits on the food door's raised panel (0.43 to 0.83 m) because 1.2 m falls on the ice door; INSPECT stays with the fridge card. Verified at WIP 0efdc84b (implementation/slice30b): fabrication batch 0 failures; apartment batch 236 (the branch baseline); household state 154 checks, 0 failures; completion 2C 9 waypoints with its one failure at the private hall's bath-door leaf, as at the merge-base; upper kitchens 206 (the branch baseline); the two-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -34490,7 +34490,7 @@
       </c>
       <c r="T458" s="2" t="inlineStr">
         <is>
-          <t>5A_planshelf posts are oak (BW-003); the placeholder blocks on it stay as source stock. (implementation/slice34/images/F05_A_STUDY_OV.jpg)</t>
+          <t>5A_planshelf posts are oak (BW-003); the placeholder blocks on it stay as source stock. (implementation/slice4/images/F05_A_STUDY_OV.jpg)</t>
         </is>
       </c>
     </row>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="T466" s="2" t="inlineStr">
         <is>
-          <t>5B_din_t is the pedestal form now (BW-003). (implementation/slice34)</t>
+          <t>5B_din_t is the pedestal form now (BW-003). (implementation/slice4)</t>
         </is>
       </c>
     </row>
@@ -36800,7 +36800,7 @@
       </c>
       <c r="T489" s="2" t="inlineStr">
         <is>
-          <t>Iris's second wardrobe is the pigment store: its own variant (Wardrobe14) adds two shelves above the case's middle shelf and stands rows of pigment tins with painted lids, jars of ground colour and rolled canvas, with no rail (implementation/slice35b/images: Wardrobe14_open, F05_C_STUDIO_DT1). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+          <t>Iris's second wardrobe is the pigment store: its own variant (Wardrobe14) adds two shelves above the case's middle shelf and stands rows of pigment tins with painted lids, jars of ground colour and rolled canvas, with no rail (implementation/slice35b/images: Wardrobe14_open, F05_C_STUDIO_DT1). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing bath-door-leaf failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
         </is>
       </c>
     </row>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="T493" s="2" t="inlineStr">
         <is>
-          <t>A ChairOak copy (5C_bed_chair) stands at the foot of Iris's bed with her navy overalls folded on the seat, both buckled straps over the edge; a small study canvas lies face down on the nightstand, stretcher bars up (5C_overalls_stock, F05_C_BED1_DT2/DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing kitchen-leg failure; upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
+          <t>A ChairOak copy (5C_bed_chair) stands at the foot of Iris's bed with her navy overalls folded on the seat, both buckled straps over the edge; a small study canvas lies face down on the nightstand, stretcher bars up (5C_overalls_stock, F05_C_BED1_DT2/DT3). Verified at WIP 54f7aee1 (implementation/slice31b): fabrication batch 0 failures (rerun_c: the 1D and 3D bedroom close-ups found no clear camera station, so the rerun captures only the jersey, overalls and organizer); apartment batch 236 on the long runner (the batch now exceeds the 180 s serial ceiling); household state 154 checks, 0 failures; completion 1D 25 waypoints, 0 failures; 3D 16 and 4C 9 with their pre-existing failures (3D's kitchen leg at the fridge in the kitchen-hall opening, 4C's leg into the bathroom, blocked by the open bath-door leaf); upper lighting 0 failures; upper furniture 488 against 484 at 40110d19, the four new failures being new stock meshes in the suite's pre-existing material-binding check; the five-room sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -37996,7 +37996,7 @@
       </c>
       <c r="T505" s="2" t="inlineStr">
         <is>
-          <t>Deferred with BW-006. The service spine's halls are 1.2 m wide and the whole width is the route, so the riser cluster, crate and hose this row asks for have no place outside it until BW-006 gives the spine its risers in a chase, its dado and its lighting.</t>
+          <t>Deferred, no longer on BW-006's chase. Corrected reason (follow-ups; the earlier note said 1.2 m and deferred the row with BW-006): F06_SERVICE_HALL is 2.4 m wide (x 7.1 to 9.5 in orison_v2_blockout.json), twice the 1.2 m of F01's and F02's halls. The risers (HEAT_STACK, TELEPHONE_MESSAGE_RISER, ELECTRICAL_SERVICE_RISER) stand in the hall's east half at x 8.45 to 9.3, z 0.3 to 1.15, so beside the cluster the free floor is about 1.35 m, which is the bypass itself; the spare width outside a 1.2 m route is along the rest of the east half, not against the cluster as the row places the crate and hose. The marked pipes can go on the risers. Whether the east half is clear floor is not yet measured: a node probe of the hall at the tip comes first, and the new forms need their own family glb, since surface_stock.glb is 1.72 MiB under GitHub's 100 MiB limit.</t>
         </is>
       </c>
     </row>
@@ -38398,7 +38398,7 @@
       </c>
       <c r="T510" s="2" t="inlineStr">
         <is>
-          <t>6B's worn mat in the hall and 6C's coir mat with a string-tied parcel for the appraiser at the core (F06_WEST_HALL_OV, 6C_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at slice 51's WIP 0bac8f87 (86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
+          <t>6B's worn mat in the hall and 6C's coir mat with a string-tied parcel for the appraiser at the core (F06_WEST_HALL_OV, 6C_threshold_native). Verified at WIP 36f8f9bb (implementation/slice49): fabrication batch 0 failures (six thresholds captured natively); apartment batch 204 on the long runner; household state 154 checks, 0 failures; upper kitchens 206 and upper furniture 488, both identical to slice 48; upper lighting, public doors, the remaining upper transfers, the apartment door route, the first upper hall, the 4B door and rear wing A, all 0 failures; the resident key route, which the serial runner's 180 s ceiling ended without a verdict at this WIP, passes on the long runner at 3f3f0d75, the tree its receipt records (implementation/slice51; 86 waypoints, 0 failures), a tree that carries slice 49 unchanged. Rear wing C's one failure (the 2C bookshelf collision) is identical at slice 48's tip. The three hall sweeps (17 spaces) report 0 failures. Every threshold lies flat inside the 1.2 m hall route, within 0.5 m of its jamb and outside the swing.</t>
         </is>
       </c>
     </row>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="T548" s="2" t="inlineStr">
         <is>
-          <t>6C_sofa carries rolled arms (BW-003); 6C_cof (Coffee06) is unchanged. (implementation/slice34/images/F06_C_MAIN_OV.jpg)</t>
+          <t>6C_sofa carries rolled arms (BW-003); 6C_cof (Coffee06) is unchanged. (implementation/slice4/images/F06_C_MAIN_OV.jpg)</t>
         </is>
       </c>
     </row>
@@ -41608,7 +41608,7 @@
       </c>
       <c r="T553" s="2" t="inlineStr">
         <is>
-          <t>Mae's second wardrobe is the packing store: its variant (Wardrobe12, only 6C_w1's) shelves stacked flat cartons in kraft, folded brown paper and balls of string, with no rail (Wardrobe12_open, F06_C_STUDIO_DT2). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing kitchen-leg failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
+          <t>Mae's second wardrobe is the packing store: its variant (Wardrobe12, only 6C_w1's) shelves stacked flat cartons in kraft, folded brown paper and balls of string, with no rail (Wardrobe12_open, F06_C_STUDIO_DT2). Verified at WIP 815745ee (implementation/slice35b): fabrication batch 0 failures (the wardrobe module accounts for every built variant once Wardrobe08 keeps an instance); apartment batch 236 on the long runner; household state 154 checks, 0 failures; completion 4C 9 waypoints with its pre-existing bath-door-leaf failure; upper kitchens 206; upper furniture 482 (six fewer pre-existing material-binding failures as two wardrobes lose their garments); upper lighting 0 failures; the four-space sweep 0 failures; native renders with the leaves open (images/Wardrobe08_open, 12, 14, 15).</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -1309,12 +1309,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Deferred. Corrected reason (follow-ups; the earlier note deferred it to a 16/16 lighting budget): on desktop there is no 16/16 budget to exceed. The V2 runtime root composes LightRig, whose per-frame light budget has been off on desktop since 2026-08-08 (light_rig.gd; only shadow casters stay capped, at 32), and BW-017's twelve hall domes already rely on that; mobile keeps its caps (ACTIVE_N_MOBILE 12, SHADOW_N_MOBILE 4). The open work is the two cage bulbs over the firing aisle from the fixed-lighting family's cage_bulb_rise assemblies, rebuilt into that family as slice 3 did, then its fabrication module and a capture of the firing aisle.</t>
+          <t>Two cage_bulb_rise160 over the firing aisle at x 10.6, z -1.6 and 0.6 (anchors B1_BOILER_ROOM_LT_A/B, each under an F01 floor with collision, the cage's lowest point about 2.27 m, clear of the 2.13 m fire-door head and of the steam header at z -0.55 and its hangers), on a new B1_BOILER_ROOM circuit whose switch follows the B1 convention on the south wall (10.15, 1.12, -5.4); completion lighting gains the cage_bulb kind. The 16/16 budget the row names does not exist on desktop (light_rig.gd). Verified at 34b4c7c8 (implementation/slice83): fixed lighting 0 failures (ceiling contacts by ray, the door-head clearance, the circuit), switch model, boiler route, basement route and coal delivery 0 failures, wet cloth 0 failures. With the hand lamp off the firing-door station reads the firing door, gauge glass and controls (images/B1_firing_door_before_lampoff against _after_lampoff). The switch is about 5 m from the fire door, by the B1 convention; no route test walks to it.</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Twelve flush domes (flush_dome_rise100 at 2.9 m) on the west and east public halls of F02-F06 (two on the 6.1 m halls of F05/F06), each hall on a landlord's switch beside the stair end or the unit door jamb; blockout anchors, room_lighting records, fixed_lighting plan instances and mirror; family rebuilt. Landings and cores (open stair voids) still have no practical: they need a wall sconce placed against the stair geometry and stay open. Verified at 4e589c0c: upper lighting 9,257 checks, 0 failures (the first run's four F05_C standing-capsule failures cleared with the 5C wardrobe and pigment-table moves); the hall sweep overviews show the domes lit and the switches on the wainscot (implementation/slice3b; the 4e589c0c upper-lighting receipt is implementation/slice4/receipts/upper_lighting.log.receipt.json).</t>
+          <t>Twelve flush domes (flush_dome_rise100 at 2.9 m) on the west and east public halls of F02-F06 (two on the 6.1 m halls of F05/F06), each hall on a landlord's switch beside the stair end or the unit door jamb; blockout anchors, room_lighting records, fixed_lighting plan instances and mirror; family rebuilt. Landings and cores (open stair voids) had no practical here; slice 83 puts a sconce on each landing lobby's south core wall, F02-F06 (F04_LANDING-003). Verified at 4e589c0c: upper lighting 9,257 checks, 0 failures (the first run's four F05_C standing-capsule failures cleared with the 5C wardrobe and pigment-table moves); the hall sweep overviews show the domes lit and the switches on the wainscot (implementation/slice3b; the 4e589c0c upper-lighting receipt is implementation/slice4/receipts/upper_lighting.log.receipt.json).</t>
         </is>
       </c>
     </row>
@@ -24831,12 +24831,12 @@
       </c>
       <c r="S329" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T329" s="2" t="inlineStr">
         <is>
-          <t>The landing has no ceiling (stair void); a sconce on the core wall is the remaining item after BW-017's hall domes.</t>
+          <t>A sconce_globe_back050 on the south core wall of the F04 lift lobby (anchor F04_LANDING_LT_SCONCE [-1.5, 2.0, -3.73], yaw 0: the wall face plus the 50 mm stand-off), on F04_WEST_HALL's circuit (BW-017: switched with the floor); the same sconce stands on the F02, F03, F05 and F06 landings, BW-017's 'one per landing'. Verified at 34b4c7c8 (implementation/slice83): fixed lighting 218 actors, 6,438 checks, 0 failures (each landing sconce's two wall contacts by ray, its envelope clear of the lift front and core wall, its circuit); upper lighting 9,677 checks, 0 failures; household state 210 controls; the elevator, vertical, first-upper-hall, golden-repair and resident-key routes, which walk the lobby, 0 failures. With the hand lamp off at 20:00 the landing station reads the lift plate (images/F04_landing_liftplate_before_lampoff against _after_lampoff) and the 4B transom, which BW-017's hall dome already lit.</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -3133,12 +3133,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>orison_v2_room_lighting.gd adds a brass signal-outlet plate (70 x 115 x 6 mm, brass_dull) beside every switch of the room and completion rosters, on the side toward the room centre so it stays on wall rather than on a jamb. Passive draw: no owner, no collision, no lead stub until a device record connects to it. Verified at 992ae898: upper lighting and LightSwitchModelTest exit 0 with the plates in place; implementation/slice6/images/outlet_detail_F01_A_BED.jpg shows the brass plate beside the bedroom switch.</t>
+          <t>Removed at the owner's direction (2026-10-10): the blank brass plate beside each switch read as an older dark switch that the toggle replaces. It was implemented in slice 6 and verified (implementation/slice6); orison_v2_room_lighting.gd no longer mounts it, so each room has its toggle alone. The Bible VIII.3 signal outlet waits for a form that reads as a socket rather than a switch plate, if the owner wants one back. The same direction seats every switch plate flush on its finished wall.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>Teresa's house bell (new wallbell object): a Bakelite dome on a brass bracket high on the main room's west wall, directly above the switch's signal outlet, its grey cloth flex run down the wall to the outlet with a band of black tape where she tried to cut it; no sound added (implementation/slice42/images: 1D_house_bell_native). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
+          <t>Teresa's house bell (new wallbell object): a Bakelite dome on a brass bracket high on the main room's west wall above the switch, its grey cloth flex run down the wall beside the switch to a Bakelite terminal block above the skirting (it ended at BW-013's signal outlet until the owner had that removed on 2026-10-10), with a band of black tape where she tried to cut it; no sound added (implementation/slice42/images: 1D_house_bell_native). Verified at WIP b0770fb2 (implementation/slice42): fabrication batch 0 failures across 13 modules (the bell, the quiet sign and the route map captured natively); household state 154 checks, 0 failures; upper kitchens 206; upper lighting 0 failures; completion 1D 25 waypoints, 0 failures; the domestic radio test 80/80; the seven-space sweep and two 130-station city sweeps 0 failures. With the cone speaker's materials settled (WIP d351823a, receipts prefixed c_): apartment batch 204 on the long runner (32 fewer of the pre-existing receiver-texture class); upper furniture 496 (eight more of the pre-existing material-binding class); the domestic radio test 80/80; the four-space radio sweep 0 failures.</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="T207" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="T225" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="T241" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="T278" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -22116,7 +22116,7 @@
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -23344,7 +23344,7 @@
       </c>
       <c r="T309" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="T349" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="T367" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -29380,7 +29380,7 @@
       </c>
       <c r="T389" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -30654,7 +30654,7 @@
       </c>
       <c r="T406" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -33256,7 +33256,7 @@
       </c>
       <c r="T441" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
       </c>
       <c r="T460" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -34724,7 +34724,7 @@
       </c>
       <c r="T461" s="2" t="inlineStr">
         <is>
-          <t>5B_battery_case (batterycase form: a wooden case with two glass cells and brass terminals) on the floor west of the switch, where the signal-outlet plate sits, clear of the switch stance and the main opening. The cloth lead to the plate waits for a lead form. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
+          <t>5B_battery_case (batterycase form: a wooden case with two glass cells and brass terminals) on the floor west of the switch, clear of the switch stance and the main opening. The signal plate it would have charged at (BW-013) was removed at the owner's direction on 2026-10-10, so the case stands unconnected. Verified at 3ee31793 (slice24: apartment batch 236, the apartment door route 45 waypoints with 0 failures, completion route 3D 16 as before, upper lighting and the household save owner 0 failures, the five-space sweep 0 failures) and at 2c52a53e (slice24c, the light table withdrawn and the upper-kitchen material check scoped to the cabinets: fabrication 28,545 checks with 0 failures, every piece bearing on its support; upper kitchens 206 with the baseline's three stance labels); captures in implementation/slice24.</t>
         </is>
       </c>
     </row>
@@ -36014,7 +36014,7 @@
       </c>
       <c r="T478" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -38644,7 +38644,7 @@
       </c>
       <c r="T513" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -39906,7 +39906,7 @@
       </c>
       <c r="T530" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>
@@ -40838,7 +40838,7 @@
       </c>
       <c r="T542" s="2" t="inlineStr">
         <is>
-          <t>The brass signal-outlet plate beside the switch came with BW-013 (slice 6); the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
+          <t>The signal-outlet plate beside the switch (BW-013, slice 6) was removed at the owner's direction on 2026-10-10, as the blank brass plate beside each switch read as an older dark switch that the toggle replaces; the chain door guard is on the entry leaf's apartment face: slotted plate by the latch stile, anchor plate and unhooked chain beside it (slice 10). Verified at d38ba7ac (slice10, slice10b): the thirteen families pass the fabrication batch (24,276 checks, 0 failures; seating 51 actors with the two armchairs, 1A's captured natively), door casings and fitted door fabric 0 failures, door hinges 10 as before (the 105-door count and one leaf's knuckles, identical at 6d99760d, slice10c), both door-route suites unchanged (45 and 32 waypoints, 0 failures), completion route 1A 15 waypoints as before (the kitchen leg), apartment batch 236 as before, upper lighting 0 failures, the seven-space sweep 0 failures; the chain guards are shown at the vestibule thresholds and the armchairs in F05_B_MAIN and F01_A_MAIN (implementation/slice10).</t>
         </is>
       </c>
     </row>

--- a/art/reviews/v2_environment_design_20261008/change_register.xlsx
+++ b/art/reviews/v2_environment_design_20261008/change_register.xlsx
@@ -6837,12 +6837,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>Deferred. Corrected reason (follow-ups; the earlier note deferred it to a lighting-budget decision): on desktop there is no 16/16 budget to exceed. The V2 runtime root composes LightRig, whose per-frame light budget has been off on desktop since 2026-08-08 (light_rig.gd; only shadow casters stay capped, at 32), and BW-017's twelve hall domes already rely on that; mobile keeps its caps (ACTIVE_N_MOBILE 12, SHADOW_N_MOBILE 4). The open work is the practical itself, and it is more than a lamp: orison_v2_druggist_carboys.gd turns shadow casting off on the carboy glass, so the glass throws no coloured light of its own; the colour on the terrazzo must come from a tinted light (or a projector) behind the carboys, judged at the pavement-through-glass station.</t>
+          <t>Verified at the owner's go-ahead (2026-10-15): the show globes burn as a druggist's window did. orison_v2_druggist_carboys.gd sets a tinted spot lamp inside each of the four carboy fills (teal, red, green, ochre), aimed out through the shopfront and down onto the aisle terrazzo about 1.5 m from the glass, shadow-free, and gives each fill an emissive override so the globes read as backlit; the shipping mesh materials are untouched. Evidence implementation/otis_lamp at e326950a: OrisonV2DruggistCarboysTest 470 checks, 0 failures, including 19 new show-globe checks (four lamps, inside their carboys, aimed out and down, each its own colour, landing on the aisle floor). The acceptance station, the pavement through the glass with the hand lamp off, shows the four colours on the terrazzo (images/pavement_through_glass).</t>
         </is>
       </c>
     </row>
